--- a/bom/Filament_Falcon_BOM.xlsx
+++ b/bom/Filament_Falcon_BOM.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="564">
   <si>
     <t xml:space="preserve">Category</t>
   </si>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">2x4 SPF stud 8 ft (2438 mm), kiln dried</t>
   </si>
   <si>
-    <t xml:space="preserve">22 used by the cut list + 2 spares. 38 x 89 mm (1.5" x 3.5"). Pick straight boards. Kent web price (store shown: Edmundston) - Moncton may differ</t>
+    <t xml:space="preserve">22 used by the cut list + 2 spares. 38 x 89 mm (1.5" x 3.5"). Pick straight boards. Kent Fredericton price (South/Bishop Dr and North/Two Nations Crossing, same price) checked 2026-10-09</t>
   </si>
   <si>
     <t xml:space="preserve">Frame (see frame/cut_list.md)</t>
@@ -878,19 +878,22 @@
     <t xml:space="preserve">https://kent.ca/en/search?q=2x4x8+stud</t>
   </si>
   <si>
-    <t xml:space="preserve">Kent.ca web price (Edmundston store shown)</t>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kent.ca web price (Fredericton store)</t>
   </si>
   <si>
     <t xml:space="preserve">2x4 SPF 10 ft (3048 mm), kiln dried</t>
   </si>
   <si>
-    <t xml:space="preserve">The two 2450 mm sills. Kent web price from category listing</t>
+    <t xml:space="preserve">The two 2450 mm sills. Kent Fredericton price checked 2026-10-09</t>
   </si>
   <si>
     <t xml:space="preserve">Base sills</t>
   </si>
   <si>
-    <t xml:space="preserve">https://kent.ca/en/shop/building-materials/lumber-plywood/dimensional-lumber-studs</t>
+    <t xml:space="preserve">https://kent.ca/en/2-x-4-x-10-2-better-spf-lumber-kiln-dried-1016338</t>
   </si>
   <si>
     <t xml:space="preserve">https://kent.ca/en/search?q=2x4x10</t>
@@ -1106,7 +1109,7 @@
     <t xml:space="preserve">Local metal supplier</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/search?q=25mm+steel+round+bar+Moncton+NB</t>
+    <t xml:space="preserve">https://www.google.com/search?q=25mm+steel+round+bar+Fredericton+NB</t>
   </si>
   <si>
     <t xml:space="preserve">Estimate - get a quote</t>
@@ -1172,7 +1175,7 @@
     <t xml:space="preserve">Under the pod bearings / supports on the tower posts. Metal shop or cut from flat bar</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/search?q=6mm+steel+plate+Moncton+NB</t>
+    <t xml:space="preserve">https://www.google.com/search?q=6mm+steel+plate+Fredericton+NB</t>
   </si>
   <si>
     <t xml:space="preserve">M10 x 90 coach screws + washers</t>
@@ -1283,7 +1286,7 @@
     <t xml:space="preserve">Pod mechanical locks</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/search?q=laser+cutting+steel+plate+moncton+Moncton+NB</t>
+    <t xml:space="preserve">https://www.google.com/search?q=laser+cutting+steel+plate+Fredericton+NB</t>
   </si>
   <si>
     <t xml:space="preserve">Spring-loaded steel pawl (barrel bolt / gate latch)</t>
@@ -1718,7 +1721,7 @@
     <t xml:space="preserve">Amazon cart total</t>
   </si>
   <si>
-    <t xml:space="preserve">The Filament Falcon - BOM notes (built 2026-10-08, America/Moncton)</t>
+    <t xml:space="preserve">The Filament Falcon - BOM notes (built 2026-10-09, Atlantic time ADT/AST; location Fredericton, NB)</t>
   </si>
   <si>
     <t xml:space="preserve">Sources: filament-falcon/docs/SPEC.md; ff-fw/docs/electronics/README.md; ff-cad (branch cad, commit b743d58): frame/BOM.md v0.2, frame/cut_list.md, docs/mechanical/README.md, switch_bom.md, displays.md.</t>
@@ -1730,7 +1733,7 @@
     <t xml:space="preserve">Filament result: black 3601 cm3 -&gt; 5.26 kg (buy 6 x 1 kg); white 44 cm3 -&gt; 0.06 kg (buy 1 x 1 kg). Red/grey parts (guard lids, throttle grip, gear arm, adapter plates) are counted in black - print them in red/grey if you have it. PLA would need ~2 % less mass, but PETG is required for the harness hub and recommended everywhere.</t>
   </si>
   <si>
-    <t xml:space="preserve">Prices: "Verified amazon.ca price" = read from the amazon.ca product page on 2026-10-08 (buy-box price, CAD, before tax). Kent prices are from kent.ca (store shown online: Edmundston); Moncton store prices may differ. Rows marked Estimate/placeholder are NOT verified prices.</t>
+    <t xml:space="preserve">Prices: "Verified amazon.ca price" = read from the amazon.ca product page on 2026-10-08 (buy-box price, CAD, before tax). Kent prices were read from kent.ca on 2026-10-09 with the Fredericton store selected (Fredericton South, 809 Bishop Dr, and Fredericton North, 25 Two Nations Crossing showed identical prices); they can change, check before buying. Local metal-supplier rows have Google search links for Fredericton NB. Rows marked Estimate/placeholder are NOT verified prices.</t>
   </si>
   <si>
     <t xml:space="preserve">Motion system (v0.2, final per commit b743d58): 2 cradle actuators 10"/1500 N (~364 mm retracted), 2 pod actuators 12"/1000 N (~415 mm retracted), both self-locking; 2 gas struts ~590 N; 25 mm shafts, UCP205/UCF205/SHF25; spring pawls + latch plates + Bowden release; steel hard stops; key, E-stop, 20 A fuse, hold-to-run DPDT, relays as H-bridges, 10 roller limit switches, safety edge. Check actuator retracted length and self-locking before ordering.</t>
@@ -4869,7 +4872,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
         <v>267</v>
       </c>
@@ -4910,10 +4913,10 @@
         <v>273</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>42</v>
+        <v>274</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O53" s="6" t="str">
         <f aca="false">IF(AND(J53="Amazon.ca",G53&gt;0,ISERROR(SEARCH("ALTERNATIVE",A53))),MAX(O$1:O52)+1,"")</f>
@@ -4925,13 +4928,13 @@
         <v>267</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>2</v>
@@ -4955,16 +4958,16 @@
         <v>271</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>42</v>
+        <v>274</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O54" s="6" t="str">
         <f aca="false">IF(AND(J54="Amazon.ca",G54&gt;0,ISERROR(SEARCH("ALTERNATIVE",A54))),MAX(O$1:O53)+1,"")</f>
@@ -4976,13 +4979,13 @@
         <v>267</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>6</v>
@@ -4996,26 +4999,26 @@
         <v>6</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>64.98</v>
+        <v>63.98</v>
       </c>
       <c r="I55" s="5" t="n">
         <f aca="false">IF(H55="","",G55*H55)</f>
-        <v>389.88</v>
+        <v>383.88</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>271</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>42</v>
+        <v>274</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O55" s="6" t="str">
         <f aca="false">IF(AND(J55="Amazon.ca",G55&gt;0,ISERROR(SEARCH("ALTERNATIVE",A55))),MAX(O$1:O54)+1,"")</f>
@@ -5027,13 +5030,13 @@
         <v>267</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>4</v>
@@ -5057,16 +5060,16 @@
         <v>271</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>42</v>
+        <v>274</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O56" s="6" t="str">
         <f aca="false">IF(AND(J56="Amazon.ca",G56&gt;0,ISERROR(SEARCH("ALTERNATIVE",A56))),MAX(O$1:O55)+1,"")</f>
@@ -5078,13 +5081,13 @@
         <v>267</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>1</v>
@@ -5108,16 +5111,16 @@
         <v>271</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>42</v>
+        <v>274</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O57" s="6" t="str">
         <f aca="false">IF(AND(J57="Amazon.ca",G57&gt;0,ISERROR(SEARCH("ALTERNATIVE",A57))),MAX(O$1:O56)+1,"")</f>
@@ -5126,16 +5129,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1</v>
@@ -5156,15 +5159,15 @@
         <v>25</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K58" s="2"/>
       <c r="L58" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O58" s="6" t="str">
         <f aca="false">IF(AND(J58="Amazon.ca",G58&gt;0,ISERROR(SEARCH("ALTERNATIVE",A58))),MAX(O$1:O57)+1,"")</f>
@@ -5173,16 +5176,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>1</v>
@@ -5203,15 +5206,15 @@
         <v>15</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K59" s="2"/>
       <c r="L59" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O59" s="6" t="str">
         <f aca="false">IF(AND(J59="Amazon.ca",G59&gt;0,ISERROR(SEARCH("ALTERNATIVE",A59))),MAX(O$1:O58)+1,"")</f>
@@ -5220,16 +5223,16 @@
     </row>
     <row r="60" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>1</v>
@@ -5250,15 +5253,15 @@
         <v>12</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O60" s="6" t="str">
         <f aca="false">IF(AND(J60="Amazon.ca",G60&gt;0,ISERROR(SEARCH("ALTERNATIVE",A60))),MAX(O$1:O59)+1,"")</f>
@@ -5267,16 +5270,16 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>1</v>
@@ -5297,15 +5300,15 @@
         <v>15</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K61" s="2"/>
       <c r="L61" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O61" s="6" t="str">
         <f aca="false">IF(AND(J61="Amazon.ca",G61&gt;0,ISERROR(SEARCH("ALTERNATIVE",A61))),MAX(O$1:O60)+1,"")</f>
@@ -5314,16 +5317,16 @@
     </row>
     <row r="62" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>1</v>
@@ -5347,10 +5350,10 @@
         <v>39</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>42</v>
@@ -5365,16 +5368,16 @@
     </row>
     <row r="63" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>4</v>
@@ -5398,10 +5401,10 @@
         <v>39</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>42</v>
@@ -5416,16 +5419,16 @@
     </row>
     <row r="64" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>1</v>
@@ -5449,10 +5452,10 @@
         <v>39</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>42</v>
@@ -5467,16 +5470,16 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>8</v>
@@ -5497,15 +5500,15 @@
         <v>12</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K65" s="2"/>
       <c r="L65" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O65" s="6" t="str">
         <f aca="false">IF(AND(J65="Amazon.ca",G65&gt;0,ISERROR(SEARCH("ALTERNATIVE",A65))),MAX(O$1:O64)+1,"")</f>
@@ -5514,16 +5517,16 @@
     </row>
     <row r="66" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>1</v>
@@ -5547,10 +5550,10 @@
         <v>39</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M66" s="2" t="s">
         <v>42</v>
@@ -5565,16 +5568,16 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>1</v>
@@ -5595,15 +5598,15 @@
         <v>4</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O67" s="6" t="str">
         <f aca="false">IF(AND(J67="Amazon.ca",G67&gt;0,ISERROR(SEARCH("ALTERNATIVE",A67))),MAX(O$1:O66)+1,"")</f>
@@ -5612,16 +5615,16 @@
     </row>
     <row r="68" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>1</v>
@@ -5645,10 +5648,10 @@
         <v>39</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>42</v>
@@ -5663,16 +5666,16 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>1</v>
@@ -5693,15 +5696,15 @@
         <v>30</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O69" s="6" t="str">
         <f aca="false">IF(AND(J69="Amazon.ca",G69&gt;0,ISERROR(SEARCH("ALTERNATIVE",A69))),MAX(O$1:O68)+1,"")</f>
@@ -5710,16 +5713,16 @@
     </row>
     <row r="70" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>2</v>
@@ -5743,10 +5746,10 @@
         <v>39</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>42</v>
@@ -5761,16 +5764,16 @@
     </row>
     <row r="71" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>1</v>
@@ -5794,10 +5797,10 @@
         <v>39</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>42</v>
@@ -5812,16 +5815,16 @@
     </row>
     <row r="72" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>2</v>
@@ -5845,10 +5848,10 @@
         <v>39</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>42</v>
@@ -5863,16 +5866,16 @@
     </row>
     <row r="73" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>2</v>
@@ -5896,10 +5899,10 @@
         <v>39</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>42</v>
@@ -5914,16 +5917,16 @@
     </row>
     <row r="74" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>4</v>
@@ -5944,15 +5947,15 @@
         <v>40</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K74" s="2"/>
       <c r="L74" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O74" s="6" t="str">
         <f aca="false">IF(AND(J74="Amazon.ca",G74&gt;0,ISERROR(SEARCH("ALTERNATIVE",A74))),MAX(O$1:O73)+1,"")</f>
@@ -5961,16 +5964,16 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>20</v>
@@ -5991,15 +5994,15 @@
         <v>25</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K75" s="2"/>
       <c r="L75" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O75" s="6" t="str">
         <f aca="false">IF(AND(J75="Amazon.ca",G75&gt;0,ISERROR(SEARCH("ALTERNATIVE",A75))),MAX(O$1:O74)+1,"")</f>
@@ -6008,16 +6011,16 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>8</v>
@@ -6038,15 +6041,15 @@
         <v>12</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K76" s="2"/>
       <c r="L76" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O76" s="6" t="str">
         <f aca="false">IF(AND(J76="Amazon.ca",G76&gt;0,ISERROR(SEARCH("ALTERNATIVE",A76))),MAX(O$1:O75)+1,"")</f>
@@ -6055,16 +6058,16 @@
     </row>
     <row r="77" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>2</v>
@@ -6088,10 +6091,10 @@
         <v>39</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>42</v>
@@ -6106,16 +6109,16 @@
     </row>
     <row r="78" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>2</v>
@@ -6139,10 +6142,10 @@
         <v>39</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>42</v>
@@ -6157,16 +6160,16 @@
     </row>
     <row r="79" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>1</v>
@@ -6190,10 +6193,10 @@
         <v>39</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>42</v>
@@ -6208,16 +6211,16 @@
     </row>
     <row r="80" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>1</v>
@@ -6241,10 +6244,10 @@
         <v>39</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>42</v>
@@ -6259,16 +6262,16 @@
     </row>
     <row r="81" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>4</v>
@@ -6289,15 +6292,15 @@
         <v>32</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K81" s="2"/>
       <c r="L81" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O81" s="6" t="str">
         <f aca="false">IF(AND(J81="Amazon.ca",G81&gt;0,ISERROR(SEARCH("ALTERNATIVE",A81))),MAX(O$1:O80)+1,"")</f>
@@ -6306,16 +6309,16 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>2</v>
@@ -6336,15 +6339,15 @@
         <v>50</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K82" s="2"/>
       <c r="L82" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O82" s="6" t="str">
         <f aca="false">IF(AND(J82="Amazon.ca",G82&gt;0,ISERROR(SEARCH("ALTERNATIVE",A82))),MAX(O$1:O81)+1,"")</f>
@@ -6353,16 +6356,16 @@
     </row>
     <row r="83" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>2</v>
@@ -6386,10 +6389,10 @@
         <v>39</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M83" s="2" t="s">
         <v>42</v>
@@ -6404,16 +6407,16 @@
     </row>
     <row r="84" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>1</v>
@@ -6437,10 +6440,10 @@
         <v>39</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M84" s="2" t="s">
         <v>42</v>
@@ -6455,16 +6458,16 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>4</v>
@@ -6485,15 +6488,15 @@
         <v>16</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K85" s="2"/>
       <c r="L85" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O85" s="6" t="str">
         <f aca="false">IF(AND(J85="Amazon.ca",G85&gt;0,ISERROR(SEARCH("ALTERNATIVE",A85))),MAX(O$1:O84)+1,"")</f>
@@ -6502,16 +6505,16 @@
     </row>
     <row r="86" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>1</v>
@@ -6535,10 +6538,10 @@
         <v>39</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M86" s="2" t="s">
         <v>42</v>
@@ -6553,16 +6556,16 @@
     </row>
     <row r="87" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>1</v>
@@ -6586,10 +6589,10 @@
         <v>39</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M87" s="2" t="s">
         <v>42</v>
@@ -6604,16 +6607,16 @@
     </row>
     <row r="88" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>1</v>
@@ -6637,10 +6640,10 @@
         <v>39</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>42</v>
@@ -6655,16 +6658,16 @@
     </row>
     <row r="89" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>1</v>
@@ -6706,16 +6709,16 @@
     </row>
     <row r="90" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>1</v>
@@ -6739,10 +6742,10 @@
         <v>39</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M90" s="2" t="s">
         <v>42</v>
@@ -6757,16 +6760,16 @@
     </row>
     <row r="91" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E91" s="2" t="n">
         <v>1</v>
@@ -6790,10 +6793,10 @@
         <v>39</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M91" s="2" t="s">
         <v>42</v>
@@ -6808,16 +6811,16 @@
     </row>
     <row r="92" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>1</v>
@@ -6841,10 +6844,10 @@
         <v>39</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M92" s="2" t="s">
         <v>42</v>
@@ -6859,16 +6862,16 @@
     </row>
     <row r="93" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>2</v>
@@ -6892,10 +6895,10 @@
         <v>39</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M93" s="2" t="s">
         <v>42</v>
@@ -6910,16 +6913,16 @@
     </row>
     <row r="94" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>1</v>
@@ -6943,10 +6946,10 @@
         <v>39</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M94" s="2" t="s">
         <v>42</v>
@@ -6961,16 +6964,16 @@
     </row>
     <row r="95" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>1</v>
@@ -6991,15 +6994,15 @@
         <v>150</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K95" s="2"/>
       <c r="L95" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M95" s="2"/>
       <c r="N95" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O95" s="6" t="str">
         <f aca="false">IF(AND(J95="Amazon.ca",G95&gt;0,ISERROR(SEARCH("ALTERNATIVE",A95))),MAX(O$1:O94)+1,"")</f>
@@ -7008,16 +7011,16 @@
     </row>
     <row r="96" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>2</v>
@@ -7041,10 +7044,10 @@
         <v>39</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M96" s="2" t="s">
         <v>42</v>
@@ -7059,16 +7062,16 @@
     </row>
     <row r="97" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>1</v>
@@ -7092,10 +7095,10 @@
         <v>39</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M97" s="2" t="s">
         <v>42</v>
@@ -7110,16 +7113,16 @@
     </row>
     <row r="98" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>1</v>
@@ -7144,7 +7147,7 @@
       </c>
       <c r="K98" s="2"/>
       <c r="L98" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M98" s="2"/>
       <c r="N98" s="3" t="s">
@@ -7157,16 +7160,16 @@
     </row>
     <row r="99" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>1</v>
@@ -7190,10 +7193,10 @@
         <v>39</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M99" s="2" t="s">
         <v>42</v>
@@ -7208,16 +7211,16 @@
     </row>
     <row r="100" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>1</v>
@@ -7241,16 +7244,16 @@
         <v>39</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M100" s="2" t="s">
         <v>42</v>
       </c>
       <c r="N100" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O100" s="6" t="n">
         <f aca="false">IF(AND(J100="Amazon.ca",G100&gt;0,ISERROR(SEARCH("ALTERNATIVE",A100))),MAX(O$1:O99)+1,"")</f>
@@ -7259,16 +7262,16 @@
     </row>
     <row r="101" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>1</v>
@@ -7292,10 +7295,10 @@
         <v>39</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M101" s="2" t="s">
         <v>42</v>
@@ -7310,16 +7313,16 @@
     </row>
     <row r="102" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>1</v>
@@ -7343,10 +7346,10 @@
         <v>39</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L102" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M102" s="2" t="s">
         <v>42</v>
@@ -7361,16 +7364,16 @@
     </row>
     <row r="103" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>1</v>
@@ -7394,10 +7397,10 @@
         <v>39</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M103" s="2" t="s">
         <v>42</v>
@@ -7412,16 +7415,16 @@
     </row>
     <row r="104" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>10</v>
@@ -7442,15 +7445,15 @@
         <v>60</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K104" s="2"/>
       <c r="L104" s="7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M104" s="2"/>
       <c r="N104" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O104" s="6" t="str">
         <f aca="false">IF(AND(J104="Amazon.ca",G104&gt;0,ISERROR(SEARCH("ALTERNATIVE",A104))),MAX(O$1:O103)+1,"")</f>
@@ -7459,16 +7462,16 @@
     </row>
     <row r="105" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>1</v>
@@ -7492,10 +7495,10 @@
         <v>39</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L105" s="7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M105" s="2" t="s">
         <v>42</v>
@@ -7510,16 +7513,16 @@
     </row>
     <row r="106" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>1</v>
@@ -7543,10 +7546,10 @@
         <v>39</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L106" s="7" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M106" s="2" t="s">
         <v>42</v>
@@ -7561,16 +7564,16 @@
     </row>
     <row r="107" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>1</v>
@@ -7594,10 +7597,10 @@
         <v>39</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L107" s="7" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M107" s="2" t="s">
         <v>42</v>
@@ -7612,16 +7615,16 @@
     </row>
     <row r="108" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>2</v>
@@ -7645,10 +7648,10 @@
         <v>39</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L108" s="7" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M108" s="2" t="s">
         <v>42</v>
@@ -7769,7 +7772,7 @@
     <hyperlink ref="L52" r:id="rId89" display="https://www.amazon.ca/s?k=self+tapping+screw+assortment+m2.5+m3"/>
     <hyperlink ref="K53" r:id="rId90" display="https://kent.ca/en/2-x-4-x-8-spf-stud-kiln-dried-1016318"/>
     <hyperlink ref="L53" r:id="rId91" display="https://kent.ca/en/search?q=2x4x8+stud"/>
-    <hyperlink ref="K54" r:id="rId92" display="https://kent.ca/en/shop/building-materials/lumber-plywood/dimensional-lumber-studs"/>
+    <hyperlink ref="K54" r:id="rId92" display="https://kent.ca/en/2-x-4-x-10-2-better-spf-lumber-kiln-dried-1016338"/>
     <hyperlink ref="L54" r:id="rId93" display="https://kent.ca/en/search?q=2x4x10"/>
     <hyperlink ref="K55" r:id="rId94" display="https://kent.ca/en/3-4-x-4-x-8-18-5mm-spruce-plywood-standard-1015824"/>
     <hyperlink ref="L55" r:id="rId95" display="https://kent.ca/en/search?q=3%2F4+plywood+4x8"/>
@@ -7793,7 +7796,7 @@
     <hyperlink ref="L67" r:id="rId113" display="https://kent.ca/en/search?q=m6+x+30+bolt"/>
     <hyperlink ref="K68" r:id="rId114" display="https://www.amazon.ca/dp/B0G5ZDQB47"/>
     <hyperlink ref="L68" r:id="rId115" display="https://www.amazon.ca/s?k=25mm+shaft+1000mm"/>
-    <hyperlink ref="L69" r:id="rId116" display="https://www.google.com/search?q=25mm+steel+round+bar+Moncton+NB"/>
+    <hyperlink ref="L69" r:id="rId116" display="https://www.google.com/search?q=25mm+steel+round+bar+Fredericton+NB"/>
     <hyperlink ref="K70" r:id="rId117" display="https://www.amazon.ca/dp/B0D9RTBQF2"/>
     <hyperlink ref="L70" r:id="rId118" display="https://www.amazon.ca/s?k=shf25+shaft+support"/>
     <hyperlink ref="K71" r:id="rId119" display="https://www.amazon.ca/dp/B08HJYZK1X"/>
@@ -7802,7 +7805,7 @@
     <hyperlink ref="L72" r:id="rId122" display="https://www.amazon.ca/s?k=ucf205+flange+bearing+25mm"/>
     <hyperlink ref="K73" r:id="rId123" display="https://www.amazon.ca/dp/B0G2Q98L26"/>
     <hyperlink ref="L73" r:id="rId124" display="https://www.amazon.ca/s?k=25mm+shaft+collar+steel"/>
-    <hyperlink ref="L74" r:id="rId125" display="https://www.google.com/search?q=6mm+steel+plate+Moncton+NB"/>
+    <hyperlink ref="L74" r:id="rId125" display="https://www.google.com/search?q=6mm+steel+plate+Fredericton+NB"/>
     <hyperlink ref="L75" r:id="rId126" display="https://kent.ca/en/search?q=m10+x+90+lag+screw"/>
     <hyperlink ref="L76" r:id="rId127" display="https://kent.ca/en/search?q=m8+x+60+bolt"/>
     <hyperlink ref="K77" r:id="rId128" display="https://www.amazon.ca/dp/B0FKMS7Y12"/>
@@ -7814,7 +7817,7 @@
     <hyperlink ref="K80" r:id="rId134" display="https://www.amazon.ca/dp/B07SJ6B3QP"/>
     <hyperlink ref="L80" r:id="rId135" display="https://www.amazon.ca/s?k=10mm+ball+stud+gas+strut+bracket"/>
     <hyperlink ref="L81" r:id="rId136" display="https://kent.ca/en/search?q=heavy+steel+angle+bracket"/>
-    <hyperlink ref="L82" r:id="rId137" display="https://www.google.com/search?q=laser+cutting+steel+plate+moncton+Moncton+NB"/>
+    <hyperlink ref="L82" r:id="rId137" display="https://www.google.com/search?q=laser+cutting+steel+plate+Fredericton+NB"/>
     <hyperlink ref="K83" r:id="rId138" display="https://www.amazon.ca/dp/B07GZHSCP6"/>
     <hyperlink ref="L83" r:id="rId139" display="https://www.amazon.ca/s?k=spring+loaded+barrel+bolt+latch+heavy+duty"/>
     <hyperlink ref="K84" r:id="rId140" display="https://www.amazon.ca/dp/B0B8C66T4Q"/>
@@ -7893,13 +7896,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8018,12 +8021,12 @@
       </c>
       <c r="D8" s="9" t="n">
         <f aca="false">SUMIF(BOM!$A$2:$A$108,A8,BOM!$I$2:$I$108)</f>
-        <v>682.07</v>
+        <v>676.07</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">COUNTIF(BOM!$A$2:$A$108,A9)</f>
@@ -8040,7 +8043,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">COUNTIF(BOM!$A$2:$A$108,A10)</f>
@@ -8057,7 +8060,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">COUNTIF(BOM!$A$2:$A$108,A11)</f>
@@ -8074,7 +8077,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">COUNTIF(BOM!$A$2:$A$108,A12)</f>
@@ -8091,7 +8094,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B13" s="0" t="n">
         <f aca="false">COUNTIF(BOM!$A$2:$A$108,A13)</f>
@@ -8108,7 +8111,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B14" s="0" t="n">
         <f aca="false">COUNTIF(BOM!$A$2:$A$108,A14)</f>
@@ -8125,7 +8128,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">COUNTIF(BOM!$A$2:$A$108,A15)</f>
@@ -8142,7 +8145,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C17" s="0" t="n">
         <f aca="false">SUMPRODUCT((ISERROR(SEARCH("ALTERNATIVE",A2:A15)))*C2:C15)</f>
@@ -8150,12 +8153,12 @@
       </c>
       <c r="D17" s="11" t="n">
         <f aca="false">SUMPRODUCT((ISERROR(SEARCH("ALTERNATIVE",A2:A15)))*D2:D15)</f>
-        <v>3370.04</v>
+        <v>3364.04</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D18" s="9" t="n">
         <f aca="false">SUMPRODUCT((BOM!$J$2:$J$108="Amazon.ca")*ISERROR(SEARCH("ALTERNATIVE",BOM!$A$2:$A$108))*N(+BOM!$I$2:$I$108))</f>
@@ -8164,16 +8167,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D19" s="9" t="n">
         <f aca="false">SUMPRODUCT(ISNUMBER(SEARCH("Kent",BOM!$J$2:$J$108))*N(+BOM!$I$2:$I$108))</f>
-        <v>910.07</v>
+        <v>904.07</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D20" s="9" t="n">
         <f aca="false">SUMPRODUCT((ISNUMBER(SEARCH("supplier",BOM!$J$2:$J$108)))*N(+BOM!$I$2:$I$108))</f>
@@ -8182,16 +8185,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D21" s="9" t="n">
         <f aca="false">SUMPRODUCT((ISNUMBER(SEARCH("Verified amazon.ca price",BOM!$N$2:$N$108))+ISNUMBER(SEARCH("Kent.ca web price",BOM!$N$2:$N$108))&gt;0)*ISERROR(SEARCH("ALTERNATIVE",BOM!$A$2:$A$108))*N(+BOM!$I$2:$I$108))</f>
-        <v>2779.04</v>
+        <v>2773.04</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D22" s="9" t="n">
         <f aca="false">SUMPRODUCT((ISNUMBER(SEARCH("estimate",BOM!$N$2:$N$108)))*ISERROR(SEARCH("ALTERNATIVE",BOM!$A$2:$A$108))*N(+BOM!$I$2:$I$108))</f>
@@ -8200,7 +8203,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D23" s="9" t="n">
         <f aca="false">SUMPRODUCT(ISNUMBER(SEARCH("ALTERNATIVE",BOM!$A$2:$A$108))*N(+BOM!$I$2:$I$108))</f>
@@ -8209,12 +8212,12 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -8246,7 +8249,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>1</v>
@@ -8267,7 +8270,7 @@
         <v>11</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11872,7 +11875,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="10" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E123" s="9" t="n">
         <f aca="false">SUM(E2:E121)</f>
@@ -11903,47 +11906,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>

--- a/bom/Filament_Falcon_BOM.xlsx
+++ b/bom/Filament_Falcon_BOM.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">BOM!$A$1:$O$108</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">BOM!$A$1:$O$110</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="569">
   <si>
     <t xml:space="preserve">Category</t>
   </si>
@@ -1220,55 +1220,37 @@
     <t xml:space="preserve">https://www.amazon.ca/s?k=12v+linear+actuator+10+inch+stroke+330+lbs</t>
   </si>
   <si>
-    <t xml:space="preserve">Pod linear actuator 12 V, 12" (305 mm) stroke, 1000 N (225 lbf), self-locking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spec: ~415 mm (16.3") retracted, &lt;= 10 mm/s, PULL to raise; 141 N normally, 390 N each if both struts fail. Listing: 300 mm stroke, retracted 405 mm (10 mm short of 415 - adjust anchor in frame_model.py or confirm), self-locking, built-in limits, IP65 | Listing: "Justech 225 LBS/1000N-12inch/300mm 12V Linear Actuator, Electric Actuator"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pod rotate up/down</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amazon.ca/dp/B0CPHS87F8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amazon.ca/s?k=12v+linear+actuator+12+inch+stroke+225+lbs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gas struts (pair), 10" (254 mm) extended, 120 lb / 534 N, 10 mm ball-stud ends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPEC: F1 = 590 N, ~240 mm extended, &gt;= 70 mm stroke; buy 550-600 N or an adjustable-valve strut. This listing (254 mm extended, 169 mm compressed = 85 mm stroke) is the closest found but only 534 N (~10 % low) - an adjustable 600 N strut is better (see search link) | Listing: "Qty (2) 4062 10 inch 120LB/534n Gas Strut Shocks Spring Lift Supports for Leer Camper Shell Window, "</t>
+    <t xml:space="preserve">Pod linear actuator 12 V, 12" (300 mm) stroke, 1500 N (330 lbf), self-locking - ONE (left casing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: 420 mm retracted pin-to-pin (model uses 436 -&gt; 706 mm of 420 -&gt; 720), &lt;= 10 mm/s, EXTEND to lower / RETRACT to raise; &lt;= 561 N normally, 850 N if both struts fail (1.8x margin). Listing (checked 2026-10-10, CA$67.82): RVMARINEPAT LA03-12-300-1500N, 300 mm stroke, 420/720 mm, 10 mm/s, self-locking, built-in limits, 4 A, brackets + polarity switch; same family as the cradle actuators. Pick size "300-1500N" | Listing: "Electric Actuator 12V 12 Inch Stroke, 330lb Heavy Duty Linear Actuator Lift, High Speed Linear Actua"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pod rotate up/down (single actuator + torque tube)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ca/dp/B0FKMVCQPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ca/s?k=12v+linear+actuator+12+inch+stroke+330+lbs+1500N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gas struts (pair), ~250 mm extended, ~1050 N (235 lbf) each, M8 eye ends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPEC: F1 ~1050 N (buy 1000-1100 N), ~240 mm extended, &gt;= 71 mm stroke, 10 mm rod / 22-28 mm body, M8 eyelets (NOT 10 mm ball studs - only ~890 N rated). Sized so the pod is LIFT-biased (+16..+88 N m): an actuator failure sends it UP. Candidate (not verifiable today): YLLL 250 mm universal gas strut pair, 1000/1100 N, 8 mm eye hole, https://www.amazon.ca/dp/B09VDN2PX8 - price is an estimate</t>
   </si>
   <si>
     <t xml:space="preserve">Pod counterbalance</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.amazon.ca/dp/B0D7ZRQNJ9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amazon.ca/s?k=adjustable+gas+strut+600N+250mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 mm ball-stud gas strut mounting brackets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If the struts do not include ball-stud brackets | Listing: "Vepagoo 10mm Ball Stud Gas Strut Mounting Brackets, Silver"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strut anchors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amazon.ca/dp/B07SJ6B3QP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amazon.ca/s?k=10mm+ball+stud+gas+strut+bracket</t>
+    <t xml:space="preserve">https://www.amazon.ca/s?k=gas+strut+1000N+250mm+M8+eyelet+pair</t>
   </si>
   <si>
     <t xml:space="preserve">Steel angle brackets 50 x 50 x 5 mm with M8 hole</t>
   </si>
   <si>
-    <t xml:space="preserve">Strut and actuator anchors on the tower posts / casings (heavy, not shelf brackets)</t>
+    <t xml:space="preserve">2 strut anchors + 1 pod actuator anchor on the casings (heavy, not shelf brackets)</t>
   </si>
   <si>
     <t xml:space="preserve">Strut + actuator anchors</t>
@@ -1277,6 +1259,39 @@
     <t xml:space="preserve">https://kent.ca/en/search?q=heavy+steel+angle+bracket</t>
   </si>
   <si>
+    <t xml:space="preserve">Torque tube: 2" x 2" x 1/8" square steel tube (HSS / A500), 1600 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ties the right cheek to the driven left cheek, behind the back sheet between the 2x4 stiffener rails. 298 N m/deg: 0.42 deg (6 mm at the chin) with both struts failed; 1.5 deg / 32 MPa if the actuator stalls against a right-side stop. Cut to length at the metal shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pod: one actuator drives both cheeks without racking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/search?q=2x2x1%2F8+square+steel+tube+Fredericton+NB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 mm steel plates 150 x 61 mm, 4 x 11 mm holes (2 welded tube end plates + 2 backing plates)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End plates welded square to the tube (or no-weld: 2 x 50x50x5 angles per end); backing plates on the outside of each cheek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torque tube to cheeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/search?q=6mm+steel+plate+cut+to+size+welding+Fredericton+NB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M10 x 70 bolts grade 8.8 + nylocks + washers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 per tube end through the 36 mm cheek + backing plate; 1 mm reamed holes, torque to spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://kent.ca/en/search?q=m10+x+70+bolt+grade+8.8</t>
+  </si>
+  <si>
     <t xml:space="preserve">6 mm steel latch plates with UP and DOWN notches</t>
   </si>
   <si>
@@ -1349,7 +1364,7 @@
     <t xml:space="preserve">12 V 20 A (240 W) enclosed power supply</t>
   </si>
   <si>
-    <t xml:space="preserve">BOM: 12 V 20 A, enclosed, mains fused. Only one motion runs at a time (2 actuators) | Listing: "inShareplus 12V 20A 240W, DC Universal Regulated Switching Power Supply, Converter AC 100-240V to DC"</t>
+    <t xml:space="preserve">BOM: 12 V 20 A, enclosed, mains fused. Only one motion runs at a time (cradle: 2 actuators in parallel, pod: 1 actuator) | Listing: "inShareplus 12V 20A 240W, DC Universal Regulated Switching Power Supply, Converter AC 100-240V to DC"</t>
   </si>
   <si>
     <t xml:space="preserve">Actuator power</t>
@@ -1418,7 +1433,7 @@
     <t xml:space="preserve">12 V 30/40 A automotive relays SPDT 5-pin, 10 pcs</t>
   </si>
   <si>
-    <t xml:space="preserve">5 needed: 4 as two H-bridges (cradle, pod) + 1 for the key. Add relay sockets/harnesses | Listing: "10 Pcs 5-Pin Automotive Relays, 12V 30/40 A SPDT Relays, Electrical Relays Switch for Truck Marine B"</t>
+    <t xml:space="preserve">5 needed: 4 as two H-bridges (cradle: 2 actuators in parallel; pod: the single actuator) + 1 for the key. Add relay sockets/harnesses | Listing: "10 Pcs 5-Pin Automotive Relays, 12V 30/40 A SPDT Relays, Electrical Relays Switch for Truck Marine B"</t>
   </si>
   <si>
     <t xml:space="preserve">Motor switching</t>
@@ -1433,7 +1448,7 @@
     <t xml:space="preserve">V-15 roller-lever micro switches 15 A, 10 pcs</t>
   </si>
   <si>
-    <t xml:space="preserve">10 needed (8 motor-path limits/lock switches + 2 READ contacts) + printed limit_switch_mount; 2nd pack = spares | Listing: "10pcs Micro Switches V-156-1C25 15A 125/250VAC Hinge Roller Lever Switch"</t>
+    <t xml:space="preserve">10 needed (8 motor-path limit/lock switches: CRADLE_UPRIGHT, CRADLE_RECLINED x2, ONE pod limit set POD_UP + POD_DOWN on the left/driven cheek only, POD_UP_LOCKED x2, lever switch; + 2 READ contacts) + printed limit_switch_mount; 2nd pack = spares | Listing: "10pcs Micro Switches V-156-1C25 15A 125/250VAC Hinge Roller Lever Switch"</t>
   </si>
   <si>
     <t xml:space="preserve">Limit + lock switches</t>
@@ -1724,7 +1739,7 @@
     <t xml:space="preserve">The Filament Falcon - BOM notes (built 2026-10-09, Atlantic time ADT/AST; location Fredericton, NB)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sources: filament-falcon/docs/SPEC.md; ff-fw/docs/electronics/README.md; ff-cad (branch cad, commit b743d58): frame/BOM.md v0.2, frame/cut_list.md, docs/mechanical/README.md, switch_bom.md, displays.md.</t>
+    <t xml:space="preserve">Sources: filament-falcon/docs/SPEC.md; ff-fw/docs/electronics/README.md; filament-falcon (branch pod-single, frame v0.3 single pod actuator): frame/BOM.md v0.3, frame/cut_list.md, docs/mechanical/README.md, switch_bom.md, displays.md.</t>
   </si>
   <si>
     <t xml:space="preserve">Filament method: python trimesh volume V and surface area A of every 3MF (panels: single-material body = black, letter inserts = white; printed parts x quantities from docs/mechanical/README.md). Printed volume = shell + infill x (V - shell), shell = min(V, A x 1.2 mm) (3 perimeters x 0.4 mm, also used as top/bottom skin proxy); infill 25 % (monitor standoffs 50 %, harness hub 45 %). PETG 1.27 g/cm3, +15 % for purge/brim/failed prints.</t>
@@ -1736,7 +1751,7 @@
     <t xml:space="preserve">Prices: "Verified amazon.ca price" = read from the amazon.ca product page on 2026-10-08 (buy-box price, CAD, before tax). Kent prices were read from kent.ca on 2026-10-09 with the Fredericton store selected (Fredericton South, 809 Bishop Dr, and Fredericton North, 25 Two Nations Crossing showed identical prices); they can change, check before buying. Local metal-supplier rows have Google search links for Fredericton NB. Rows marked Estimate/placeholder are NOT verified prices.</t>
   </si>
   <si>
-    <t xml:space="preserve">Motion system (v0.2, final per commit b743d58): 2 cradle actuators 10"/1500 N (~364 mm retracted), 2 pod actuators 12"/1000 N (~415 mm retracted), both self-locking; 2 gas struts ~590 N; 25 mm shafts, UCP205/UCF205/SHF25; spring pawls + latch plates + Bowden release; steel hard stops; key, E-stop, 20 A fuse, hold-to-run DPDT, relays as H-bridges, 10 roller limit switches, safety edge. Check actuator retracted length and self-locking before ordering.</t>
+    <t xml:space="preserve">Motion system (v0.3, branch pod-single): 2 cradle actuators 10"/1500 N (~364 mm retracted, self-locking); ONE pod actuator 12"/1500 N self-locking (420 mm retracted, left casing) driving both pod cheeks through a 2x2x1/8" steel torque tube; 2 gas struts ~1050 N with M8 eye ends, sized so the pod is lift-biased (actuator or clevis-pin failure sends it UP, never down); 25 mm shafts, UCP205/UCF205/SHF25; spring pawls + latch plates + Bowden release; steel hard stops; key, E-stop, 20 A fuse, hold-to-run DPDT, relays as 2 H-bridges, one pod limit set (left cheek), roller limit switches, safety edge. Check actuator retracted length and self-locking before ordering.</t>
   </si>
   <si>
     <t xml:space="preserve">SAFETY: the B0B3J1GCVQ buckles are plastic luggage buckles (~50 kg quoted break load, not safety-rated). Positioning harness only for a slow reclining seat. A rated metal-buckle 4-point harness is listed as an ALTERNATIVE row (excluded from totals; switch if you prefer).</t>
@@ -2248,7 +2263,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O108"/>
+  <dimension ref="A1:O110"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -6107,7 +6122,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
         <v>382</v>
       </c>
@@ -6121,7 +6136,7 @@
         <v>390</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -6129,14 +6144,14 @@
       </c>
       <c r="G78" s="2" t="n">
         <f aca="false">IF(OR(F78=TRUE(),F78="TRUE"),0,E78)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>48.49</v>
+        <v>67.82</v>
       </c>
       <c r="I78" s="5" t="n">
         <f aca="false">IF(H78="","",G78*H78)</f>
-        <v>96.98</v>
+        <v>67.82</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>39</v>
@@ -6158,7 +6173,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
         <v>382</v>
       </c>
@@ -6183,47 +6198,43 @@
         <v>1</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>30.09</v>
+        <v>60</v>
       </c>
       <c r="I79" s="5" t="n">
         <f aca="false">IF(H79="","",G79*H79)</f>
-        <v>30.09</v>
+        <v>60</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K79" s="7" t="s">
+      <c r="K79" s="2"/>
+      <c r="L79" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="L79" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="M79" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="M79" s="2"/>
       <c r="N79" s="3" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="O79" s="6" t="n">
         <f aca="false">IF(AND(J79="Amazon.ca",G79&gt;0,ISERROR(SEARCH("ALTERNATIVE",A79))),MAX(O$1:O78)+1,"")</f>
         <v>57</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
         <v>382</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="D80" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>400</v>
-      </c>
       <c r="E80" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F80" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -6231,50 +6242,46 @@
       </c>
       <c r="G80" s="2" t="n">
         <f aca="false">IF(OR(F80=TRUE(),F80="TRUE"),0,E80)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>21.99</v>
+        <v>8</v>
       </c>
       <c r="I80" s="5" t="n">
         <f aca="false">IF(H80="","",G80*H80)</f>
-        <v>21.99</v>
+        <v>24</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K80" s="7" t="s">
-        <v>401</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="K80" s="2"/>
       <c r="L80" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="M80" s="2"/>
       <c r="N80" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O80" s="6" t="n">
+        <v>302</v>
+      </c>
+      <c r="O80" s="6" t="str">
         <f aca="false">IF(AND(J80="Amazon.ca",G80&gt;0,ISERROR(SEARCH("ALTERNATIVE",A80))),MAX(O$1:O79)+1,"")</f>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v/>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
         <v>382</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>405</v>
-      </c>
       <c r="E81" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F81" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -6282,46 +6289,46 @@
       </c>
       <c r="G81" s="2" t="n">
         <f aca="false">IF(OR(F81=TRUE(),F81="TRUE"),0,E81)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="I81" s="5" t="n">
         <f aca="false">IF(H81="","",G81*H81)</f>
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K81" s="2"/>
       <c r="L81" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="3" t="s">
-        <v>302</v>
+        <v>352</v>
       </c>
       <c r="O81" s="6" t="str">
         <f aca="false">IF(AND(J81="Amazon.ca",G81&gt;0,ISERROR(SEARCH("ALTERNATIVE",A81))),MAX(O$1:O80)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
         <v>382</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>409</v>
-      </c>
       <c r="E82" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -6329,21 +6336,21 @@
       </c>
       <c r="G82" s="2" t="n">
         <f aca="false">IF(OR(F82=TRUE(),F82="TRUE"),0,E82)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I82" s="5" t="n">
         <f aca="false">IF(H82="","",G82*H82)</f>
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>350</v>
       </c>
       <c r="K82" s="2"/>
       <c r="L82" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="3" t="s">
@@ -6354,21 +6361,21 @@
         <v/>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
         <v>382</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F83" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -6376,50 +6383,46 @@
       </c>
       <c r="G83" s="2" t="n">
         <f aca="false">IF(OR(F83=TRUE(),F83="TRUE"),0,E83)</f>
+        <v>8</v>
+      </c>
+      <c r="H83" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H83" s="5" t="n">
-        <v>16.99</v>
       </c>
       <c r="I83" s="5" t="n">
         <f aca="false">IF(H83="","",G83*H83)</f>
-        <v>33.98</v>
+        <v>16</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K83" s="7" t="s">
-        <v>413</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="K83" s="2"/>
       <c r="L83" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="M83" s="2"/>
       <c r="N83" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O83" s="6" t="n">
+        <v>302</v>
+      </c>
+      <c r="O83" s="6" t="str">
         <f aca="false">IF(AND(J83="Amazon.ca",G83&gt;0,ISERROR(SEARCH("ALTERNATIVE",A83))),MAX(O$1:O82)+1,"")</f>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v/>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
         <v>382</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -6427,50 +6430,46 @@
       </c>
       <c r="G84" s="2" t="n">
         <f aca="false">IF(OR(F84=TRUE(),F84="TRUE"),0,E84)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>23.99</v>
+        <v>25</v>
       </c>
       <c r="I84" s="5" t="n">
         <f aca="false">IF(H84="","",G84*H84)</f>
-        <v>23.99</v>
+        <v>50</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K84" s="7" t="s">
-        <v>418</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="K84" s="2"/>
       <c r="L84" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="M84" s="2"/>
       <c r="N84" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O84" s="6" t="n">
+        <v>352</v>
+      </c>
+      <c r="O84" s="6" t="str">
         <f aca="false">IF(AND(J84="Amazon.ca",G84&gt;0,ISERROR(SEARCH("ALTERNATIVE",A84))),MAX(O$1:O83)+1,"")</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v/>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
         <v>382</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F85" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -6478,29 +6477,33 @@
       </c>
       <c r="G85" s="2" t="n">
         <f aca="false">IF(OR(F85=TRUE(),F85="TRUE"),0,E85)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>4</v>
+        <v>16.99</v>
       </c>
       <c r="I85" s="5" t="n">
         <f aca="false">IF(H85="","",G85*H85)</f>
-        <v>16</v>
+        <v>33.98</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="K85" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="K85" s="7" t="s">
+        <v>418</v>
+      </c>
       <c r="L85" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="M85" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="N85" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="O85" s="6" t="str">
+        <v>43</v>
+      </c>
+      <c r="O85" s="6" t="n">
         <f aca="false">IF(AND(J85="Amazon.ca",G85&gt;0,ISERROR(SEARCH("ALTERNATIVE",A85))),MAX(O$1:O84)+1,"")</f>
-        <v/>
+        <v>58</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6508,13 +6511,13 @@
         <v>382</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>1</v>
@@ -6528,20 +6531,20 @@
         <v>1</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>17.99</v>
+        <v>23.99</v>
       </c>
       <c r="I86" s="5" t="n">
         <f aca="false">IF(H86="","",G86*H86)</f>
-        <v>17.99</v>
+        <v>23.99</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="M86" s="2" t="s">
         <v>42</v>
@@ -6551,24 +6554,24 @@
       </c>
       <c r="O86" s="6" t="n">
         <f aca="false">IF(AND(J86="Amazon.ca",G86&gt;0,ISERROR(SEARCH("ALTERNATIVE",A86))),MAX(O$1:O85)+1,"")</f>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>429</v>
+        <v>382</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -6576,47 +6579,43 @@
       </c>
       <c r="G87" s="2" t="n">
         <f aca="false">IF(OR(F87=TRUE(),F87="TRUE"),0,E87)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>33.99</v>
+        <v>4</v>
       </c>
       <c r="I87" s="5" t="n">
         <f aca="false">IF(H87="","",G87*H87)</f>
-        <v>33.99</v>
+        <v>16</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K87" s="7" t="s">
-        <v>433</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="K87" s="2"/>
       <c r="L87" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="M87" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="M87" s="2"/>
       <c r="N87" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O87" s="6" t="n">
+        <v>302</v>
+      </c>
+      <c r="O87" s="6" t="str">
         <f aca="false">IF(AND(J87="Amazon.ca",G87&gt;0,ISERROR(SEARCH("ALTERNATIVE",A87))),MAX(O$1:O86)+1,"")</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v/>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>435</v>
-      </c>
       <c r="C88" s="3" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>1</v>
@@ -6630,20 +6629,20 @@
         <v>1</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>18.99</v>
+        <v>17.99</v>
       </c>
       <c r="I88" s="5" t="n">
         <f aca="false">IF(H88="","",G88*H88)</f>
-        <v>18.99</v>
+        <v>17.99</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>42</v>
@@ -6653,21 +6652,21 @@
       </c>
       <c r="O88" s="6" t="n">
         <f aca="false">IF(AND(J88="Amazon.ca",G88&gt;0,ISERROR(SEARCH("ALTERNATIVE",A88))),MAX(O$1:O87)+1,"")</f>
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>1</v>
@@ -6681,20 +6680,20 @@
         <v>1</v>
       </c>
       <c r="H89" s="5" t="n">
-        <v>26.11</v>
+        <v>33.99</v>
       </c>
       <c r="I89" s="5" t="n">
         <f aca="false">IF(H89="","",G89*H89)</f>
-        <v>26.11</v>
+        <v>33.99</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>198</v>
+        <v>438</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>199</v>
+        <v>439</v>
       </c>
       <c r="M89" s="2" t="s">
         <v>42</v>
@@ -6704,21 +6703,21 @@
       </c>
       <c r="O89" s="6" t="n">
         <f aca="false">IF(AND(J89="Amazon.ca",G89&gt;0,ISERROR(SEARCH("ALTERNATIVE",A89))),MAX(O$1:O88)+1,"")</f>
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>1</v>
@@ -6732,20 +6731,20 @@
         <v>1</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>16.24</v>
+        <v>18.99</v>
       </c>
       <c r="I90" s="5" t="n">
         <f aca="false">IF(H90="","",G90*H90)</f>
-        <v>16.24</v>
+        <v>18.99</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="M90" s="2" t="s">
         <v>42</v>
@@ -6755,21 +6754,21 @@
       </c>
       <c r="O90" s="6" t="n">
         <f aca="false">IF(AND(J90="Amazon.ca",G90&gt;0,ISERROR(SEARCH("ALTERNATIVE",A90))),MAX(O$1:O89)+1,"")</f>
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E91" s="2" t="n">
         <v>1</v>
@@ -6783,20 +6782,20 @@
         <v>1</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>13.98</v>
+        <v>26.11</v>
       </c>
       <c r="I91" s="5" t="n">
         <f aca="false">IF(H91="","",G91*H91)</f>
-        <v>13.98</v>
+        <v>26.11</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>451</v>
+        <v>198</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>452</v>
+        <v>199</v>
       </c>
       <c r="M91" s="2" t="s">
         <v>42</v>
@@ -6806,21 +6805,21 @@
       </c>
       <c r="O91" s="6" t="n">
         <f aca="false">IF(AND(J91="Amazon.ca",G91&gt;0,ISERROR(SEARCH("ALTERNATIVE",A91))),MAX(O$1:O90)+1,"")</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>1</v>
@@ -6834,20 +6833,20 @@
         <v>1</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>22.99</v>
+        <v>16.24</v>
       </c>
       <c r="I92" s="5" t="n">
         <f aca="false">IF(H92="","",G92*H92)</f>
-        <v>22.99</v>
+        <v>16.24</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="M92" s="2" t="s">
         <v>42</v>
@@ -6857,24 +6856,24 @@
       </c>
       <c r="O92" s="6" t="n">
         <f aca="false">IF(AND(J92="Amazon.ca",G92&gt;0,ISERROR(SEARCH("ALTERNATIVE",A92))),MAX(O$1:O91)+1,"")</f>
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -6882,23 +6881,23 @@
       </c>
       <c r="G93" s="2" t="n">
         <f aca="false">IF(OR(F93=TRUE(),F93="TRUE"),0,E93)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>16.69</v>
+        <v>13.98</v>
       </c>
       <c r="I93" s="5" t="n">
         <f aca="false">IF(H93="","",G93*H93)</f>
-        <v>33.38</v>
+        <v>13.98</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="M93" s="2" t="s">
         <v>42</v>
@@ -6908,21 +6907,21 @@
       </c>
       <c r="O93" s="6" t="n">
         <f aca="false">IF(AND(J93="Amazon.ca",G93&gt;0,ISERROR(SEARCH("ALTERNATIVE",A93))),MAX(O$1:O92)+1,"")</f>
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>1</v>
@@ -6936,20 +6935,20 @@
         <v>1</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>8.99</v>
+        <v>22.99</v>
       </c>
       <c r="I94" s="5" t="n">
         <f aca="false">IF(H94="","",G94*H94)</f>
-        <v>8.99</v>
+        <v>22.99</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="M94" s="2" t="s">
         <v>42</v>
@@ -6959,24 +6958,24 @@
       </c>
       <c r="O94" s="6" t="n">
         <f aca="false">IF(AND(J94="Amazon.ca",G94&gt;0,ISERROR(SEARCH("ALTERNATIVE",A94))),MAX(O$1:O93)+1,"")</f>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -6984,46 +6983,50 @@
       </c>
       <c r="G95" s="2" t="n">
         <f aca="false">IF(OR(F95=TRUE(),F95="TRUE"),0,E95)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>150</v>
+        <v>16.69</v>
       </c>
       <c r="I95" s="5" t="n">
         <f aca="false">IF(H95="","",G95*H95)</f>
-        <v>150</v>
+        <v>33.38</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="K95" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="K95" s="7" t="s">
+        <v>466</v>
+      </c>
       <c r="L95" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="M95" s="2"/>
+        <v>467</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="N95" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="O95" s="6" t="str">
+        <v>43</v>
+      </c>
+      <c r="O95" s="6" t="n">
         <f aca="false">IF(AND(J95="Amazon.ca",G95&gt;0,ISERROR(SEARCH("ALTERNATIVE",A95))),MAX(O$1:O94)+1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -7031,23 +7034,23 @@
       </c>
       <c r="G96" s="2" t="n">
         <f aca="false">IF(OR(F96=TRUE(),F96="TRUE"),0,E96)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>17.09</v>
+        <v>8.99</v>
       </c>
       <c r="I96" s="5" t="n">
         <f aca="false">IF(H96="","",G96*H96)</f>
-        <v>34.18</v>
+        <v>8.99</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="M96" s="2" t="s">
         <v>42</v>
@@ -7057,21 +7060,21 @@
       </c>
       <c r="O96" s="6" t="n">
         <f aca="false">IF(AND(J96="Amazon.ca",G96&gt;0,ISERROR(SEARCH("ALTERNATIVE",A96))),MAX(O$1:O95)+1,"")</f>
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>1</v>
@@ -7085,47 +7088,43 @@
         <v>1</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>29.99</v>
+        <v>150</v>
       </c>
       <c r="I97" s="5" t="n">
         <f aca="false">IF(H97="","",G97*H97)</f>
-        <v>29.99</v>
+        <v>150</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K97" s="7" t="s">
-        <v>481</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="K97" s="2"/>
       <c r="L97" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="M97" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="M97" s="2"/>
       <c r="N97" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O97" s="6" t="n">
+        <v>352</v>
+      </c>
+      <c r="O97" s="6" t="str">
         <f aca="false">IF(AND(J97="Amazon.ca",G97&gt;0,ISERROR(SEARCH("ALTERNATIVE",A97))),MAX(O$1:O96)+1,"")</f>
-        <v>71</v>
+        <v/>
       </c>
     </row>
     <row r="98" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>483</v>
+        <v>434</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -7133,43 +7132,47 @@
       </c>
       <c r="G98" s="2" t="n">
         <f aca="false">IF(OR(F98=TRUE(),F98="TRUE"),0,E98)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>60</v>
+        <v>17.09</v>
       </c>
       <c r="I98" s="5" t="n">
         <f aca="false">IF(H98="","",G98*H98)</f>
-        <v>60</v>
+        <v>34.18</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K98" s="2"/>
+      <c r="K98" s="7" t="s">
+        <v>481</v>
+      </c>
       <c r="L98" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="M98" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="N98" s="3" t="s">
-        <v>210</v>
+        <v>43</v>
       </c>
       <c r="O98" s="6" t="n">
         <f aca="false">IF(AND(J98="Amazon.ca",G98&gt;0,ISERROR(SEARCH("ALTERNATIVE",A98))),MAX(O$1:O97)+1,"")</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>488</v>
-      </c>
       <c r="C99" s="3" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>1</v>
@@ -7183,20 +7186,20 @@
         <v>1</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>32.15</v>
+        <v>29.99</v>
       </c>
       <c r="I99" s="5" t="n">
         <f aca="false">IF(H99="","",G99*H99)</f>
-        <v>32.15</v>
+        <v>29.99</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="M99" s="2" t="s">
         <v>42</v>
@@ -7206,21 +7209,21 @@
       </c>
       <c r="O99" s="6" t="n">
         <f aca="false">IF(AND(J99="Amazon.ca",G99&gt;0,ISERROR(SEARCH("ALTERNATIVE",A99))),MAX(O$1:O98)+1,"")</f>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>1</v>
@@ -7234,44 +7237,40 @@
         <v>1</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="I100" s="5" t="n">
         <f aca="false">IF(H100="","",G100*H100)</f>
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K100" s="7" t="s">
-        <v>497</v>
-      </c>
+      <c r="K100" s="2"/>
       <c r="L100" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="M100" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="M100" s="2"/>
       <c r="N100" s="3" t="s">
-        <v>499</v>
+        <v>210</v>
       </c>
       <c r="O100" s="6" t="n">
         <f aca="false">IF(AND(J100="Amazon.ca",G100&gt;0,ISERROR(SEARCH("ALTERNATIVE",A100))),MAX(O$1:O99)+1,"")</f>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>500</v>
-      </c>
       <c r="C101" s="3" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>1</v>
@@ -7285,20 +7284,20 @@
         <v>1</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>19.99</v>
+        <v>32.15</v>
       </c>
       <c r="I101" s="5" t="n">
         <f aca="false">IF(H101="","",G101*H101)</f>
-        <v>19.99</v>
+        <v>32.15</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="M101" s="2" t="s">
         <v>42</v>
@@ -7308,21 +7307,21 @@
       </c>
       <c r="O101" s="6" t="n">
         <f aca="false">IF(AND(J101="Amazon.ca",G101&gt;0,ISERROR(SEARCH("ALTERNATIVE",A101))),MAX(O$1:O100)+1,"")</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>1</v>
@@ -7336,44 +7335,44 @@
         <v>1</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>15.99</v>
+        <v>13</v>
       </c>
       <c r="I102" s="5" t="n">
         <f aca="false">IF(H102="","",G102*H102)</f>
-        <v>15.99</v>
+        <v>13</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="L102" s="7" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="M102" s="2" t="s">
         <v>42</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>43</v>
+        <v>504</v>
       </c>
       <c r="O102" s="6" t="n">
         <f aca="false">IF(AND(J102="Amazon.ca",G102&gt;0,ISERROR(SEARCH("ALTERNATIVE",A102))),MAX(O$1:O101)+1,"")</f>
-        <v>76</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>1</v>
@@ -7387,20 +7386,20 @@
         <v>1</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>15.97</v>
+        <v>19.99</v>
       </c>
       <c r="I103" s="5" t="n">
         <f aca="false">IF(H103="","",G103*H103)</f>
-        <v>15.97</v>
+        <v>19.99</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="M103" s="2" t="s">
         <v>42</v>
@@ -7410,24 +7409,24 @@
       </c>
       <c r="O103" s="6" t="n">
         <f aca="false">IF(AND(J103="Amazon.ca",G103&gt;0,ISERROR(SEARCH("ALTERNATIVE",A103))),MAX(O$1:O102)+1,"")</f>
-        <v>77</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F104" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -7435,43 +7434,47 @@
       </c>
       <c r="G104" s="2" t="n">
         <f aca="false">IF(OR(F104=TRUE(),F104="TRUE"),0,E104)</f>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>6</v>
+        <v>15.99</v>
       </c>
       <c r="I104" s="5" t="n">
         <f aca="false">IF(H104="","",G104*H104)</f>
-        <v>60</v>
+        <v>15.99</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="K104" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="K104" s="7" t="s">
+        <v>513</v>
+      </c>
       <c r="L104" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="M104" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="N104" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="O104" s="6" t="str">
+        <v>43</v>
+      </c>
+      <c r="O104" s="6" t="n">
         <f aca="false">IF(AND(J104="Amazon.ca",G104&gt;0,ISERROR(SEARCH("ALTERNATIVE",A104))),MAX(O$1:O103)+1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>1</v>
@@ -7485,20 +7488,20 @@
         <v>1</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>24.99</v>
+        <v>15.97</v>
       </c>
       <c r="I105" s="5" t="n">
         <f aca="false">IF(H105="","",G105*H105)</f>
-        <v>24.99</v>
+        <v>15.97</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="L105" s="7" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="M105" s="2" t="s">
         <v>42</v>
@@ -7508,24 +7511,24 @@
       </c>
       <c r="O105" s="6" t="n">
         <f aca="false">IF(AND(J105="Amazon.ca",G105&gt;0,ISERROR(SEARCH("ALTERNATIVE",A105))),MAX(O$1:O104)+1,"")</f>
-        <v>78</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F106" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -7533,47 +7536,43 @@
       </c>
       <c r="G106" s="2" t="n">
         <f aca="false">IF(OR(F106=TRUE(),F106="TRUE"),0,E106)</f>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>54.54</v>
+        <v>6</v>
       </c>
       <c r="I106" s="5" t="n">
         <f aca="false">IF(H106="","",G106*H106)</f>
-        <v>54.54</v>
+        <v>60</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K106" s="7" t="s">
-        <v>527</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="K106" s="2"/>
       <c r="L106" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="M106" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="M106" s="2"/>
       <c r="N106" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O106" s="6" t="n">
+        <v>302</v>
+      </c>
+      <c r="O106" s="6" t="str">
         <f aca="false">IF(AND(J106="Amazon.ca",G106&gt;0,ISERROR(SEARCH("ALTERNATIVE",A106))),MAX(O$1:O105)+1,"")</f>
-        <v>79</v>
+        <v/>
       </c>
     </row>
     <row r="107" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>1</v>
@@ -7587,20 +7586,20 @@
         <v>1</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>43.69</v>
+        <v>24.99</v>
       </c>
       <c r="I107" s="5" t="n">
         <f aca="false">IF(H107="","",G107*H107)</f>
-        <v>43.69</v>
+        <v>24.99</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="L107" s="7" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="M107" s="2" t="s">
         <v>42</v>
@@ -7610,24 +7609,24 @@
       </c>
       <c r="O107" s="6" t="n">
         <f aca="false">IF(AND(J107="Amazon.ca",G107&gt;0,ISERROR(SEARCH("ALTERNATIVE",A107))),MAX(O$1:O106)+1,"")</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>534</v>
+        <v>498</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -7635,23 +7634,23 @@
       </c>
       <c r="G108" s="2" t="n">
         <f aca="false">IF(OR(F108=TRUE(),F108="TRUE"),0,E108)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>55.99</v>
+        <v>54.54</v>
       </c>
       <c r="I108" s="5" t="n">
         <f aca="false">IF(H108="","",G108*H108)</f>
-        <v>111.98</v>
+        <v>54.54</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="L108" s="7" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="M108" s="2" t="s">
         <v>42</v>
@@ -7659,14 +7658,116 @@
       <c r="N108" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="O108" s="6" t="str">
+      <c r="O108" s="6" t="n">
         <f aca="false">IF(AND(J108="Amazon.ca",G108&gt;0,ISERROR(SEARCH("ALTERNATIVE",A108))),MAX(O$1:O107)+1,"")</f>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="4" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <f aca="false">IF(OR(F109=TRUE(),F109="TRUE"),0,E109)</f>
+        <v>1</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>43.69</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <f aca="false">IF(H109="","",G109*H109)</f>
+        <v>43.69</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K109" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="L109" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N109" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O109" s="6" t="n">
+        <f aca="false">IF(AND(J109="Amazon.ca",G109&gt;0,ISERROR(SEARCH("ALTERNATIVE",A109))),MAX(O$1:O108)+1,"")</f>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" s="4" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <f aca="false">IF(OR(F110=TRUE(),F110="TRUE"),0,E110)</f>
+        <v>2</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <f aca="false">IF(H110="","",G110*H110)</f>
+        <v>111.98</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K110" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="L110" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N110" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O110" s="6" t="str">
+        <f aca="false">IF(AND(J110="Amazon.ca",G110&gt;0,ISERROR(SEARCH("ALTERNATIVE",A110))),MAX(O$1:O109)+1,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O108"/>
-  <conditionalFormatting sqref="A2:N108">
+  <autoFilter ref="A1:O110"/>
+  <conditionalFormatting sqref="A2:N110">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>OR($F2=TRUE(),$F2="TRUE")</formula>
     </cfRule>
@@ -7675,7 +7776,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" error="Choose TRUE or FALSE" errorStyle="stop" operator="between" prompt="TRUE = you already have it" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F108" type="list">
+    <dataValidation allowBlank="false" error="Choose TRUE or FALSE" errorStyle="stop" operator="between" prompt="TRUE = you already have it" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F110" type="list">
       <formula1>"TRUE,FALSE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7810,62 +7911,62 @@
     <hyperlink ref="L76" r:id="rId127" display="https://kent.ca/en/search?q=m8+x+60+bolt"/>
     <hyperlink ref="K77" r:id="rId128" display="https://www.amazon.ca/dp/B0FKMS7Y12"/>
     <hyperlink ref="L77" r:id="rId129" display="https://www.amazon.ca/s?k=12v+linear+actuator+10+inch+stroke+330+lbs"/>
-    <hyperlink ref="K78" r:id="rId130" display="https://www.amazon.ca/dp/B0CPHS87F8"/>
-    <hyperlink ref="L78" r:id="rId131" display="https://www.amazon.ca/s?k=12v+linear+actuator+12+inch+stroke+225+lbs"/>
-    <hyperlink ref="K79" r:id="rId132" display="https://www.amazon.ca/dp/B0D7ZRQNJ9"/>
-    <hyperlink ref="L79" r:id="rId133" display="https://www.amazon.ca/s?k=adjustable+gas+strut+600N+250mm"/>
-    <hyperlink ref="K80" r:id="rId134" display="https://www.amazon.ca/dp/B07SJ6B3QP"/>
-    <hyperlink ref="L80" r:id="rId135" display="https://www.amazon.ca/s?k=10mm+ball+stud+gas+strut+bracket"/>
-    <hyperlink ref="L81" r:id="rId136" display="https://kent.ca/en/search?q=heavy+steel+angle+bracket"/>
-    <hyperlink ref="L82" r:id="rId137" display="https://www.google.com/search?q=laser+cutting+steel+plate+Fredericton+NB"/>
-    <hyperlink ref="K83" r:id="rId138" display="https://www.amazon.ca/dp/B07GZHSCP6"/>
-    <hyperlink ref="L83" r:id="rId139" display="https://www.amazon.ca/s?k=spring+loaded+barrel+bolt+latch+heavy+duty"/>
-    <hyperlink ref="K84" r:id="rId140" display="https://www.amazon.ca/dp/B0B8C66T4Q"/>
-    <hyperlink ref="L84" r:id="rId141" display="https://www.amazon.ca/s?k=bicycle+brake+lever+cable+set"/>
-    <hyperlink ref="L85" r:id="rId142" display="https://kent.ca/en/search?q=1%2F2+inch+clevis+pin"/>
-    <hyperlink ref="K86" r:id="rId143" display="https://www.amazon.ca/dp/B0D1XSZ8SF"/>
-    <hyperlink ref="L86" r:id="rId144" display="https://www.amazon.ca/s?k=rubber+bumper+pads+with+screws"/>
-    <hyperlink ref="K87" r:id="rId145" display="https://www.amazon.ca/dp/B07RJMG3FB"/>
-    <hyperlink ref="L87" r:id="rId146" display="https://www.amazon.ca/s?k=12v+20a+power+supply+enclosed"/>
-    <hyperlink ref="K88" r:id="rId147" display="https://www.amazon.ca/dp/B0BHY1RQQR"/>
-    <hyperlink ref="L88" r:id="rId148" display="https://www.amazon.ca/s?k=12+awg+inline+atc+fuse+holder"/>
-    <hyperlink ref="K89" r:id="rId149" display="https://www.amazon.ca/dp/B09M849WCK"/>
-    <hyperlink ref="L89" r:id="rId150" display="https://www.amazon.ca/s?k=19mm+key+switch+2+position"/>
-    <hyperlink ref="K90" r:id="rId151" display="https://www.amazon.ca/dp/B019DSZWPC"/>
-    <hyperlink ref="L90" r:id="rId152" display="https://www.amazon.ca/s?k=22mm+emergency+stop+nc"/>
-    <hyperlink ref="K91" r:id="rId153" display="https://www.amazon.ca/dp/B0C22K75FZ"/>
-    <hyperlink ref="L91" r:id="rId154" display="https://www.amazon.ca/s?k=dpdt+momentary+toggle+on+off+on"/>
-    <hyperlink ref="K92" r:id="rId155" display="https://www.amazon.ca/dp/B0DNJVMMF9"/>
-    <hyperlink ref="L92" r:id="rId156" display="https://www.amazon.ca/s?k=12v+30a+relay+spdt+5+pin"/>
-    <hyperlink ref="K93" r:id="rId157" display="https://www.amazon.ca/dp/B0F8HJ4V9J"/>
-    <hyperlink ref="L93" r:id="rId158" display="https://www.amazon.ca/s?k=v-156-1c25+roller+lever+micro+switch+15a"/>
-    <hyperlink ref="K94" r:id="rId159" display="https://www.amazon.ca/dp/B079KF3VJG"/>
-    <hyperlink ref="L94" r:id="rId160" display="https://www.amazon.ca/s?k=6a10+diode"/>
-    <hyperlink ref="L95" r:id="rId161" display="https://www.amazon.ca/s?k=pressure+sensitive+safety+edge+NC"/>
-    <hyperlink ref="K96" r:id="rId162" display="https://www.amazon.ca/dp/B0CXY76JGX"/>
-    <hyperlink ref="L96" r:id="rId163" display="https://www.amazon.ca/s?k=14+awg+red+black+copper+wire+50+ft"/>
-    <hyperlink ref="K97" r:id="rId164" display="https://www.amazon.ca/dp/B0B569WMNP"/>
-    <hyperlink ref="L97" r:id="rId165" display="https://www.amazon.ca/s?k=heat+shrink+ring+terminal+kit"/>
-    <hyperlink ref="L98" r:id="rId166" display="https://www.amazon.ca/s?k=strip+brush+aluminum+holder+25mm"/>
-    <hyperlink ref="K99" r:id="rId167" display="https://www.amazon.ca/dp/B0DQXC46NQ"/>
-    <hyperlink ref="L99" r:id="rId168" display="https://www.amazon.ca/s?k=high+density+foam+1+inch+24+x+72"/>
-    <hyperlink ref="K100" r:id="rId169" display="https://www.amazon.ca/dp/B0B3J1GCVQ"/>
-    <hyperlink ref="L100" r:id="rId170" display="https://www.amazon.ca/s?k=1+inch+side+release+buckle+kit"/>
-    <hyperlink ref="K101" r:id="rId171" display="https://www.amazon.ca/dp/B0B7RHCFMV"/>
-    <hyperlink ref="L101" r:id="rId172" display="https://www.amazon.ca/s?k=1+inch+rated+webbing+4000+lb+polyester"/>
-    <hyperlink ref="K102" r:id="rId173" display="https://www.amazon.ca/dp/B0D781P6JB"/>
-    <hyperlink ref="L102" r:id="rId174" display="https://www.amazon.ca/s?k=welded+steel+o+ring+2+inch+heavy+duty"/>
-    <hyperlink ref="K103" r:id="rId175" display="https://www.amazon.ca/dp/B0CS9SL864"/>
-    <hyperlink ref="L103" r:id="rId176" display="https://www.amazon.ca/s?k=welded+steel+d+ring+1+inch"/>
-    <hyperlink ref="L104" r:id="rId177" display="https://kent.ca/en/search?q=forged+eye+bolt+3%2F8"/>
-    <hyperlink ref="K105" r:id="rId178" display="https://www.amazon.ca/dp/B0BFPZ5ZGW"/>
-    <hyperlink ref="L105" r:id="rId179" display="https://www.amazon.ca/s?k=2+point+lap+belt+adjustable"/>
-    <hyperlink ref="K106" r:id="rId180" display="https://www.amazon.ca/dp/B078SJ86G7"/>
-    <hyperlink ref="L106" r:id="rId181" display="https://www.amazon.ca/s?k=high+density+foam+2+inch+24+x+72"/>
-    <hyperlink ref="K107" r:id="rId182" display="https://www.amazon.ca/dp/B0744QFFS8"/>
-    <hyperlink ref="L107" r:id="rId183" display="https://www.amazon.ca/s?k=marine+vinyl+fabric+black"/>
-    <hyperlink ref="K108" r:id="rId184" display="https://www.amazon.ca/dp/B08TB7NLJB"/>
-    <hyperlink ref="L108" r:id="rId185" display="https://www.amazon.ca/s?k=4+point+harness+metal+buckle+2+inch"/>
+    <hyperlink ref="K78" r:id="rId130" display="https://www.amazon.ca/dp/B0FKMVCQPC"/>
+    <hyperlink ref="L78" r:id="rId131" display="https://www.amazon.ca/s?k=12v+linear+actuator+12+inch+stroke+330+lbs+1500N"/>
+    <hyperlink ref="L79" r:id="rId132" display="https://www.amazon.ca/s?k=gas+strut+1000N+250mm+M8+eyelet+pair"/>
+    <hyperlink ref="L80" r:id="rId133" display="https://kent.ca/en/search?q=heavy+steel+angle+bracket"/>
+    <hyperlink ref="L81" r:id="rId134" display="https://www.google.com/search?q=2x2x1%2F8+square+steel+tube+Fredericton+NB"/>
+    <hyperlink ref="L82" r:id="rId135" display="https://www.google.com/search?q=6mm+steel+plate+cut+to+size+welding+Fredericton+NB"/>
+    <hyperlink ref="L83" r:id="rId136" display="https://kent.ca/en/search?q=m10+x+70+bolt+grade+8.8"/>
+    <hyperlink ref="L84" r:id="rId137" display="https://www.google.com/search?q=laser+cutting+steel+plate+Fredericton+NB"/>
+    <hyperlink ref="K85" r:id="rId138" display="https://www.amazon.ca/dp/B07GZHSCP6"/>
+    <hyperlink ref="L85" r:id="rId139" display="https://www.amazon.ca/s?k=spring+loaded+barrel+bolt+latch+heavy+duty"/>
+    <hyperlink ref="K86" r:id="rId140" display="https://www.amazon.ca/dp/B0B8C66T4Q"/>
+    <hyperlink ref="L86" r:id="rId141" display="https://www.amazon.ca/s?k=bicycle+brake+lever+cable+set"/>
+    <hyperlink ref="L87" r:id="rId142" display="https://kent.ca/en/search?q=1%2F2+inch+clevis+pin"/>
+    <hyperlink ref="K88" r:id="rId143" display="https://www.amazon.ca/dp/B0D1XSZ8SF"/>
+    <hyperlink ref="L88" r:id="rId144" display="https://www.amazon.ca/s?k=rubber+bumper+pads+with+screws"/>
+    <hyperlink ref="K89" r:id="rId145" display="https://www.amazon.ca/dp/B07RJMG3FB"/>
+    <hyperlink ref="L89" r:id="rId146" display="https://www.amazon.ca/s?k=12v+20a+power+supply+enclosed"/>
+    <hyperlink ref="K90" r:id="rId147" display="https://www.amazon.ca/dp/B0BHY1RQQR"/>
+    <hyperlink ref="L90" r:id="rId148" display="https://www.amazon.ca/s?k=12+awg+inline+atc+fuse+holder"/>
+    <hyperlink ref="K91" r:id="rId149" display="https://www.amazon.ca/dp/B09M849WCK"/>
+    <hyperlink ref="L91" r:id="rId150" display="https://www.amazon.ca/s?k=19mm+key+switch+2+position"/>
+    <hyperlink ref="K92" r:id="rId151" display="https://www.amazon.ca/dp/B019DSZWPC"/>
+    <hyperlink ref="L92" r:id="rId152" display="https://www.amazon.ca/s?k=22mm+emergency+stop+nc"/>
+    <hyperlink ref="K93" r:id="rId153" display="https://www.amazon.ca/dp/B0C22K75FZ"/>
+    <hyperlink ref="L93" r:id="rId154" display="https://www.amazon.ca/s?k=dpdt+momentary+toggle+on+off+on"/>
+    <hyperlink ref="K94" r:id="rId155" display="https://www.amazon.ca/dp/B0DNJVMMF9"/>
+    <hyperlink ref="L94" r:id="rId156" display="https://www.amazon.ca/s?k=12v+30a+relay+spdt+5+pin"/>
+    <hyperlink ref="K95" r:id="rId157" display="https://www.amazon.ca/dp/B0F8HJ4V9J"/>
+    <hyperlink ref="L95" r:id="rId158" display="https://www.amazon.ca/s?k=v-156-1c25+roller+lever+micro+switch+15a"/>
+    <hyperlink ref="K96" r:id="rId159" display="https://www.amazon.ca/dp/B079KF3VJG"/>
+    <hyperlink ref="L96" r:id="rId160" display="https://www.amazon.ca/s?k=6a10+diode"/>
+    <hyperlink ref="L97" r:id="rId161" display="https://www.amazon.ca/s?k=pressure+sensitive+safety+edge+NC"/>
+    <hyperlink ref="K98" r:id="rId162" display="https://www.amazon.ca/dp/B0CXY76JGX"/>
+    <hyperlink ref="L98" r:id="rId163" display="https://www.amazon.ca/s?k=14+awg+red+black+copper+wire+50+ft"/>
+    <hyperlink ref="K99" r:id="rId164" display="https://www.amazon.ca/dp/B0B569WMNP"/>
+    <hyperlink ref="L99" r:id="rId165" display="https://www.amazon.ca/s?k=heat+shrink+ring+terminal+kit"/>
+    <hyperlink ref="L100" r:id="rId166" display="https://www.amazon.ca/s?k=strip+brush+aluminum+holder+25mm"/>
+    <hyperlink ref="K101" r:id="rId167" display="https://www.amazon.ca/dp/B0DQXC46NQ"/>
+    <hyperlink ref="L101" r:id="rId168" display="https://www.amazon.ca/s?k=high+density+foam+1+inch+24+x+72"/>
+    <hyperlink ref="K102" r:id="rId169" display="https://www.amazon.ca/dp/B0B3J1GCVQ"/>
+    <hyperlink ref="L102" r:id="rId170" display="https://www.amazon.ca/s?k=1+inch+side+release+buckle+kit"/>
+    <hyperlink ref="K103" r:id="rId171" display="https://www.amazon.ca/dp/B0B7RHCFMV"/>
+    <hyperlink ref="L103" r:id="rId172" display="https://www.amazon.ca/s?k=1+inch+rated+webbing+4000+lb+polyester"/>
+    <hyperlink ref="K104" r:id="rId173" display="https://www.amazon.ca/dp/B0D781P6JB"/>
+    <hyperlink ref="L104" r:id="rId174" display="https://www.amazon.ca/s?k=welded+steel+o+ring+2+inch+heavy+duty"/>
+    <hyperlink ref="K105" r:id="rId175" display="https://www.amazon.ca/dp/B0CS9SL864"/>
+    <hyperlink ref="L105" r:id="rId176" display="https://www.amazon.ca/s?k=welded+steel+d+ring+1+inch"/>
+    <hyperlink ref="L106" r:id="rId177" display="https://kent.ca/en/search?q=forged+eye+bolt+3%2F8"/>
+    <hyperlink ref="K107" r:id="rId178" display="https://www.amazon.ca/dp/B0BFPZ5ZGW"/>
+    <hyperlink ref="L107" r:id="rId179" display="https://www.amazon.ca/s?k=2+point+lap+belt+adjustable"/>
+    <hyperlink ref="K108" r:id="rId180" display="https://www.amazon.ca/dp/B078SJ86G7"/>
+    <hyperlink ref="L108" r:id="rId181" display="https://www.amazon.ca/s?k=high+density+foam+2+inch+24+x+72"/>
+    <hyperlink ref="K109" r:id="rId182" display="https://www.amazon.ca/dp/B0744QFFS8"/>
+    <hyperlink ref="L109" r:id="rId183" display="https://www.amazon.ca/s?k=marine+vinyl+fabric+black"/>
+    <hyperlink ref="K110" r:id="rId184" display="https://www.amazon.ca/dp/B08TB7NLJB"/>
+    <hyperlink ref="L110" r:id="rId185" display="https://www.amazon.ca/s?k=4+point+harness+metal+buckle+2+inch"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7896,13 +7997,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7910,15 +8011,15 @@
         <v>15</v>
       </c>
       <c r="B2" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A2)</f>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A2)</f>
         <v>6</v>
       </c>
       <c r="C2" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A2,BOM!$G$2:$G$108,"&gt;0")</f>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A2,BOM!$G$2:$G$110,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="D2" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A2,BOM!$I$2:$I$108)</f>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A2,BOM!$I$2:$I$110)</f>
         <v>0</v>
       </c>
     </row>
@@ -7927,15 +8028,15 @@
         <v>35</v>
       </c>
       <c r="B3" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A3)</f>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A3)</f>
         <v>7</v>
       </c>
       <c r="C3" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A3,BOM!$G$2:$G$108,"&gt;0")</f>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A3,BOM!$G$2:$G$110,"&gt;0")</f>
         <v>7</v>
       </c>
       <c r="D3" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A3,BOM!$I$2:$I$108)</f>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A3,BOM!$I$2:$I$110)</f>
         <v>123.69</v>
       </c>
     </row>
@@ -7944,15 +8045,15 @@
         <v>74</v>
       </c>
       <c r="B4" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A4)</f>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A4)</f>
         <v>16</v>
       </c>
       <c r="C4" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A4,BOM!$G$2:$G$108,"&gt;0")</f>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A4,BOM!$G$2:$G$110,"&gt;0")</f>
         <v>16</v>
       </c>
       <c r="D4" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A4,BOM!$I$2:$I$108)</f>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A4,BOM!$I$2:$I$110)</f>
         <v>295.28</v>
       </c>
     </row>
@@ -7961,15 +8062,15 @@
         <v>154</v>
       </c>
       <c r="B5" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A5)</f>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A5)</f>
         <v>9</v>
       </c>
       <c r="C5" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A5,BOM!$G$2:$G$108,"&gt;0")</f>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A5,BOM!$G$2:$G$110,"&gt;0")</f>
         <v>9</v>
       </c>
       <c r="D5" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A5,BOM!$I$2:$I$108)</f>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A5,BOM!$I$2:$I$110)</f>
         <v>198.92</v>
       </c>
     </row>
@@ -7978,15 +8079,15 @@
         <v>200</v>
       </c>
       <c r="B6" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A6)</f>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A6)</f>
         <v>8</v>
       </c>
       <c r="C6" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A6,BOM!$G$2:$G$108,"&gt;0")</f>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A6,BOM!$G$2:$G$110,"&gt;0")</f>
         <v>8</v>
       </c>
       <c r="D6" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A6,BOM!$I$2:$I$108)</f>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A6,BOM!$I$2:$I$110)</f>
         <v>177.14</v>
       </c>
     </row>
@@ -7995,15 +8096,15 @@
         <v>241</v>
       </c>
       <c r="B7" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A7)</f>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A7)</f>
         <v>5</v>
       </c>
       <c r="C7" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A7,BOM!$G$2:$G$108,"&gt;0")</f>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A7,BOM!$G$2:$G$110,"&gt;0")</f>
         <v>5</v>
       </c>
       <c r="D7" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A7,BOM!$I$2:$I$108)</f>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A7,BOM!$I$2:$I$110)</f>
         <v>213.5</v>
       </c>
     </row>
@@ -8012,15 +8113,15 @@
         <v>267</v>
       </c>
       <c r="B8" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A8)</f>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A8)</f>
         <v>5</v>
       </c>
       <c r="C8" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A8,BOM!$G$2:$G$108,"&gt;0")</f>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A8,BOM!$G$2:$G$110,"&gt;0")</f>
         <v>5</v>
       </c>
       <c r="D8" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A8,BOM!$I$2:$I$108)</f>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A8,BOM!$I$2:$I$110)</f>
         <v>676.07</v>
       </c>
     </row>
@@ -8029,15 +8130,15 @@
         <v>296</v>
       </c>
       <c r="B9" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A9)</f>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A9)</f>
         <v>10</v>
       </c>
       <c r="C9" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A9,BOM!$G$2:$G$108,"&gt;0")</f>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A9,BOM!$G$2:$G$110,"&gt;0")</f>
         <v>10</v>
       </c>
       <c r="D9" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A9,BOM!$I$2:$I$108)</f>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A9,BOM!$I$2:$I$110)</f>
         <v>207.32</v>
       </c>
     </row>
@@ -8046,15 +8147,15 @@
         <v>341</v>
       </c>
       <c r="B10" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A10)</f>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A10)</f>
         <v>9</v>
       </c>
       <c r="C10" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A10,BOM!$G$2:$G$108,"&gt;0")</f>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A10,BOM!$G$2:$G$110,"&gt;0")</f>
         <v>9</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A10,BOM!$I$2:$I$108)</f>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A10,BOM!$I$2:$I$110)</f>
         <v>295.28</v>
       </c>
     </row>
@@ -8063,161 +8164,161 @@
         <v>382</v>
       </c>
       <c r="B11" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A11)</f>
-        <v>10</v>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A11)</f>
+        <v>12</v>
       </c>
       <c r="C11" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A11,BOM!$G$2:$G$108,"&gt;0")</f>
-        <v>10</v>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A11,BOM!$G$2:$G$110,"&gt;0")</f>
+        <v>12</v>
       </c>
       <c r="D11" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A11,BOM!$I$2:$I$108)</f>
-        <v>447.68</v>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A11,BOM!$I$2:$I$110)</f>
+        <v>519.44</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B12" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A12)</f>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A12)</f>
         <v>11</v>
       </c>
       <c r="C12" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A12,BOM!$G$2:$G$108,"&gt;0")</f>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A12,BOM!$G$2:$G$110,"&gt;0")</f>
         <v>11</v>
       </c>
       <c r="D12" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A12,BOM!$I$2:$I$108)</f>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A12,BOM!$I$2:$I$110)</f>
         <v>388.84</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B13" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A13)</f>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A13)</f>
         <v>2</v>
       </c>
       <c r="C13" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A13,BOM!$G$2:$G$108,"&gt;0")</f>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A13,BOM!$G$2:$G$110,"&gt;0")</f>
         <v>2</v>
       </c>
       <c r="D13" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A13,BOM!$I$2:$I$108)</f>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A13,BOM!$I$2:$I$110)</f>
         <v>92.15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B14" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A14)</f>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A14)</f>
         <v>8</v>
       </c>
       <c r="C14" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A14,BOM!$G$2:$G$108,"&gt;0")</f>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A14,BOM!$G$2:$G$110,"&gt;0")</f>
         <v>8</v>
       </c>
       <c r="D14" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A14,BOM!$I$2:$I$108)</f>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A14,BOM!$I$2:$I$110)</f>
         <v>248.17</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B15" s="0" t="n">
-        <f aca="false">COUNTIF(BOM!$A$2:$A$108,A15)</f>
+        <f aca="false">COUNTIF(BOM!$A$2:$A$110,A15)</f>
         <v>1</v>
       </c>
       <c r="C15" s="0" t="n">
-        <f aca="false">COUNTIFS(BOM!$A$2:$A$108,A15,BOM!$G$2:$G$108,"&gt;0")</f>
+        <f aca="false">COUNTIFS(BOM!$A$2:$A$110,A15,BOM!$G$2:$G$110,"&gt;0")</f>
         <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
-        <f aca="false">SUMIF(BOM!$A$2:$A$108,A15,BOM!$I$2:$I$108)</f>
+        <f aca="false">SUMIF(BOM!$A$2:$A$110,A15,BOM!$I$2:$I$110)</f>
         <v>111.98</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C17" s="0" t="n">
         <f aca="false">SUMPRODUCT((ISERROR(SEARCH("ALTERNATIVE",A2:A15)))*C2:C15)</f>
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D17" s="11" t="n">
         <f aca="false">SUMPRODUCT((ISERROR(SEARCH("ALTERNATIVE",A2:A15)))*D2:D15)</f>
-        <v>3364.04</v>
+        <v>3435.8</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="D18" s="9" t="n">
-        <f aca="false">SUMPRODUCT((BOM!$J$2:$J$108="Amazon.ca")*ISERROR(SEARCH("ALTERNATIVE",BOM!$A$2:$A$108))*N(+BOM!$I$2:$I$108))</f>
-        <v>2189.97</v>
+        <f aca="false">SUMPRODUCT((BOM!$J$2:$J$110="Amazon.ca")*ISERROR(SEARCH("ALTERNATIVE",BOM!$A$2:$A$110))*N(+BOM!$I$2:$I$110))</f>
+        <v>2168.73</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="D19" s="9" t="n">
-        <f aca="false">SUMPRODUCT(ISNUMBER(SEARCH("Kent",BOM!$J$2:$J$108))*N(+BOM!$I$2:$I$108))</f>
-        <v>904.07</v>
+        <f aca="false">SUMPRODUCT(ISNUMBER(SEARCH("Kent",BOM!$J$2:$J$110))*N(+BOM!$I$2:$I$110))</f>
+        <v>912.07</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D20" s="9" t="n">
-        <f aca="false">SUMPRODUCT((ISNUMBER(SEARCH("supplier",BOM!$J$2:$J$108)))*N(+BOM!$I$2:$I$108))</f>
-        <v>270</v>
+        <f aca="false">SUMPRODUCT((ISNUMBER(SEARCH("supplier",BOM!$J$2:$J$110)))*N(+BOM!$I$2:$I$110))</f>
+        <v>355</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="D21" s="9" t="n">
-        <f aca="false">SUMPRODUCT((ISNUMBER(SEARCH("Verified amazon.ca price",BOM!$N$2:$N$108))+ISNUMBER(SEARCH("Kent.ca web price",BOM!$N$2:$N$108))&gt;0)*ISERROR(SEARCH("ALTERNATIVE",BOM!$A$2:$A$108))*N(+BOM!$I$2:$I$108))</f>
-        <v>2773.04</v>
+        <f aca="false">SUMPRODUCT((ISNUMBER(SEARCH("Verified amazon.ca price",BOM!$N$2:$N$110))+ISNUMBER(SEARCH("Kent.ca web price",BOM!$N$2:$N$110))&gt;0)*ISERROR(SEARCH("ALTERNATIVE",BOM!$A$2:$A$110))*N(+BOM!$I$2:$I$110))</f>
+        <v>2691.8</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D22" s="9" t="n">
-        <f aca="false">SUMPRODUCT((ISNUMBER(SEARCH("estimate",BOM!$N$2:$N$108)))*ISERROR(SEARCH("ALTERNATIVE",BOM!$A$2:$A$108))*N(+BOM!$I$2:$I$108))</f>
-        <v>591</v>
+        <f aca="false">SUMPRODUCT((ISNUMBER(SEARCH("estimate",BOM!$N$2:$N$110)))*ISERROR(SEARCH("ALTERNATIVE",BOM!$A$2:$A$110))*N(+BOM!$I$2:$I$110))</f>
+        <v>744</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="D23" s="9" t="n">
-        <f aca="false">SUMPRODUCT(ISNUMBER(SEARCH("ALTERNATIVE",BOM!$A$2:$A$108))*N(+BOM!$I$2:$I$108))</f>
+        <f aca="false">SUMPRODUCT(ISNUMBER(SEARCH("ALTERNATIVE",BOM!$A$2:$A$110))*N(+BOM!$I$2:$I$110))</f>
         <v>111.98</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
   </sheetData>
@@ -8249,7 +8350,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>1</v>
@@ -8270,3616 +8371,3616 @@
         <v>11</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(1,BOM!$O$2:$O$108,0)),"",1)</f>
+        <f aca="false">IF(ISNA(MATCH(1,BOM!$O$2:$O$110,0)),"",1)</f>
         <v>1</v>
       </c>
       <c r="B2" s="0" t="str">
-        <f aca="false">IF($A2="","",INDEX(BOM!$B$2:$B$108,MATCH(1,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A2="","",INDEX(BOM!$B$2:$B$110,MATCH(1,BOM!$O$2:$O$110,0)))</f>
         <v>DisplayPort 1.4 cable, 3 m (10 ft), VESA certified</v>
       </c>
       <c r="C2" s="0" t="n">
-        <f aca="false">IF($A2="","",INDEX(BOM!$G$2:$G$108,MATCH(1,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A2="","",INDEX(BOM!$G$2:$G$110,MATCH(1,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D2" s="9" t="n">
-        <f aca="false">IF($A2="","",INDEX(BOM!$H$2:$H$108,MATCH(1,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A2="","",INDEX(BOM!$H$2:$H$110,MATCH(1,BOM!$O$2:$O$110,0)))</f>
         <v>16.99</v>
       </c>
       <c r="E2" s="9" t="n">
-        <f aca="false">IF($A2="","",INDEX(BOM!$I$2:$I$108,MATCH(1,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A2="","",INDEX(BOM!$I$2:$I$110,MATCH(1,BOM!$O$2:$O$110,0)))</f>
         <v>16.99</v>
       </c>
       <c r="F2" s="0" t="str">
-        <f aca="false">IF($A2="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(1,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(1,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A2="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(1,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(1,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G2" s="0" t="str">
-        <f aca="false">IF($A2="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(1,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A2="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(1,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(2,BOM!$O$2:$O$108,0)),"",2)</f>
+        <f aca="false">IF(ISNA(MATCH(2,BOM!$O$2:$O$110,0)),"",2)</f>
         <v>2</v>
       </c>
       <c r="B3" s="0" t="str">
-        <f aca="false">IF($A3="","",INDEX(BOM!$B$2:$B$108,MATCH(2,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A3="","",INDEX(BOM!$B$2:$B$110,MATCH(2,BOM!$O$2:$O$110,0)))</f>
         <v>HDMI cable, 3 m (10 ft)</v>
       </c>
       <c r="C3" s="0" t="n">
-        <f aca="false">IF($A3="","",INDEX(BOM!$G$2:$G$108,MATCH(2,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A3="","",INDEX(BOM!$G$2:$G$110,MATCH(2,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D3" s="9" t="n">
-        <f aca="false">IF($A3="","",INDEX(BOM!$H$2:$H$108,MATCH(2,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A3="","",INDEX(BOM!$H$2:$H$110,MATCH(2,BOM!$O$2:$O$110,0)))</f>
         <v>10.76</v>
       </c>
       <c r="E3" s="9" t="n">
-        <f aca="false">IF($A3="","",INDEX(BOM!$I$2:$I$108,MATCH(2,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A3="","",INDEX(BOM!$I$2:$I$110,MATCH(2,BOM!$O$2:$O$110,0)))</f>
         <v>10.76</v>
       </c>
       <c r="F3" s="0" t="str">
-        <f aca="false">IF($A3="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(2,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(2,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A3="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(2,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(2,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G3" s="0" t="str">
-        <f aca="false">IF($A3="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(2,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A3="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(2,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(3,BOM!$O$2:$O$108,0)),"",3)</f>
+        <f aca="false">IF(ISNA(MATCH(3,BOM!$O$2:$O$110,0)),"",3)</f>
         <v>3</v>
       </c>
       <c r="B4" s="0" t="str">
-        <f aca="false">IF($A4="","",INDEX(BOM!$B$2:$B$108,MATCH(3,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A4="","",INDEX(BOM!$B$2:$B$110,MATCH(3,BOM!$O$2:$O$110,0)))</f>
         <v>DisplayPort -&gt; DVI-D adapter cable, passive, 3 m (10 ft)</v>
       </c>
       <c r="C4" s="0" t="n">
-        <f aca="false">IF($A4="","",INDEX(BOM!$G$2:$G$108,MATCH(3,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A4="","",INDEX(BOM!$G$2:$G$110,MATCH(3,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D4" s="9" t="n">
-        <f aca="false">IF($A4="","",INDEX(BOM!$H$2:$H$108,MATCH(3,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A4="","",INDEX(BOM!$H$2:$H$110,MATCH(3,BOM!$O$2:$O$110,0)))</f>
         <v>16.99</v>
       </c>
       <c r="E4" s="9" t="n">
-        <f aca="false">IF($A4="","",INDEX(BOM!$I$2:$I$108,MATCH(3,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A4="","",INDEX(BOM!$I$2:$I$110,MATCH(3,BOM!$O$2:$O$110,0)))</f>
         <v>16.99</v>
       </c>
       <c r="F4" s="0" t="str">
-        <f aca="false">IF($A4="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(3,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(3,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A4="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(3,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(3,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G4" s="0" t="str">
-        <f aca="false">IF($A4="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(3,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A4="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(3,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(4,BOM!$O$2:$O$108,0)),"",4)</f>
+        <f aca="false">IF(ISNA(MATCH(4,BOM!$O$2:$O$110,0)),"",4)</f>
         <v>4</v>
       </c>
       <c r="B5" s="0" t="str">
-        <f aca="false">IF($A5="","",INDEX(BOM!$B$2:$B$108,MATCH(4,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A5="","",INDEX(BOM!$B$2:$B$110,MATCH(4,BOM!$O$2:$O$110,0)))</f>
         <v>USB-A to USB-B cable, 3 m (10 ft)</v>
       </c>
       <c r="C5" s="0" t="n">
-        <f aca="false">IF($A5="","",INDEX(BOM!$G$2:$G$108,MATCH(4,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A5="","",INDEX(BOM!$G$2:$G$110,MATCH(4,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D5" s="9" t="n">
-        <f aca="false">IF($A5="","",INDEX(BOM!$H$2:$H$108,MATCH(4,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A5="","",INDEX(BOM!$H$2:$H$110,MATCH(4,BOM!$O$2:$O$110,0)))</f>
         <v>12.99</v>
       </c>
       <c r="E5" s="9" t="n">
-        <f aca="false">IF($A5="","",INDEX(BOM!$I$2:$I$108,MATCH(4,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A5="","",INDEX(BOM!$I$2:$I$110,MATCH(4,BOM!$O$2:$O$110,0)))</f>
         <v>12.99</v>
       </c>
       <c r="F5" s="0" t="str">
-        <f aca="false">IF($A5="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(4,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(4,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A5="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(4,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(4,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G5" s="0" t="str">
-        <f aca="false">IF($A5="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(4,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A5="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(4,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(5,BOM!$O$2:$O$108,0)),"",5)</f>
+        <f aca="false">IF(ISNA(MATCH(5,BOM!$O$2:$O$110,0)),"",5)</f>
         <v>5</v>
       </c>
       <c r="B6" s="0" t="str">
-        <f aca="false">IF($A6="","",INDEX(BOM!$B$2:$B$108,MATCH(5,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A6="","",INDEX(BOM!$B$2:$B$110,MATCH(5,BOM!$O$2:$O$110,0)))</f>
         <v>USB-A to USB-C data cables 1.8 m (6 ft), 3-pack</v>
       </c>
       <c r="C6" s="0" t="n">
-        <f aca="false">IF($A6="","",INDEX(BOM!$G$2:$G$108,MATCH(5,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A6="","",INDEX(BOM!$G$2:$G$110,MATCH(5,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D6" s="9" t="n">
-        <f aca="false">IF($A6="","",INDEX(BOM!$H$2:$H$108,MATCH(5,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A6="","",INDEX(BOM!$H$2:$H$110,MATCH(5,BOM!$O$2:$O$110,0)))</f>
         <v>9.99</v>
       </c>
       <c r="E6" s="9" t="n">
-        <f aca="false">IF($A6="","",INDEX(BOM!$I$2:$I$108,MATCH(5,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A6="","",INDEX(BOM!$I$2:$I$110,MATCH(5,BOM!$O$2:$O$110,0)))</f>
         <v>9.99</v>
       </c>
       <c r="F6" s="0" t="str">
-        <f aca="false">IF($A6="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(5,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(5,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A6="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(5,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(5,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G6" s="0" t="str">
-        <f aca="false">IF($A6="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(5,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A6="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(5,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(6,BOM!$O$2:$O$108,0)),"",6)</f>
+        <f aca="false">IF(ISNA(MATCH(6,BOM!$O$2:$O$110,0)),"",6)</f>
         <v>6</v>
       </c>
       <c r="B7" s="0" t="str">
-        <f aca="false">IF($A7="","",INDEX(BOM!$B$2:$B$108,MATCH(6,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A7="","",INDEX(BOM!$B$2:$B$110,MATCH(6,BOM!$O$2:$O$110,0)))</f>
         <v>Powered USB 3.0 hub, 7-port, with power adapter</v>
       </c>
       <c r="C7" s="0" t="n">
-        <f aca="false">IF($A7="","",INDEX(BOM!$G$2:$G$108,MATCH(6,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A7="","",INDEX(BOM!$G$2:$G$110,MATCH(6,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D7" s="9" t="n">
-        <f aca="false">IF($A7="","",INDEX(BOM!$H$2:$H$108,MATCH(6,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A7="","",INDEX(BOM!$H$2:$H$110,MATCH(6,BOM!$O$2:$O$110,0)))</f>
         <v>39.99</v>
       </c>
       <c r="E7" s="9" t="n">
-        <f aca="false">IF($A7="","",INDEX(BOM!$I$2:$I$108,MATCH(6,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A7="","",INDEX(BOM!$I$2:$I$110,MATCH(6,BOM!$O$2:$O$110,0)))</f>
         <v>39.99</v>
       </c>
       <c r="F7" s="0" t="str">
-        <f aca="false">IF($A7="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(6,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(6,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A7="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(6,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(6,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G7" s="0" t="str">
-        <f aca="false">IF($A7="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(6,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A7="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(6,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(7,BOM!$O$2:$O$108,0)),"",7)</f>
+        <f aca="false">IF(ISNA(MATCH(7,BOM!$O$2:$O$110,0)),"",7)</f>
         <v>7</v>
       </c>
       <c r="B8" s="0" t="str">
-        <f aca="false">IF($A8="","",INDEX(BOM!$B$2:$B$108,MATCH(7,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A8="","",INDEX(BOM!$B$2:$B$110,MATCH(7,BOM!$O$2:$O$110,0)))</f>
         <v>Expandable braided sleeve 25 mm (1"), 7.6 m (25 ft)</v>
       </c>
       <c r="C8" s="0" t="n">
-        <f aca="false">IF($A8="","",INDEX(BOM!$G$2:$G$108,MATCH(7,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A8="","",INDEX(BOM!$G$2:$G$110,MATCH(7,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D8" s="9" t="n">
-        <f aca="false">IF($A8="","",INDEX(BOM!$H$2:$H$108,MATCH(7,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A8="","",INDEX(BOM!$H$2:$H$110,MATCH(7,BOM!$O$2:$O$110,0)))</f>
         <v>15.98</v>
       </c>
       <c r="E8" s="9" t="n">
-        <f aca="false">IF($A8="","",INDEX(BOM!$I$2:$I$108,MATCH(7,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A8="","",INDEX(BOM!$I$2:$I$110,MATCH(7,BOM!$O$2:$O$110,0)))</f>
         <v>15.98</v>
       </c>
       <c r="F8" s="0" t="str">
-        <f aca="false">IF($A8="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(7,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(7,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A8="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(7,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(7,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G8" s="0" t="str">
-        <f aca="false">IF($A8="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(7,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A8="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(7,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(8,BOM!$O$2:$O$108,0)),"",8)</f>
+        <f aca="false">IF(ISNA(MATCH(8,BOM!$O$2:$O$110,0)),"",8)</f>
         <v>8</v>
       </c>
       <c r="B9" s="0" t="str">
-        <f aca="false">IF($A9="","",INDEX(BOM!$B$2:$B$108,MATCH(8,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A9="","",INDEX(BOM!$B$2:$B$110,MATCH(8,BOM!$O$2:$O$110,0)))</f>
         <v>ESP32-S3-DevKitC-1-N8R8, 5-pack</v>
       </c>
       <c r="C9" s="0" t="n">
-        <f aca="false">IF($A9="","",INDEX(BOM!$G$2:$G$108,MATCH(8,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A9="","",INDEX(BOM!$G$2:$G$110,MATCH(8,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D9" s="9" t="n">
-        <f aca="false">IF($A9="","",INDEX(BOM!$H$2:$H$108,MATCH(8,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A9="","",INDEX(BOM!$H$2:$H$110,MATCH(8,BOM!$O$2:$O$110,0)))</f>
         <v>71.98</v>
       </c>
       <c r="E9" s="9" t="n">
-        <f aca="false">IF($A9="","",INDEX(BOM!$I$2:$I$108,MATCH(8,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A9="","",INDEX(BOM!$I$2:$I$110,MATCH(8,BOM!$O$2:$O$110,0)))</f>
         <v>71.98</v>
       </c>
       <c r="F9" s="0" t="str">
-        <f aca="false">IF($A9="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(8,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(8,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A9="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(8,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(8,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G9" s="0" t="str">
-        <f aca="false">IF($A9="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(8,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A9="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(8,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(9,BOM!$O$2:$O$108,0)),"",9)</f>
+        <f aca="false">IF(ISNA(MATCH(9,BOM!$O$2:$O$110,0)),"",9)</f>
         <v>9</v>
       </c>
       <c r="B10" s="0" t="str">
-        <f aca="false">IF($A10="","",INDEX(BOM!$B$2:$B$108,MATCH(9,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A10="","",INDEX(BOM!$B$2:$B$110,MATCH(9,BOM!$O$2:$O$110,0)))</f>
         <v>74HC165 shift register DIP-16, 25 pcs</v>
       </c>
       <c r="C10" s="0" t="n">
-        <f aca="false">IF($A10="","",INDEX(BOM!$G$2:$G$108,MATCH(9,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A10="","",INDEX(BOM!$G$2:$G$110,MATCH(9,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">IF($A10="","",INDEX(BOM!$H$2:$H$108,MATCH(9,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A10="","",INDEX(BOM!$H$2:$H$110,MATCH(9,BOM!$O$2:$O$110,0)))</f>
         <v>18.49</v>
       </c>
       <c r="E10" s="9" t="n">
-        <f aca="false">IF($A10="","",INDEX(BOM!$I$2:$I$108,MATCH(9,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A10="","",INDEX(BOM!$I$2:$I$110,MATCH(9,BOM!$O$2:$O$110,0)))</f>
         <v>18.49</v>
       </c>
       <c r="F10" s="0" t="str">
-        <f aca="false">IF($A10="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(9,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(9,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A10="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(9,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(9,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G10" s="0" t="str">
-        <f aca="false">IF($A10="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(9,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A10="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(9,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(10,BOM!$O$2:$O$108,0)),"",10)</f>
+        <f aca="false">IF(ISNA(MATCH(10,BOM!$O$2:$O$110,0)),"",10)</f>
         <v>10</v>
       </c>
       <c r="B11" s="0" t="str">
-        <f aca="false">IF($A11="","",INDEX(BOM!$B$2:$B$108,MATCH(10,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A11="","",INDEX(BOM!$B$2:$B$110,MATCH(10,BOM!$O$2:$O$110,0)))</f>
         <v>DIP IC socket assortment (incl. 14- and 16-pin)</v>
       </c>
       <c r="C11" s="0" t="n">
-        <f aca="false">IF($A11="","",INDEX(BOM!$G$2:$G$108,MATCH(10,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A11="","",INDEX(BOM!$G$2:$G$110,MATCH(10,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D11" s="9" t="n">
-        <f aca="false">IF($A11="","",INDEX(BOM!$H$2:$H$108,MATCH(10,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A11="","",INDEX(BOM!$H$2:$H$110,MATCH(10,BOM!$O$2:$O$110,0)))</f>
         <v>16.99</v>
       </c>
       <c r="E11" s="9" t="n">
-        <f aca="false">IF($A11="","",INDEX(BOM!$I$2:$I$108,MATCH(10,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A11="","",INDEX(BOM!$I$2:$I$110,MATCH(10,BOM!$O$2:$O$110,0)))</f>
         <v>16.99</v>
       </c>
       <c r="F11" s="0" t="str">
-        <f aca="false">IF($A11="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(10,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(10,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A11="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(10,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(10,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G11" s="0" t="str">
-        <f aca="false">IF($A11="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(10,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A11="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(10,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(11,BOM!$O$2:$O$108,0)),"",11)</f>
+        <f aca="false">IF(ISNA(MATCH(11,BOM!$O$2:$O$110,0)),"",11)</f>
         <v>11</v>
       </c>
       <c r="B12" s="0" t="str">
-        <f aca="false">IF($A12="","",INDEX(BOM!$B$2:$B$108,MATCH(11,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A12="","",INDEX(BOM!$B$2:$B$110,MATCH(11,BOM!$O$2:$O$110,0)))</f>
         <v>10 kOhm bussed resistor network SIP-9 (A103J), 20 pcs</v>
       </c>
       <c r="C12" s="0" t="n">
-        <f aca="false">IF($A12="","",INDEX(BOM!$G$2:$G$108,MATCH(11,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A12="","",INDEX(BOM!$G$2:$G$110,MATCH(11,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D12" s="9" t="n">
-        <f aca="false">IF($A12="","",INDEX(BOM!$H$2:$H$108,MATCH(11,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A12="","",INDEX(BOM!$H$2:$H$110,MATCH(11,BOM!$O$2:$O$110,0)))</f>
         <v>8.88</v>
       </c>
       <c r="E12" s="9" t="n">
-        <f aca="false">IF($A12="","",INDEX(BOM!$I$2:$I$108,MATCH(11,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A12="","",INDEX(BOM!$I$2:$I$110,MATCH(11,BOM!$O$2:$O$110,0)))</f>
         <v>8.88</v>
       </c>
       <c r="F12" s="0" t="str">
-        <f aca="false">IF($A12="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(11,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(11,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A12="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(11,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(11,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G12" s="0" t="str">
-        <f aca="false">IF($A12="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(11,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A12="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(11,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(12,BOM!$O$2:$O$108,0)),"",12)</f>
+        <f aca="false">IF(ISNA(MATCH(12,BOM!$O$2:$O$110,0)),"",12)</f>
         <v>12</v>
       </c>
       <c r="B13" s="0" t="str">
-        <f aca="false">IF($A13="","",INDEX(BOM!$B$2:$B$108,MATCH(12,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A13="","",INDEX(BOM!$B$2:$B$110,MATCH(12,BOM!$O$2:$O$110,0)))</f>
         <v>100 nF ceramic capacitors, 100 pcs</v>
       </c>
       <c r="C13" s="0" t="n">
-        <f aca="false">IF($A13="","",INDEX(BOM!$G$2:$G$108,MATCH(12,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A13="","",INDEX(BOM!$G$2:$G$110,MATCH(12,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D13" s="9" t="n">
-        <f aca="false">IF($A13="","",INDEX(BOM!$H$2:$H$108,MATCH(12,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A13="","",INDEX(BOM!$H$2:$H$110,MATCH(12,BOM!$O$2:$O$110,0)))</f>
         <v>6.55</v>
       </c>
       <c r="E13" s="9" t="n">
-        <f aca="false">IF($A13="","",INDEX(BOM!$I$2:$I$108,MATCH(12,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A13="","",INDEX(BOM!$I$2:$I$110,MATCH(12,BOM!$O$2:$O$110,0)))</f>
         <v>6.55</v>
       </c>
       <c r="F13" s="0" t="str">
-        <f aca="false">IF($A13="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(12,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(12,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A13="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(12,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(12,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G13" s="0" t="str">
-        <f aca="false">IF($A13="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(12,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A13="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(12,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(13,BOM!$O$2:$O$108,0)),"",13)</f>
+        <f aca="false">IF(ISNA(MATCH(13,BOM!$O$2:$O$110,0)),"",13)</f>
         <v>13</v>
       </c>
       <c r="B14" s="0" t="str">
-        <f aca="false">IF($A14="","",INDEX(BOM!$B$2:$B$108,MATCH(13,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A14="","",INDEX(BOM!$B$2:$B$110,MATCH(13,BOM!$O$2:$O$110,0)))</f>
         <v>Electrolytic capacitor assortment 0.1-1000 uF (10-50 V)</v>
       </c>
       <c r="C14" s="0" t="n">
-        <f aca="false">IF($A14="","",INDEX(BOM!$G$2:$G$108,MATCH(13,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A14="","",INDEX(BOM!$G$2:$G$110,MATCH(13,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D14" s="9" t="n">
-        <f aca="false">IF($A14="","",INDEX(BOM!$H$2:$H$108,MATCH(13,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A14="","",INDEX(BOM!$H$2:$H$110,MATCH(13,BOM!$O$2:$O$110,0)))</f>
         <v>16.99</v>
       </c>
       <c r="E14" s="9" t="n">
-        <f aca="false">IF($A14="","",INDEX(BOM!$I$2:$I$108,MATCH(13,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A14="","",INDEX(BOM!$I$2:$I$110,MATCH(13,BOM!$O$2:$O$110,0)))</f>
         <v>16.99</v>
       </c>
       <c r="F14" s="0" t="str">
-        <f aca="false">IF($A14="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(13,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(13,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A14="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(13,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(13,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G14" s="0" t="str">
-        <f aca="false">IF($A14="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(13,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A14="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(13,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(14,BOM!$O$2:$O$108,0)),"",14)</f>
+        <f aca="false">IF(ISNA(MATCH(14,BOM!$O$2:$O$110,0)),"",14)</f>
         <v>14</v>
       </c>
       <c r="B15" s="0" t="str">
-        <f aca="false">IF($A15="","",INDEX(BOM!$B$2:$B$108,MATCH(14,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A15="","",INDEX(BOM!$B$2:$B$110,MATCH(14,BOM!$O$2:$O$110,0)))</f>
         <v>74AHCT125N DIP-14 level shifter, 10 pcs</v>
       </c>
       <c r="C15" s="0" t="n">
-        <f aca="false">IF($A15="","",INDEX(BOM!$G$2:$G$108,MATCH(14,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A15="","",INDEX(BOM!$G$2:$G$110,MATCH(14,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
-        <f aca="false">IF($A15="","",INDEX(BOM!$H$2:$H$108,MATCH(14,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A15="","",INDEX(BOM!$H$2:$H$110,MATCH(14,BOM!$O$2:$O$110,0)))</f>
         <v>11.56</v>
       </c>
       <c r="E15" s="9" t="n">
-        <f aca="false">IF($A15="","",INDEX(BOM!$I$2:$I$108,MATCH(14,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A15="","",INDEX(BOM!$I$2:$I$110,MATCH(14,BOM!$O$2:$O$110,0)))</f>
         <v>11.56</v>
       </c>
       <c r="F15" s="0" t="str">
-        <f aca="false">IF($A15="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(14,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(14,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A15="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(14,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(14,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G15" s="0" t="str">
-        <f aca="false">IF($A15="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(14,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A15="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(14,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(15,BOM!$O$2:$O$108,0)),"",15)</f>
+        <f aca="false">IF(ISNA(MATCH(15,BOM!$O$2:$O$110,0)),"",15)</f>
         <v>15</v>
       </c>
       <c r="B16" s="0" t="str">
-        <f aca="false">IF($A16="","",INDEX(BOM!$B$2:$B$108,MATCH(15,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A16="","",INDEX(BOM!$B$2:$B$110,MATCH(15,BOM!$O$2:$O$110,0)))</f>
         <v>Resistor kit 1/4 W 1%, 50 values</v>
       </c>
       <c r="C16" s="0" t="n">
-        <f aca="false">IF($A16="","",INDEX(BOM!$G$2:$G$108,MATCH(15,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A16="","",INDEX(BOM!$G$2:$G$110,MATCH(15,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D16" s="9" t="n">
-        <f aca="false">IF($A16="","",INDEX(BOM!$H$2:$H$108,MATCH(15,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A16="","",INDEX(BOM!$H$2:$H$110,MATCH(15,BOM!$O$2:$O$110,0)))</f>
         <v>19.99</v>
       </c>
       <c r="E16" s="9" t="n">
-        <f aca="false">IF($A16="","",INDEX(BOM!$I$2:$I$108,MATCH(15,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A16="","",INDEX(BOM!$I$2:$I$110,MATCH(15,BOM!$O$2:$O$110,0)))</f>
         <v>19.99</v>
       </c>
       <c r="F16" s="0" t="str">
-        <f aca="false">IF($A16="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(15,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(15,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A16="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(15,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(15,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G16" s="0" t="str">
-        <f aca="false">IF($A16="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(15,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A16="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(15,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(16,BOM!$O$2:$O$108,0)),"",16)</f>
+        <f aca="false">IF(ISNA(MATCH(16,BOM!$O$2:$O$110,0)),"",16)</f>
         <v>16</v>
       </c>
       <c r="B17" s="0" t="str">
-        <f aca="false">IF($A17="","",INDEX(BOM!$B$2:$B$108,MATCH(16,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A17="","",INDEX(BOM!$B$2:$B$110,MATCH(16,BOM!$O$2:$O$110,0)))</f>
         <v>2.2 kOhm 1/2 W resistors, 10 pcs</v>
       </c>
       <c r="C17" s="0" t="n">
-        <f aca="false">IF($A17="","",INDEX(BOM!$G$2:$G$108,MATCH(16,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A17="","",INDEX(BOM!$G$2:$G$110,MATCH(16,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">IF($A17="","",INDEX(BOM!$H$2:$H$108,MATCH(16,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A17="","",INDEX(BOM!$H$2:$H$110,MATCH(16,BOM!$O$2:$O$110,0)))</f>
         <v>8.76</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">IF($A17="","",INDEX(BOM!$I$2:$I$108,MATCH(16,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A17="","",INDEX(BOM!$I$2:$I$110,MATCH(16,BOM!$O$2:$O$110,0)))</f>
         <v>8.76</v>
       </c>
       <c r="F17" s="0" t="str">
-        <f aca="false">IF($A17="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(16,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(16,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A17="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(16,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(16,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G17" s="0" t="str">
-        <f aca="false">IF($A17="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(16,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A17="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(16,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(17,BOM!$O$2:$O$108,0)),"",17)</f>
+        <f aca="false">IF(ISNA(MATCH(17,BOM!$O$2:$O$110,0)),"",17)</f>
         <v>17</v>
       </c>
       <c r="B18" s="0" t="str">
-        <f aca="false">IF($A18="","",INDEX(BOM!$B$2:$B$108,MATCH(17,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A18="","",INDEX(BOM!$B$2:$B$110,MATCH(17,BOM!$O$2:$O$110,0)))</f>
         <v>PC817 optocoupler DIP-4, 20 pcs</v>
       </c>
       <c r="C18" s="0" t="n">
-        <f aca="false">IF($A18="","",INDEX(BOM!$G$2:$G$108,MATCH(17,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A18="","",INDEX(BOM!$G$2:$G$110,MATCH(17,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D18" s="9" t="n">
-        <f aca="false">IF($A18="","",INDEX(BOM!$H$2:$H$108,MATCH(17,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A18="","",INDEX(BOM!$H$2:$H$110,MATCH(17,BOM!$O$2:$O$110,0)))</f>
         <v>10.68</v>
       </c>
       <c r="E18" s="9" t="n">
-        <f aca="false">IF($A18="","",INDEX(BOM!$I$2:$I$108,MATCH(17,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A18="","",INDEX(BOM!$I$2:$I$110,MATCH(17,BOM!$O$2:$O$110,0)))</f>
         <v>10.68</v>
       </c>
       <c r="F18" s="0" t="str">
-        <f aca="false">IF($A18="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(17,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(17,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A18="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(17,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(17,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G18" s="0" t="str">
-        <f aca="false">IF($A18="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(17,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A18="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(17,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(18,BOM!$O$2:$O$108,0)),"",18)</f>
+        <f aca="false">IF(ISNA(MATCH(18,BOM!$O$2:$O$110,0)),"",18)</f>
         <v>18</v>
       </c>
       <c r="B19" s="0" t="str">
-        <f aca="false">IF($A19="","",INDEX(BOM!$B$2:$B$108,MATCH(18,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A19="","",INDEX(BOM!$B$2:$B$110,MATCH(18,BOM!$O$2:$O$110,0)))</f>
         <v>Perfboard 7 x 9 cm, 10 pcs</v>
       </c>
       <c r="C19" s="0" t="n">
-        <f aca="false">IF($A19="","",INDEX(BOM!$G$2:$G$108,MATCH(18,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A19="","",INDEX(BOM!$G$2:$G$110,MATCH(18,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D19" s="9" t="n">
-        <f aca="false">IF($A19="","",INDEX(BOM!$H$2:$H$108,MATCH(18,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A19="","",INDEX(BOM!$H$2:$H$110,MATCH(18,BOM!$O$2:$O$110,0)))</f>
         <v>12.96</v>
       </c>
       <c r="E19" s="9" t="n">
-        <f aca="false">IF($A19="","",INDEX(BOM!$I$2:$I$108,MATCH(18,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A19="","",INDEX(BOM!$I$2:$I$110,MATCH(18,BOM!$O$2:$O$110,0)))</f>
         <v>12.96</v>
       </c>
       <c r="F19" s="0" t="str">
-        <f aca="false">IF($A19="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(18,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(18,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A19="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(18,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(18,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G19" s="0" t="str">
-        <f aca="false">IF($A19="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(18,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A19="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(18,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(19,BOM!$O$2:$O$108,0)),"",19)</f>
+        <f aca="false">IF(ISNA(MATCH(19,BOM!$O$2:$O$110,0)),"",19)</f>
         <v>19</v>
       </c>
       <c r="B20" s="0" t="str">
-        <f aca="false">IF($A20="","",INDEX(BOM!$B$2:$B$108,MATCH(19,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A20="","",INDEX(BOM!$B$2:$B$110,MATCH(19,BOM!$O$2:$O$110,0)))</f>
         <v>2.54 mm male + female pin header kit</v>
       </c>
       <c r="C20" s="0" t="n">
-        <f aca="false">IF($A20="","",INDEX(BOM!$G$2:$G$108,MATCH(19,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A20="","",INDEX(BOM!$G$2:$G$110,MATCH(19,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D20" s="9" t="n">
-        <f aca="false">IF($A20="","",INDEX(BOM!$H$2:$H$108,MATCH(19,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A20="","",INDEX(BOM!$H$2:$H$110,MATCH(19,BOM!$O$2:$O$110,0)))</f>
         <v>18.99</v>
       </c>
       <c r="E20" s="9" t="n">
-        <f aca="false">IF($A20="","",INDEX(BOM!$I$2:$I$108,MATCH(19,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A20="","",INDEX(BOM!$I$2:$I$110,MATCH(19,BOM!$O$2:$O$110,0)))</f>
         <v>18.99</v>
       </c>
       <c r="F20" s="0" t="str">
-        <f aca="false">IF($A20="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(19,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(19,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A20="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(19,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(19,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G20" s="0" t="str">
-        <f aca="false">IF($A20="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(19,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A20="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(19,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(20,BOM!$O$2:$O$108,0)),"",20)</f>
+        <f aca="false">IF(ISNA(MATCH(20,BOM!$O$2:$O$110,0)),"",20)</f>
         <v>20</v>
       </c>
       <c r="B21" s="0" t="str">
-        <f aca="false">IF($A21="","",INDEX(BOM!$B$2:$B$108,MATCH(20,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A21="","",INDEX(BOM!$B$2:$B$110,MATCH(20,BOM!$O$2:$O$110,0)))</f>
         <v>JST-XH 2.54 mm connector kit with pre-crimped leads</v>
       </c>
       <c r="C21" s="0" t="n">
-        <f aca="false">IF($A21="","",INDEX(BOM!$G$2:$G$108,MATCH(20,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A21="","",INDEX(BOM!$G$2:$G$110,MATCH(20,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D21" s="9" t="n">
-        <f aca="false">IF($A21="","",INDEX(BOM!$H$2:$H$108,MATCH(20,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A21="","",INDEX(BOM!$H$2:$H$110,MATCH(20,BOM!$O$2:$O$110,0)))</f>
         <v>20.99</v>
       </c>
       <c r="E21" s="9" t="n">
-        <f aca="false">IF($A21="","",INDEX(BOM!$I$2:$I$108,MATCH(20,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A21="","",INDEX(BOM!$I$2:$I$110,MATCH(20,BOM!$O$2:$O$110,0)))</f>
         <v>20.99</v>
       </c>
       <c r="F21" s="0" t="str">
-        <f aca="false">IF($A21="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(20,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(20,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A21="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(20,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(20,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G21" s="0" t="str">
-        <f aca="false">IF($A21="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(20,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A21="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(20,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(21,BOM!$O$2:$O$108,0)),"",21)</f>
+        <f aca="false">IF(ISNA(MATCH(21,BOM!$O$2:$O$110,0)),"",21)</f>
         <v>21</v>
       </c>
       <c r="B22" s="0" t="str">
-        <f aca="false">IF($A22="","",INDEX(BOM!$B$2:$B$108,MATCH(21,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A22="","",INDEX(BOM!$B$2:$B$110,MATCH(21,BOM!$O$2:$O$110,0)))</f>
         <v>Dupont jumper wires, 120 pcs</v>
       </c>
       <c r="C22" s="0" t="n">
-        <f aca="false">IF($A22="","",INDEX(BOM!$G$2:$G$108,MATCH(21,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A22="","",INDEX(BOM!$G$2:$G$110,MATCH(21,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D22" s="9" t="n">
-        <f aca="false">IF($A22="","",INDEX(BOM!$H$2:$H$108,MATCH(21,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A22="","",INDEX(BOM!$H$2:$H$110,MATCH(21,BOM!$O$2:$O$110,0)))</f>
         <v>12.99</v>
       </c>
       <c r="E22" s="9" t="n">
-        <f aca="false">IF($A22="","",INDEX(BOM!$I$2:$I$108,MATCH(21,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A22="","",INDEX(BOM!$I$2:$I$110,MATCH(21,BOM!$O$2:$O$110,0)))</f>
         <v>12.99</v>
       </c>
       <c r="F22" s="0" t="str">
-        <f aca="false">IF($A22="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(21,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(21,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A22="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(21,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(21,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G22" s="0" t="str">
-        <f aca="false">IF($A22="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(21,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A22="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(21,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(22,BOM!$O$2:$O$108,0)),"",22)</f>
+        <f aca="false">IF(ISNA(MATCH(22,BOM!$O$2:$O$110,0)),"",22)</f>
         <v>22</v>
       </c>
       <c r="B23" s="0" t="str">
-        <f aca="false">IF($A23="","",INDEX(BOM!$B$2:$B$108,MATCH(22,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A23="","",INDEX(BOM!$B$2:$B$110,MATCH(22,BOM!$O$2:$O$110,0)))</f>
         <v>Cat6 patch cable 7.6 m (25 ft)</v>
       </c>
       <c r="C23" s="0" t="n">
-        <f aca="false">IF($A23="","",INDEX(BOM!$G$2:$G$108,MATCH(22,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A23="","",INDEX(BOM!$G$2:$G$110,MATCH(22,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D23" s="9" t="n">
-        <f aca="false">IF($A23="","",INDEX(BOM!$H$2:$H$108,MATCH(22,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A23="","",INDEX(BOM!$H$2:$H$110,MATCH(22,BOM!$O$2:$O$110,0)))</f>
         <v>17.99</v>
       </c>
       <c r="E23" s="9" t="n">
-        <f aca="false">IF($A23="","",INDEX(BOM!$I$2:$I$108,MATCH(22,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A23="","",INDEX(BOM!$I$2:$I$110,MATCH(22,BOM!$O$2:$O$110,0)))</f>
         <v>17.99</v>
       </c>
       <c r="F23" s="0" t="str">
-        <f aca="false">IF($A23="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(22,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(22,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A23="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(22,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(22,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G23" s="0" t="str">
-        <f aca="false">IF($A23="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(22,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A23="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(22,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(23,BOM!$O$2:$O$108,0)),"",23)</f>
+        <f aca="false">IF(ISNA(MATCH(23,BOM!$O$2:$O$110,0)),"",23)</f>
         <v>23</v>
       </c>
       <c r="B24" s="0" t="str">
-        <f aca="false">IF($A24="","",INDEX(BOM!$B$2:$B$108,MATCH(23,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A24="","",INDEX(BOM!$B$2:$B$110,MATCH(23,BOM!$O$2:$O$110,0)))</f>
         <v>22 AWG stranded hookup wire kit (6 colours)</v>
       </c>
       <c r="C24" s="0" t="n">
-        <f aca="false">IF($A24="","",INDEX(BOM!$G$2:$G$108,MATCH(23,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A24="","",INDEX(BOM!$G$2:$G$110,MATCH(23,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D24" s="9" t="n">
-        <f aca="false">IF($A24="","",INDEX(BOM!$H$2:$H$108,MATCH(23,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A24="","",INDEX(BOM!$H$2:$H$110,MATCH(23,BOM!$O$2:$O$110,0)))</f>
         <v>20.49</v>
       </c>
       <c r="E24" s="9" t="n">
-        <f aca="false">IF($A24="","",INDEX(BOM!$I$2:$I$108,MATCH(23,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A24="","",INDEX(BOM!$I$2:$I$110,MATCH(23,BOM!$O$2:$O$110,0)))</f>
         <v>20.49</v>
       </c>
       <c r="F24" s="0" t="str">
-        <f aca="false">IF($A24="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(23,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(23,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A24="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(23,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(23,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G24" s="0" t="str">
-        <f aca="false">IF($A24="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(23,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A24="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(23,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(24,BOM!$O$2:$O$108,0)),"",24)</f>
+        <f aca="false">IF(ISNA(MATCH(24,BOM!$O$2:$O$110,0)),"",24)</f>
         <v>24</v>
       </c>
       <c r="B25" s="0" t="str">
-        <f aca="false">IF($A25="","",INDEX(BOM!$B$2:$B$108,MATCH(24,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A25="","",INDEX(BOM!$B$2:$B$110,MATCH(24,BOM!$O$2:$O$110,0)))</f>
         <v>Mini toggle switch MTS-102, 6 mm (1/4") bushing, 10 pcs</v>
       </c>
       <c r="C25" s="0" t="n">
-        <f aca="false">IF($A25="","",INDEX(BOM!$G$2:$G$108,MATCH(24,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A25="","",INDEX(BOM!$G$2:$G$110,MATCH(24,BOM!$O$2:$O$110,0)))</f>
         <v>3</v>
       </c>
       <c r="D25" s="9" t="n">
-        <f aca="false">IF($A25="","",INDEX(BOM!$H$2:$H$108,MATCH(24,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A25="","",INDEX(BOM!$H$2:$H$110,MATCH(24,BOM!$O$2:$O$110,0)))</f>
         <v>8.45</v>
       </c>
       <c r="E25" s="9" t="n">
-        <f aca="false">IF($A25="","",INDEX(BOM!$I$2:$I$108,MATCH(24,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A25="","",INDEX(BOM!$I$2:$I$110,MATCH(24,BOM!$O$2:$O$110,0)))</f>
         <v>25.35</v>
       </c>
       <c r="F25" s="0" t="str">
-        <f aca="false">IF($A25="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(24,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(24,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A25="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(24,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(24,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G25" s="0" t="str">
-        <f aca="false">IF($A25="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(24,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A25="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(24,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(25,BOM!$O$2:$O$108,0)),"",25)</f>
+        <f aca="false">IF(ISNA(MATCH(25,BOM!$O$2:$O$110,0)),"",25)</f>
         <v>25</v>
       </c>
       <c r="B26" s="0" t="str">
-        <f aca="false">IF($A26="","",INDEX(BOM!$B$2:$B$108,MATCH(25,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A26="","",INDEX(BOM!$B$2:$B$110,MATCH(25,BOM!$O$2:$O$110,0)))</f>
         <v>Mini toggle MTS-103 ON-OFF-ON, 6 mm bushing, 10 pcs</v>
       </c>
       <c r="C26" s="0" t="n">
-        <f aca="false">IF($A26="","",INDEX(BOM!$G$2:$G$108,MATCH(25,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A26="","",INDEX(BOM!$G$2:$G$110,MATCH(25,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D26" s="9" t="n">
-        <f aca="false">IF($A26="","",INDEX(BOM!$H$2:$H$108,MATCH(25,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A26="","",INDEX(BOM!$H$2:$H$110,MATCH(25,BOM!$O$2:$O$110,0)))</f>
         <v>12.99</v>
       </c>
       <c r="E26" s="9" t="n">
-        <f aca="false">IF($A26="","",INDEX(BOM!$I$2:$I$108,MATCH(25,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A26="","",INDEX(BOM!$I$2:$I$110,MATCH(25,BOM!$O$2:$O$110,0)))</f>
         <v>12.99</v>
       </c>
       <c r="F26" s="0" t="str">
-        <f aca="false">IF($A26="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(25,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(25,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A26="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(25,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(25,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G26" s="0" t="str">
-        <f aca="false">IF($A26="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(25,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A26="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(25,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(26,BOM!$O$2:$O$108,0)),"",26)</f>
+        <f aca="false">IF(ISNA(MATCH(26,BOM!$O$2:$O$110,0)),"",26)</f>
         <v>26</v>
       </c>
       <c r="B27" s="0" t="str">
-        <f aca="false">IF($A27="","",INDEX(BOM!$B$2:$B$108,MATCH(26,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A27="","",INDEX(BOM!$B$2:$B$110,MATCH(26,BOM!$O$2:$O$110,0)))</f>
         <v>22 mm momentary push buttons (LA38, 5 colours), 6 pcs</v>
       </c>
       <c r="C27" s="0" t="n">
-        <f aca="false">IF($A27="","",INDEX(BOM!$G$2:$G$108,MATCH(26,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A27="","",INDEX(BOM!$G$2:$G$110,MATCH(26,BOM!$O$2:$O$110,0)))</f>
         <v>2</v>
       </c>
       <c r="D27" s="9" t="n">
-        <f aca="false">IF($A27="","",INDEX(BOM!$H$2:$H$108,MATCH(26,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A27="","",INDEX(BOM!$H$2:$H$110,MATCH(26,BOM!$O$2:$O$110,0)))</f>
         <v>19.49</v>
       </c>
       <c r="E27" s="9" t="n">
-        <f aca="false">IF($A27="","",INDEX(BOM!$I$2:$I$108,MATCH(26,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A27="","",INDEX(BOM!$I$2:$I$110,MATCH(26,BOM!$O$2:$O$110,0)))</f>
         <v>38.98</v>
       </c>
       <c r="F27" s="0" t="str">
-        <f aca="false">IF($A27="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(26,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(26,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A27="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(26,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(26,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G27" s="0" t="str">
-        <f aca="false">IF($A27="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(26,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A27="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(26,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(27,BOM!$O$2:$O$108,0)),"",27)</f>
+        <f aca="false">IF(ISNA(MATCH(27,BOM!$O$2:$O$110,0)),"",27)</f>
         <v>27</v>
       </c>
       <c r="B28" s="0" t="str">
-        <f aca="false">IF($A28="","",INDEX(BOM!$B$2:$B$108,MATCH(27,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A28="","",INDEX(BOM!$B$2:$B$110,MATCH(27,BOM!$O$2:$O$110,0)))</f>
         <v>19 mm momentary metal push buttons, 2 pcs</v>
       </c>
       <c r="C28" s="0" t="n">
-        <f aca="false">IF($A28="","",INDEX(BOM!$G$2:$G$108,MATCH(27,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A28="","",INDEX(BOM!$G$2:$G$110,MATCH(27,BOM!$O$2:$O$110,0)))</f>
         <v>2</v>
       </c>
       <c r="D28" s="9" t="n">
-        <f aca="false">IF($A28="","",INDEX(BOM!$H$2:$H$108,MATCH(27,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A28="","",INDEX(BOM!$H$2:$H$110,MATCH(27,BOM!$O$2:$O$110,0)))</f>
         <v>15.39</v>
       </c>
       <c r="E28" s="9" t="n">
-        <f aca="false">IF($A28="","",INDEX(BOM!$I$2:$I$108,MATCH(27,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A28="","",INDEX(BOM!$I$2:$I$110,MATCH(27,BOM!$O$2:$O$110,0)))</f>
         <v>30.78</v>
       </c>
       <c r="F28" s="0" t="str">
-        <f aca="false">IF($A28="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(27,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(27,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A28="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(27,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(27,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G28" s="0" t="str">
-        <f aca="false">IF($A28="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(27,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A28="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(27,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(28,BOM!$O$2:$O$108,0)),"",28)</f>
+        <f aca="false">IF(ISNA(MATCH(28,BOM!$O$2:$O$110,0)),"",28)</f>
         <v>28</v>
       </c>
       <c r="B29" s="0" t="str">
-        <f aca="false">IF($A29="","",INDEX(BOM!$B$2:$B$108,MATCH(28,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A29="","",INDEX(BOM!$B$2:$B$110,MATCH(28,BOM!$O$2:$O$110,0)))</f>
         <v>16 mm momentary metal push buttons, 5 pcs</v>
       </c>
       <c r="C29" s="0" t="n">
-        <f aca="false">IF($A29="","",INDEX(BOM!$G$2:$G$108,MATCH(28,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A29="","",INDEX(BOM!$G$2:$G$110,MATCH(28,BOM!$O$2:$O$110,0)))</f>
         <v>2</v>
       </c>
       <c r="D29" s="9" t="n">
-        <f aca="false">IF($A29="","",INDEX(BOM!$H$2:$H$108,MATCH(28,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A29="","",INDEX(BOM!$H$2:$H$110,MATCH(28,BOM!$O$2:$O$110,0)))</f>
         <v>11.99</v>
       </c>
       <c r="E29" s="9" t="n">
-        <f aca="false">IF($A29="","",INDEX(BOM!$I$2:$I$108,MATCH(28,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A29="","",INDEX(BOM!$I$2:$I$110,MATCH(28,BOM!$O$2:$O$110,0)))</f>
         <v>23.98</v>
       </c>
       <c r="F29" s="0" t="str">
-        <f aca="false">IF($A29="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(28,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(28,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A29="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(28,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(28,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G29" s="0" t="str">
-        <f aca="false">IF($A29="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(28,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A29="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(28,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(29,BOM!$O$2:$O$108,0)),"",29)</f>
+        <f aca="false">IF(ISNA(MATCH(29,BOM!$O$2:$O$110,0)),"",29)</f>
         <v>29</v>
       </c>
       <c r="B30" s="0" t="str">
-        <f aca="false">IF($A30="","",INDEX(BOM!$B$2:$B$108,MATCH(29,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A30="","",INDEX(BOM!$B$2:$B$110,MATCH(29,BOM!$O$2:$O$110,0)))</f>
         <v>EC11 rotary encoder with push switch + knob, 10 pcs</v>
       </c>
       <c r="C30" s="0" t="n">
-        <f aca="false">IF($A30="","",INDEX(BOM!$G$2:$G$108,MATCH(29,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A30="","",INDEX(BOM!$G$2:$G$110,MATCH(29,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D30" s="9" t="n">
-        <f aca="false">IF($A30="","",INDEX(BOM!$H$2:$H$108,MATCH(29,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A30="","",INDEX(BOM!$H$2:$H$110,MATCH(29,BOM!$O$2:$O$110,0)))</f>
         <v>17.99</v>
       </c>
       <c r="E30" s="9" t="n">
-        <f aca="false">IF($A30="","",INDEX(BOM!$I$2:$I$108,MATCH(29,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A30="","",INDEX(BOM!$I$2:$I$110,MATCH(29,BOM!$O$2:$O$110,0)))</f>
         <v>17.99</v>
       </c>
       <c r="F30" s="0" t="str">
-        <f aca="false">IF($A30="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(29,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(29,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A30="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(29,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(29,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G30" s="0" t="str">
-        <f aca="false">IF($A30="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(29,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A30="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(29,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(30,BOM!$O$2:$O$108,0)),"",30)</f>
+        <f aca="false">IF(ISNA(MATCH(30,BOM!$O$2:$O$110,0)),"",30)</f>
         <v>30</v>
       </c>
       <c r="B31" s="0" t="str">
-        <f aca="false">IF($A31="","",INDEX(BOM!$B$2:$B$108,MATCH(30,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A31="","",INDEX(BOM!$B$2:$B$110,MATCH(30,BOM!$O$2:$O$110,0)))</f>
         <v>B10K linear potentiometer, 16 mm, 6 mm D shaft</v>
       </c>
       <c r="C31" s="0" t="n">
-        <f aca="false">IF($A31="","",INDEX(BOM!$G$2:$G$108,MATCH(30,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A31="","",INDEX(BOM!$G$2:$G$110,MATCH(30,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D31" s="9" t="n">
-        <f aca="false">IF($A31="","",INDEX(BOM!$H$2:$H$108,MATCH(30,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A31="","",INDEX(BOM!$H$2:$H$110,MATCH(30,BOM!$O$2:$O$110,0)))</f>
         <v>6.95</v>
       </c>
       <c r="E31" s="9" t="n">
-        <f aca="false">IF($A31="","",INDEX(BOM!$I$2:$I$108,MATCH(30,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A31="","",INDEX(BOM!$I$2:$I$110,MATCH(30,BOM!$O$2:$O$110,0)))</f>
         <v>6.95</v>
       </c>
       <c r="F31" s="0" t="str">
-        <f aca="false">IF($A31="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(30,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(30,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A31="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(30,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(30,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G31" s="0" t="str">
-        <f aca="false">IF($A31="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(30,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A31="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(30,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(31,BOM!$O$2:$O$108,0)),"",31)</f>
+        <f aca="false">IF(ISNA(MATCH(31,BOM!$O$2:$O$110,0)),"",31)</f>
         <v>31</v>
       </c>
       <c r="B32" s="0" t="str">
-        <f aca="false">IF($A32="","",INDEX(BOM!$B$2:$B$108,MATCH(31,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A32="","",INDEX(BOM!$B$2:$B$110,MATCH(31,BOM!$O$2:$O$110,0)))</f>
         <v>KW11 lever micro switch, 10 pcs</v>
       </c>
       <c r="C32" s="0" t="n">
-        <f aca="false">IF($A32="","",INDEX(BOM!$G$2:$G$108,MATCH(31,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A32="","",INDEX(BOM!$G$2:$G$110,MATCH(31,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D32" s="9" t="n">
-        <f aca="false">IF($A32="","",INDEX(BOM!$H$2:$H$108,MATCH(31,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A32="","",INDEX(BOM!$H$2:$H$110,MATCH(31,BOM!$O$2:$O$110,0)))</f>
         <v>15.79</v>
       </c>
       <c r="E32" s="9" t="n">
-        <f aca="false">IF($A32="","",INDEX(BOM!$I$2:$I$108,MATCH(31,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A32="","",INDEX(BOM!$I$2:$I$110,MATCH(31,BOM!$O$2:$O$110,0)))</f>
         <v>15.79</v>
       </c>
       <c r="F32" s="0" t="str">
-        <f aca="false">IF($A32="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(31,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(31,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A32="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(31,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(31,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G32" s="0" t="str">
-        <f aca="false">IF($A32="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(31,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A32="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(31,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(32,BOM!$O$2:$O$108,0)),"",32)</f>
+        <f aca="false">IF(ISNA(MATCH(32,BOM!$O$2:$O$110,0)),"",32)</f>
         <v>32</v>
       </c>
       <c r="B33" s="0" t="str">
-        <f aca="false">IF($A33="","",INDEX(BOM!$B$2:$B$108,MATCH(32,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A33="","",INDEX(BOM!$B$2:$B$110,MATCH(32,BOM!$O$2:$O$110,0)))</f>
         <v>19 mm key switch, 2 position, key removable in OFF</v>
       </c>
       <c r="C33" s="0" t="n">
-        <f aca="false">IF($A33="","",INDEX(BOM!$G$2:$G$108,MATCH(32,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A33="","",INDEX(BOM!$G$2:$G$110,MATCH(32,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D33" s="9" t="n">
-        <f aca="false">IF($A33="","",INDEX(BOM!$H$2:$H$108,MATCH(32,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A33="","",INDEX(BOM!$H$2:$H$110,MATCH(32,BOM!$O$2:$O$110,0)))</f>
         <v>26.11</v>
       </c>
       <c r="E33" s="9" t="n">
-        <f aca="false">IF($A33="","",INDEX(BOM!$I$2:$I$108,MATCH(32,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A33="","",INDEX(BOM!$I$2:$I$110,MATCH(32,BOM!$O$2:$O$110,0)))</f>
         <v>26.11</v>
       </c>
       <c r="F33" s="0" t="str">
-        <f aca="false">IF($A33="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(32,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(32,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A33="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(32,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(32,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G33" s="0" t="str">
-        <f aca="false">IF($A33="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(32,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A33="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(32,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(33,BOM!$O$2:$O$108,0)),"",33)</f>
+        <f aca="false">IF(ISNA(MATCH(33,BOM!$O$2:$O$110,0)),"",33)</f>
         <v>33</v>
       </c>
       <c r="B34" s="0" t="str">
-        <f aca="false">IF($A34="","",INDEX(BOM!$B$2:$B$108,MATCH(33,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A34="","",INDEX(BOM!$B$2:$B$110,MATCH(33,BOM!$O$2:$O$110,0)))</f>
         <v>WS2812B LED strip 5 V, 60 LED/m, 5 m, IP30 (no sleeve)</v>
       </c>
       <c r="C34" s="0" t="n">
-        <f aca="false">IF($A34="","",INDEX(BOM!$G$2:$G$108,MATCH(33,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A34="","",INDEX(BOM!$G$2:$G$110,MATCH(33,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D34" s="9" t="n">
-        <f aca="false">IF($A34="","",INDEX(BOM!$H$2:$H$108,MATCH(33,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A34="","",INDEX(BOM!$H$2:$H$110,MATCH(33,BOM!$O$2:$O$110,0)))</f>
         <v>25.99</v>
       </c>
       <c r="E34" s="9" t="n">
-        <f aca="false">IF($A34="","",INDEX(BOM!$I$2:$I$108,MATCH(33,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A34="","",INDEX(BOM!$I$2:$I$110,MATCH(33,BOM!$O$2:$O$110,0)))</f>
         <v>25.99</v>
       </c>
       <c r="F34" s="0" t="str">
-        <f aca="false">IF($A34="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(33,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(33,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A34="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(33,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(33,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G34" s="0" t="str">
-        <f aca="false">IF($A34="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(33,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A34="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(33,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(34,BOM!$O$2:$O$108,0)),"",34)</f>
+        <f aca="false">IF(ISNA(MATCH(34,BOM!$O$2:$O$110,0)),"",34)</f>
         <v>34</v>
       </c>
       <c r="B35" s="0" t="str">
-        <f aca="false">IF($A35="","",INDEX(BOM!$B$2:$B$108,MATCH(34,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A35="","",INDEX(BOM!$B$2:$B$110,MATCH(34,BOM!$O$2:$O$110,0)))</f>
         <v>WS2812D-F5 5 mm through-hole addressable RGB LEDs, ~40 pcs</v>
       </c>
       <c r="C35" s="0" t="n">
-        <f aca="false">IF($A35="","",INDEX(BOM!$G$2:$G$108,MATCH(34,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A35="","",INDEX(BOM!$G$2:$G$110,MATCH(34,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D35" s="9" t="n">
-        <f aca="false">IF($A35="","",INDEX(BOM!$H$2:$H$108,MATCH(34,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A35="","",INDEX(BOM!$H$2:$H$110,MATCH(34,BOM!$O$2:$O$110,0)))</f>
         <v>20</v>
       </c>
       <c r="E35" s="9" t="n">
-        <f aca="false">IF($A35="","",INDEX(BOM!$I$2:$I$108,MATCH(34,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A35="","",INDEX(BOM!$I$2:$I$110,MATCH(34,BOM!$O$2:$O$110,0)))</f>
         <v>20</v>
       </c>
       <c r="F35" s="0" t="str">
-        <f aca="false">IF($A35="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(34,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(34,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A35="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(34,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(34,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G35" s="0" t="str">
-        <f aca="false">IF($A35="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(34,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A35="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(34,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(35,BOM!$O$2:$O$108,0)),"",35)</f>
+        <f aca="false">IF(ISNA(MATCH(35,BOM!$O$2:$O$110,0)),"",35)</f>
         <v>35</v>
       </c>
       <c r="B36" s="0" t="str">
-        <f aca="false">IF($A36="","",INDEX(BOM!$B$2:$B$108,MATCH(35,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A36="","",INDEX(BOM!$B$2:$B$110,MATCH(35,BOM!$O$2:$O$110,0)))</f>
         <v>5 mm LED holders / bezels, 50 pcs</v>
       </c>
       <c r="C36" s="0" t="n">
-        <f aca="false">IF($A36="","",INDEX(BOM!$G$2:$G$108,MATCH(35,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A36="","",INDEX(BOM!$G$2:$G$110,MATCH(35,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D36" s="9" t="n">
-        <f aca="false">IF($A36="","",INDEX(BOM!$H$2:$H$108,MATCH(35,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A36="","",INDEX(BOM!$H$2:$H$110,MATCH(35,BOM!$O$2:$O$110,0)))</f>
         <v>9.19</v>
       </c>
       <c r="E36" s="9" t="n">
-        <f aca="false">IF($A36="","",INDEX(BOM!$I$2:$I$108,MATCH(35,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A36="","",INDEX(BOM!$I$2:$I$110,MATCH(35,BOM!$O$2:$O$110,0)))</f>
         <v>9.19</v>
       </c>
       <c r="F36" s="0" t="str">
-        <f aca="false">IF($A36="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(35,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(35,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A36="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(35,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(35,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G36" s="0" t="str">
-        <f aca="false">IF($A36="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(35,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A36="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(35,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(36,BOM!$O$2:$O$108,0)),"",36)</f>
+        <f aca="false">IF(ISNA(MATCH(36,BOM!$O$2:$O$110,0)),"",36)</f>
         <v>36</v>
       </c>
       <c r="B37" s="0" t="str">
-        <f aca="false">IF($A37="","",INDEX(BOM!$B$2:$B$108,MATCH(36,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A37="","",INDEX(BOM!$B$2:$B$110,MATCH(36,BOM!$O$2:$O$110,0)))</f>
         <v>Mean Well LRS-50-5 (5 V 10 A) power supply</v>
       </c>
       <c r="C37" s="0" t="n">
-        <f aca="false">IF($A37="","",INDEX(BOM!$G$2:$G$108,MATCH(36,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A37="","",INDEX(BOM!$G$2:$G$110,MATCH(36,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D37" s="9" t="n">
-        <f aca="false">IF($A37="","",INDEX(BOM!$H$2:$H$108,MATCH(36,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A37="","",INDEX(BOM!$H$2:$H$110,MATCH(36,BOM!$O$2:$O$110,0)))</f>
         <v>31.75</v>
       </c>
       <c r="E37" s="9" t="n">
-        <f aca="false">IF($A37="","",INDEX(BOM!$I$2:$I$108,MATCH(36,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A37="","",INDEX(BOM!$I$2:$I$110,MATCH(36,BOM!$O$2:$O$110,0)))</f>
         <v>31.75</v>
       </c>
       <c r="F37" s="0" t="str">
-        <f aca="false">IF($A37="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(36,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(36,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A37="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(36,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(36,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G37" s="0" t="str">
-        <f aca="false">IF($A37="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(36,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A37="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(36,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(37,BOM!$O$2:$O$108,0)),"",37)</f>
+        <f aca="false">IF(ISNA(MATCH(37,BOM!$O$2:$O$110,0)),"",37)</f>
         <v>37</v>
       </c>
       <c r="B38" s="0" t="str">
-        <f aca="false">IF($A38="","",INDEX(BOM!$B$2:$B$108,MATCH(37,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A38="","",INDEX(BOM!$B$2:$B$110,MATCH(37,BOM!$O$2:$O$110,0)))</f>
         <v>Inline 5x20 mm fuse holders + fast-blow fuse kit</v>
       </c>
       <c r="C38" s="0" t="n">
-        <f aca="false">IF($A38="","",INDEX(BOM!$G$2:$G$108,MATCH(37,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A38="","",INDEX(BOM!$G$2:$G$110,MATCH(37,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D38" s="9" t="n">
-        <f aca="false">IF($A38="","",INDEX(BOM!$H$2:$H$108,MATCH(37,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A38="","",INDEX(BOM!$H$2:$H$110,MATCH(37,BOM!$O$2:$O$110,0)))</f>
         <v>14.99</v>
       </c>
       <c r="E38" s="9" t="n">
-        <f aca="false">IF($A38="","",INDEX(BOM!$I$2:$I$108,MATCH(37,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A38="","",INDEX(BOM!$I$2:$I$110,MATCH(37,BOM!$O$2:$O$110,0)))</f>
         <v>14.99</v>
       </c>
       <c r="F38" s="0" t="str">
-        <f aca="false">IF($A38="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(37,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(37,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A38="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(37,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(37,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G38" s="0" t="str">
-        <f aca="false">IF($A38="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(37,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A38="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(37,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(38,BOM!$O$2:$O$108,0)),"",38)</f>
+        <f aca="false">IF(ISNA(MATCH(38,BOM!$O$2:$O$110,0)),"",38)</f>
         <v>38</v>
       </c>
       <c r="B39" s="0" t="str">
-        <f aca="false">IF($A39="","",INDEX(BOM!$B$2:$B$108,MATCH(38,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A39="","",INDEX(BOM!$B$2:$B$110,MATCH(38,BOM!$O$2:$O$110,0)))</f>
         <v>16 AWG red/black 2-conductor wire, 15 m (50 ft)</v>
       </c>
       <c r="C39" s="0" t="n">
-        <f aca="false">IF($A39="","",INDEX(BOM!$G$2:$G$108,MATCH(38,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A39="","",INDEX(BOM!$G$2:$G$110,MATCH(38,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D39" s="9" t="n">
-        <f aca="false">IF($A39="","",INDEX(BOM!$H$2:$H$108,MATCH(38,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A39="","",INDEX(BOM!$H$2:$H$110,MATCH(38,BOM!$O$2:$O$110,0)))</f>
         <v>16.99</v>
       </c>
       <c r="E39" s="9" t="n">
-        <f aca="false">IF($A39="","",INDEX(BOM!$I$2:$I$108,MATCH(38,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A39="","",INDEX(BOM!$I$2:$I$110,MATCH(38,BOM!$O$2:$O$110,0)))</f>
         <v>16.99</v>
       </c>
       <c r="F39" s="0" t="str">
-        <f aca="false">IF($A39="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(38,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(38,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A39="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(38,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(38,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G39" s="0" t="str">
-        <f aca="false">IF($A39="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(38,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A39="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(38,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(39,BOM!$O$2:$O$108,0)),"",39)</f>
+        <f aca="false">IF(ISNA(MATCH(39,BOM!$O$2:$O$110,0)),"",39)</f>
         <v>39</v>
       </c>
       <c r="B40" s="0" t="str">
-        <f aca="false">IF($A40="","",INDEX(BOM!$B$2:$B$108,MATCH(39,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A40="","",INDEX(BOM!$B$2:$B$110,MATCH(39,BOM!$O$2:$O$110,0)))</f>
         <v>18 AWG red/black silicone wire, 7.6 m (25 ft)</v>
       </c>
       <c r="C40" s="0" t="n">
-        <f aca="false">IF($A40="","",INDEX(BOM!$G$2:$G$108,MATCH(39,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A40="","",INDEX(BOM!$G$2:$G$110,MATCH(39,BOM!$O$2:$O$110,0)))</f>
         <v>2</v>
       </c>
       <c r="D40" s="9" t="n">
-        <f aca="false">IF($A40="","",INDEX(BOM!$H$2:$H$108,MATCH(39,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A40="","",INDEX(BOM!$H$2:$H$110,MATCH(39,BOM!$O$2:$O$110,0)))</f>
         <v>19.82</v>
       </c>
       <c r="E40" s="9" t="n">
-        <f aca="false">IF($A40="","",INDEX(BOM!$I$2:$I$108,MATCH(39,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A40="","",INDEX(BOM!$I$2:$I$110,MATCH(39,BOM!$O$2:$O$110,0)))</f>
         <v>39.64</v>
       </c>
       <c r="F40" s="0" t="str">
-        <f aca="false">IF($A40="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(39,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(39,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A40="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(39,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(39,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G40" s="0" t="str">
-        <f aca="false">IF($A40="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(39,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A40="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(39,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(40,BOM!$O$2:$O$108,0)),"",40)</f>
+        <f aca="false">IF(ISNA(MATCH(40,BOM!$O$2:$O$110,0)),"",40)</f>
         <v>40</v>
       </c>
       <c r="B41" s="0" t="str">
-        <f aca="false">IF($A41="","",INDEX(BOM!$B$2:$B$108,MATCH(40,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A41="","",INDEX(BOM!$B$2:$B$110,MATCH(40,BOM!$O$2:$O$110,0)))</f>
         <v>JST-SM 3-pin pigtails (WS2812), 60 pcs</v>
       </c>
       <c r="C41" s="0" t="n">
-        <f aca="false">IF($A41="","",INDEX(BOM!$G$2:$G$108,MATCH(40,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A41="","",INDEX(BOM!$G$2:$G$110,MATCH(40,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D41" s="9" t="n">
-        <f aca="false">IF($A41="","",INDEX(BOM!$H$2:$H$108,MATCH(40,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A41="","",INDEX(BOM!$H$2:$H$110,MATCH(40,BOM!$O$2:$O$110,0)))</f>
         <v>18.59</v>
       </c>
       <c r="E41" s="9" t="n">
-        <f aca="false">IF($A41="","",INDEX(BOM!$I$2:$I$108,MATCH(40,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A41="","",INDEX(BOM!$I$2:$I$110,MATCH(40,BOM!$O$2:$O$110,0)))</f>
         <v>18.59</v>
       </c>
       <c r="F41" s="0" t="str">
-        <f aca="false">IF($A41="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(40,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(40,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A41="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(40,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(40,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G41" s="0" t="str">
-        <f aca="false">IF($A41="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(40,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A41="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(40,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(41,BOM!$O$2:$O$108,0)),"",41)</f>
+        <f aca="false">IF(ISNA(MATCH(41,BOM!$O$2:$O$110,0)),"",41)</f>
         <v>41</v>
       </c>
       <c r="B42" s="0" t="str">
-        <f aca="false">IF($A42="","",INDEX(BOM!$B$2:$B$108,MATCH(41,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A42="","",INDEX(BOM!$B$2:$B$110,MATCH(41,BOM!$O$2:$O$110,0)))</f>
         <v>PETG filament 1.75 mm BLACK, 1 kg</v>
       </c>
       <c r="C42" s="0" t="n">
-        <f aca="false">IF($A42="","",INDEX(BOM!$G$2:$G$108,MATCH(41,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A42="","",INDEX(BOM!$G$2:$G$110,MATCH(41,BOM!$O$2:$O$110,0)))</f>
         <v>6</v>
       </c>
       <c r="D42" s="9" t="n">
-        <f aca="false">IF($A42="","",INDEX(BOM!$H$2:$H$108,MATCH(41,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A42="","",INDEX(BOM!$H$2:$H$110,MATCH(41,BOM!$O$2:$O$110,0)))</f>
         <v>19.94</v>
       </c>
       <c r="E42" s="9" t="n">
-        <f aca="false">IF($A42="","",INDEX(BOM!$I$2:$I$108,MATCH(41,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A42="","",INDEX(BOM!$I$2:$I$110,MATCH(41,BOM!$O$2:$O$110,0)))</f>
         <v>119.64</v>
       </c>
       <c r="F42" s="0" t="str">
-        <f aca="false">IF($A42="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(41,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(41,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A42="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(41,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(41,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G42" s="0" t="str">
-        <f aca="false">IF($A42="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(41,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A42="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(41,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(42,BOM!$O$2:$O$108,0)),"",42)</f>
+        <f aca="false">IF(ISNA(MATCH(42,BOM!$O$2:$O$110,0)),"",42)</f>
         <v>42</v>
       </c>
       <c r="B43" s="0" t="str">
-        <f aca="false">IF($A43="","",INDEX(BOM!$B$2:$B$108,MATCH(42,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A43="","",INDEX(BOM!$B$2:$B$110,MATCH(42,BOM!$O$2:$O$110,0)))</f>
         <v>PETG filament 1.75 mm WHITE, 1 kg</v>
       </c>
       <c r="C43" s="0" t="n">
-        <f aca="false">IF($A43="","",INDEX(BOM!$G$2:$G$108,MATCH(42,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A43="","",INDEX(BOM!$G$2:$G$110,MATCH(42,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D43" s="9" t="n">
-        <f aca="false">IF($A43="","",INDEX(BOM!$H$2:$H$108,MATCH(42,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A43="","",INDEX(BOM!$H$2:$H$110,MATCH(42,BOM!$O$2:$O$110,0)))</f>
         <v>20.89</v>
       </c>
       <c r="E43" s="9" t="n">
-        <f aca="false">IF($A43="","",INDEX(BOM!$I$2:$I$108,MATCH(42,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A43="","",INDEX(BOM!$I$2:$I$110,MATCH(42,BOM!$O$2:$O$110,0)))</f>
         <v>20.89</v>
       </c>
       <c r="F43" s="0" t="str">
-        <f aca="false">IF($A43="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(42,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(42,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A43="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(42,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(42,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G43" s="0" t="str">
-        <f aca="false">IF($A43="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(42,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A43="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(42,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(43,BOM!$O$2:$O$108,0)),"",43)</f>
+        <f aca="false">IF(ISNA(MATCH(43,BOM!$O$2:$O$110,0)),"",43)</f>
         <v>43</v>
       </c>
       <c r="B44" s="0" t="str">
-        <f aca="false">IF($A44="","",INDEX(BOM!$B$2:$B$108,MATCH(43,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A44="","",INDEX(BOM!$B$2:$B$110,MATCH(43,BOM!$O$2:$O$110,0)))</f>
         <v>Brass heat-set inserts kit M2-M6 (360 pcs)</v>
       </c>
       <c r="C44" s="0" t="n">
-        <f aca="false">IF($A44="","",INDEX(BOM!$G$2:$G$108,MATCH(43,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A44="","",INDEX(BOM!$G$2:$G$110,MATCH(43,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D44" s="9" t="n">
-        <f aca="false">IF($A44="","",INDEX(BOM!$H$2:$H$108,MATCH(43,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A44="","",INDEX(BOM!$H$2:$H$110,MATCH(43,BOM!$O$2:$O$110,0)))</f>
         <v>26.99</v>
       </c>
       <c r="E44" s="9" t="n">
-        <f aca="false">IF($A44="","",INDEX(BOM!$I$2:$I$108,MATCH(43,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A44="","",INDEX(BOM!$I$2:$I$110,MATCH(43,BOM!$O$2:$O$110,0)))</f>
         <v>26.99</v>
       </c>
       <c r="F44" s="0" t="str">
-        <f aca="false">IF($A44="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(43,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(43,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A44="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(43,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(43,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G44" s="0" t="str">
-        <f aca="false">IF($A44="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(43,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A44="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(43,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(44,BOM!$O$2:$O$108,0)),"",44)</f>
+        <f aca="false">IF(ISNA(MATCH(44,BOM!$O$2:$O$110,0)),"",44)</f>
         <v>44</v>
       </c>
       <c r="B45" s="0" t="str">
-        <f aca="false">IF($A45="","",INDEX(BOM!$B$2:$B$108,MATCH(44,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A45="","",INDEX(BOM!$B$2:$B$110,MATCH(44,BOM!$O$2:$O$110,0)))</f>
         <v>Metric socket screw assortment M2-M5 (1760 pcs)</v>
       </c>
       <c r="C45" s="0" t="n">
-        <f aca="false">IF($A45="","",INDEX(BOM!$G$2:$G$108,MATCH(44,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A45="","",INDEX(BOM!$G$2:$G$110,MATCH(44,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D45" s="9" t="n">
-        <f aca="false">IF($A45="","",INDEX(BOM!$H$2:$H$108,MATCH(44,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A45="","",INDEX(BOM!$H$2:$H$110,MATCH(44,BOM!$O$2:$O$110,0)))</f>
         <v>28.99</v>
       </c>
       <c r="E45" s="9" t="n">
-        <f aca="false">IF($A45="","",INDEX(BOM!$I$2:$I$108,MATCH(44,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A45="","",INDEX(BOM!$I$2:$I$110,MATCH(44,BOM!$O$2:$O$110,0)))</f>
         <v>28.99</v>
       </c>
       <c r="F45" s="0" t="str">
-        <f aca="false">IF($A45="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(44,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(44,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A45="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(44,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(44,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G45" s="0" t="str">
-        <f aca="false">IF($A45="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(44,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A45="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(44,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(45,BOM!$O$2:$O$108,0)),"",45)</f>
+        <f aca="false">IF(ISNA(MATCH(45,BOM!$O$2:$O$110,0)),"",45)</f>
         <v>45</v>
       </c>
       <c r="B46" s="0" t="str">
-        <f aca="false">IF($A46="","",INDEX(BOM!$B$2:$B$108,MATCH(45,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A46="","",INDEX(BOM!$B$2:$B$110,MATCH(45,BOM!$O$2:$O$110,0)))</f>
         <v>Self-tapping screw assortment M2 / M2.5 / M3</v>
       </c>
       <c r="C46" s="0" t="n">
-        <f aca="false">IF($A46="","",INDEX(BOM!$G$2:$G$108,MATCH(45,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A46="","",INDEX(BOM!$G$2:$G$110,MATCH(45,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D46" s="9" t="n">
-        <f aca="false">IF($A46="","",INDEX(BOM!$H$2:$H$108,MATCH(45,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A46="","",INDEX(BOM!$H$2:$H$110,MATCH(45,BOM!$O$2:$O$110,0)))</f>
         <v>16.99</v>
       </c>
       <c r="E46" s="9" t="n">
-        <f aca="false">IF($A46="","",INDEX(BOM!$I$2:$I$108,MATCH(45,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A46="","",INDEX(BOM!$I$2:$I$110,MATCH(45,BOM!$O$2:$O$110,0)))</f>
         <v>16.99</v>
       </c>
       <c r="F46" s="0" t="str">
-        <f aca="false">IF($A46="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(45,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(45,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A46="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(45,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(45,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G46" s="0" t="str">
-        <f aca="false">IF($A46="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(45,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A46="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(45,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(46,BOM!$O$2:$O$108,0)),"",46)</f>
+        <f aca="false">IF(ISNA(MATCH(46,BOM!$O$2:$O$110,0)),"",46)</f>
         <v>46</v>
       </c>
       <c r="B47" s="0" t="str">
-        <f aca="false">IF($A47="","",INDEX(BOM!$B$2:$B$108,MATCH(46,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A47="","",INDEX(BOM!$B$2:$B$110,MATCH(46,BOM!$O$2:$O$110,0)))</f>
         <v>M5 four-prong T-nuts, M5 x 8 mm, 200 pcs</v>
       </c>
       <c r="C47" s="0" t="n">
-        <f aca="false">IF($A47="","",INDEX(BOM!$G$2:$G$108,MATCH(46,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A47="","",INDEX(BOM!$G$2:$G$110,MATCH(46,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D47" s="9" t="n">
-        <f aca="false">IF($A47="","",INDEX(BOM!$H$2:$H$108,MATCH(46,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A47="","",INDEX(BOM!$H$2:$H$110,MATCH(46,BOM!$O$2:$O$110,0)))</f>
         <v>44.38</v>
       </c>
       <c r="E47" s="9" t="n">
-        <f aca="false">IF($A47="","",INDEX(BOM!$I$2:$I$108,MATCH(46,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A47="","",INDEX(BOM!$I$2:$I$110,MATCH(46,BOM!$O$2:$O$110,0)))</f>
         <v>44.38</v>
       </c>
       <c r="F47" s="0" t="str">
-        <f aca="false">IF($A47="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(46,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(46,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A47="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(46,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(46,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G47" s="0" t="str">
-        <f aca="false">IF($A47="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(46,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A47="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(46,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(47,BOM!$O$2:$O$108,0)),"",47)</f>
+        <f aca="false">IF(ISNA(MATCH(47,BOM!$O$2:$O$110,0)),"",47)</f>
         <v>47</v>
       </c>
       <c r="B48" s="0" t="str">
-        <f aca="false">IF($A48="","",INDEX(BOM!$B$2:$B$108,MATCH(47,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A48="","",INDEX(BOM!$B$2:$B$110,MATCH(47,BOM!$O$2:$O$110,0)))</f>
         <v>M5 x 20 flanged button-head socket screws, black, 50 pcs</v>
       </c>
       <c r="C48" s="0" t="n">
-        <f aca="false">IF($A48="","",INDEX(BOM!$G$2:$G$108,MATCH(47,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A48="","",INDEX(BOM!$G$2:$G$110,MATCH(47,BOM!$O$2:$O$110,0)))</f>
         <v>4</v>
       </c>
       <c r="D48" s="9" t="n">
-        <f aca="false">IF($A48="","",INDEX(BOM!$H$2:$H$108,MATCH(47,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A48="","",INDEX(BOM!$H$2:$H$110,MATCH(47,BOM!$O$2:$O$110,0)))</f>
         <v>14.99</v>
       </c>
       <c r="E48" s="9" t="n">
-        <f aca="false">IF($A48="","",INDEX(BOM!$I$2:$I$108,MATCH(47,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A48="","",INDEX(BOM!$I$2:$I$110,MATCH(47,BOM!$O$2:$O$110,0)))</f>
         <v>59.96</v>
       </c>
       <c r="F48" s="0" t="str">
-        <f aca="false">IF($A48="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(47,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(47,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A48="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(47,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(47,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G48" s="0" t="str">
-        <f aca="false">IF($A48="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(47,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A48="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(47,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(48,BOM!$O$2:$O$108,0)),"",48)</f>
+        <f aca="false">IF(ISNA(MATCH(48,BOM!$O$2:$O$110,0)),"",48)</f>
         <v>48</v>
       </c>
       <c r="B49" s="0" t="str">
-        <f aca="false">IF($A49="","",INDEX(BOM!$B$2:$B$108,MATCH(48,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A49="","",INDEX(BOM!$B$2:$B$110,MATCH(48,BOM!$O$2:$O$110,0)))</f>
         <v>M5 flat washers, 200 pcs</v>
       </c>
       <c r="C49" s="0" t="n">
-        <f aca="false">IF($A49="","",INDEX(BOM!$G$2:$G$108,MATCH(48,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A49="","",INDEX(BOM!$G$2:$G$110,MATCH(48,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D49" s="9" t="n">
-        <f aca="false">IF($A49="","",INDEX(BOM!$H$2:$H$108,MATCH(48,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A49="","",INDEX(BOM!$H$2:$H$110,MATCH(48,BOM!$O$2:$O$110,0)))</f>
         <v>9.99</v>
       </c>
       <c r="E49" s="9" t="n">
-        <f aca="false">IF($A49="","",INDEX(BOM!$I$2:$I$108,MATCH(48,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A49="","",INDEX(BOM!$I$2:$I$110,MATCH(48,BOM!$O$2:$O$110,0)))</f>
         <v>9.99</v>
       </c>
       <c r="F49" s="0" t="str">
-        <f aca="false">IF($A49="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(48,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(48,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A49="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(48,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(48,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G49" s="0" t="str">
-        <f aca="false">IF($A49="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(48,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A49="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(48,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(49,BOM!$O$2:$O$108,0)),"",49)</f>
+        <f aca="false">IF(ISNA(MATCH(49,BOM!$O$2:$O$110,0)),"",49)</f>
         <v>49</v>
       </c>
       <c r="B50" s="0" t="str">
-        <f aca="false">IF($A50="","",INDEX(BOM!$B$2:$B$108,MATCH(49,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A50="","",INDEX(BOM!$B$2:$B$110,MATCH(49,BOM!$O$2:$O$110,0)))</f>
         <v>2 mm stainless safety cable with loops, 300 mm (12"), 5 pcs</v>
       </c>
       <c r="C50" s="0" t="n">
-        <f aca="false">IF($A50="","",INDEX(BOM!$G$2:$G$108,MATCH(49,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A50="","",INDEX(BOM!$G$2:$G$110,MATCH(49,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D50" s="9" t="n">
-        <f aca="false">IF($A50="","",INDEX(BOM!$H$2:$H$108,MATCH(49,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A50="","",INDEX(BOM!$H$2:$H$110,MATCH(49,BOM!$O$2:$O$110,0)))</f>
         <v>9.99</v>
       </c>
       <c r="E50" s="9" t="n">
-        <f aca="false">IF($A50="","",INDEX(BOM!$I$2:$I$108,MATCH(49,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A50="","",INDEX(BOM!$I$2:$I$110,MATCH(49,BOM!$O$2:$O$110,0)))</f>
         <v>9.99</v>
       </c>
       <c r="F50" s="0" t="str">
-        <f aca="false">IF($A50="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(49,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(49,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A50="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(49,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(49,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G50" s="0" t="str">
-        <f aca="false">IF($A50="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(49,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A50="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(49,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(50,BOM!$O$2:$O$108,0)),"",50)</f>
+        <f aca="false">IF(ISNA(MATCH(50,BOM!$O$2:$O$110,0)),"",50)</f>
         <v>50</v>
       </c>
       <c r="B51" s="0" t="str">
-        <f aca="false">IF($A51="","",INDEX(BOM!$B$2:$B$108,MATCH(50,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A51="","",INDEX(BOM!$B$2:$B$110,MATCH(50,BOM!$O$2:$O$110,0)))</f>
         <v>25 mm linear shaft, 1000 mm, 2 pcs</v>
       </c>
       <c r="C51" s="0" t="n">
-        <f aca="false">IF($A51="","",INDEX(BOM!$G$2:$G$108,MATCH(50,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A51="","",INDEX(BOM!$G$2:$G$110,MATCH(50,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D51" s="9" t="n">
-        <f aca="false">IF($A51="","",INDEX(BOM!$H$2:$H$108,MATCH(50,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A51="","",INDEX(BOM!$H$2:$H$110,MATCH(50,BOM!$O$2:$O$110,0)))</f>
         <v>46.99</v>
       </c>
       <c r="E51" s="9" t="n">
-        <f aca="false">IF($A51="","",INDEX(BOM!$I$2:$I$108,MATCH(50,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A51="","",INDEX(BOM!$I$2:$I$110,MATCH(50,BOM!$O$2:$O$110,0)))</f>
         <v>46.99</v>
       </c>
       <c r="F51" s="0" t="str">
-        <f aca="false">IF($A51="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(50,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(50,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A51="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(50,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(50,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G51" s="0" t="str">
-        <f aca="false">IF($A51="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(50,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A51="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(50,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(51,BOM!$O$2:$O$108,0)),"",51)</f>
+        <f aca="false">IF(ISNA(MATCH(51,BOM!$O$2:$O$110,0)),"",51)</f>
         <v>51</v>
       </c>
       <c r="B52" s="0" t="str">
-        <f aca="false">IF($A52="","",INDEX(BOM!$B$2:$B$108,MATCH(51,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A52="","",INDEX(BOM!$B$2:$B$110,MATCH(51,BOM!$O$2:$O$110,0)))</f>
         <v>SHF25 shaft supports, 4 pcs</v>
       </c>
       <c r="C52" s="0" t="n">
-        <f aca="false">IF($A52="","",INDEX(BOM!$G$2:$G$108,MATCH(51,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A52="","",INDEX(BOM!$G$2:$G$110,MATCH(51,BOM!$O$2:$O$110,0)))</f>
         <v>2</v>
       </c>
       <c r="D52" s="9" t="n">
-        <f aca="false">IF($A52="","",INDEX(BOM!$H$2:$H$108,MATCH(51,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A52="","",INDEX(BOM!$H$2:$H$110,MATCH(51,BOM!$O$2:$O$110,0)))</f>
         <v>13.49</v>
       </c>
       <c r="E52" s="9" t="n">
-        <f aca="false">IF($A52="","",INDEX(BOM!$I$2:$I$108,MATCH(51,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A52="","",INDEX(BOM!$I$2:$I$110,MATCH(51,BOM!$O$2:$O$110,0)))</f>
         <v>26.98</v>
       </c>
       <c r="F52" s="0" t="str">
-        <f aca="false">IF($A52="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(51,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(51,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A52="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(51,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(51,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G52" s="0" t="str">
-        <f aca="false">IF($A52="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(51,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A52="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(51,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(52,BOM!$O$2:$O$108,0)),"",52)</f>
+        <f aca="false">IF(ISNA(MATCH(52,BOM!$O$2:$O$110,0)),"",52)</f>
         <v>52</v>
       </c>
       <c r="B53" s="0" t="str">
-        <f aca="false">IF($A53="","",INDEX(BOM!$B$2:$B$108,MATCH(52,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A53="","",INDEX(BOM!$B$2:$B$110,MATCH(52,BOM!$O$2:$O$110,0)))</f>
         <v>UCP205 pillow block bearings 25 mm, 2-pack</v>
       </c>
       <c r="C53" s="0" t="n">
-        <f aca="false">IF($A53="","",INDEX(BOM!$G$2:$G$108,MATCH(52,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A53="","",INDEX(BOM!$G$2:$G$110,MATCH(52,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D53" s="9" t="n">
-        <f aca="false">IF($A53="","",INDEX(BOM!$H$2:$H$108,MATCH(52,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A53="","",INDEX(BOM!$H$2:$H$110,MATCH(52,BOM!$O$2:$O$110,0)))</f>
         <v>37.75</v>
       </c>
       <c r="E53" s="9" t="n">
-        <f aca="false">IF($A53="","",INDEX(BOM!$I$2:$I$108,MATCH(52,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A53="","",INDEX(BOM!$I$2:$I$110,MATCH(52,BOM!$O$2:$O$110,0)))</f>
         <v>37.75</v>
       </c>
       <c r="F53" s="0" t="str">
-        <f aca="false">IF($A53="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(52,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(52,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A53="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(52,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(52,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G53" s="0" t="str">
-        <f aca="false">IF($A53="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(52,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A53="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(52,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(53,BOM!$O$2:$O$108,0)),"",53)</f>
+        <f aca="false">IF(ISNA(MATCH(53,BOM!$O$2:$O$110,0)),"",53)</f>
         <v>53</v>
       </c>
       <c r="B54" s="0" t="str">
-        <f aca="false">IF($A54="","",INDEX(BOM!$B$2:$B$108,MATCH(53,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A54="","",INDEX(BOM!$B$2:$B$110,MATCH(53,BOM!$O$2:$O$110,0)))</f>
         <v>UCF205 4-bolt flange bearing 25 mm</v>
       </c>
       <c r="C54" s="0" t="n">
-        <f aca="false">IF($A54="","",INDEX(BOM!$G$2:$G$108,MATCH(53,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A54="","",INDEX(BOM!$G$2:$G$110,MATCH(53,BOM!$O$2:$O$110,0)))</f>
         <v>2</v>
       </c>
       <c r="D54" s="9" t="n">
-        <f aca="false">IF($A54="","",INDEX(BOM!$H$2:$H$108,MATCH(53,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A54="","",INDEX(BOM!$H$2:$H$110,MATCH(53,BOM!$O$2:$O$110,0)))</f>
         <v>20.79</v>
       </c>
       <c r="E54" s="9" t="n">
-        <f aca="false">IF($A54="","",INDEX(BOM!$I$2:$I$108,MATCH(53,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A54="","",INDEX(BOM!$I$2:$I$110,MATCH(53,BOM!$O$2:$O$110,0)))</f>
         <v>41.58</v>
       </c>
       <c r="F54" s="0" t="str">
-        <f aca="false">IF($A54="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(53,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(53,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A54="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(53,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(53,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G54" s="0" t="str">
-        <f aca="false">IF($A54="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(53,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A54="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(53,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(54,BOM!$O$2:$O$108,0)),"",54)</f>
+        <f aca="false">IF(ISNA(MATCH(54,BOM!$O$2:$O$110,0)),"",54)</f>
         <v>54</v>
       </c>
       <c r="B55" s="0" t="str">
-        <f aca="false">IF($A55="","",INDEX(BOM!$B$2:$B$108,MATCH(54,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A55="","",INDEX(BOM!$B$2:$B$110,MATCH(54,BOM!$O$2:$O$110,0)))</f>
         <v>25 mm steel double-split shaft collars, 2 pcs</v>
       </c>
       <c r="C55" s="0" t="n">
-        <f aca="false">IF($A55="","",INDEX(BOM!$G$2:$G$108,MATCH(54,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A55="","",INDEX(BOM!$G$2:$G$110,MATCH(54,BOM!$O$2:$O$110,0)))</f>
         <v>2</v>
       </c>
       <c r="D55" s="9" t="n">
-        <f aca="false">IF($A55="","",INDEX(BOM!$H$2:$H$108,MATCH(54,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A55="","",INDEX(BOM!$H$2:$H$110,MATCH(54,BOM!$O$2:$O$110,0)))</f>
         <v>17.49</v>
       </c>
       <c r="E55" s="9" t="n">
-        <f aca="false">IF($A55="","",INDEX(BOM!$I$2:$I$108,MATCH(54,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A55="","",INDEX(BOM!$I$2:$I$110,MATCH(54,BOM!$O$2:$O$110,0)))</f>
         <v>34.98</v>
       </c>
       <c r="F55" s="0" t="str">
-        <f aca="false">IF($A55="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(54,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(54,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A55="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(54,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(54,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G55" s="0" t="str">
-        <f aca="false">IF($A55="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(54,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A55="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(54,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(55,BOM!$O$2:$O$108,0)),"",55)</f>
+        <f aca="false">IF(ISNA(MATCH(55,BOM!$O$2:$O$110,0)),"",55)</f>
         <v>55</v>
       </c>
       <c r="B56" s="0" t="str">
-        <f aca="false">IF($A56="","",INDEX(BOM!$B$2:$B$108,MATCH(55,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A56="","",INDEX(BOM!$B$2:$B$110,MATCH(55,BOM!$O$2:$O$110,0)))</f>
         <v>Cradle linear actuator 12 V, 10" (254 mm) stroke, 1500 N (330 lbf), self-locking</v>
       </c>
       <c r="C56" s="0" t="n">
-        <f aca="false">IF($A56="","",INDEX(BOM!$G$2:$G$108,MATCH(55,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A56="","",INDEX(BOM!$G$2:$G$110,MATCH(55,BOM!$O$2:$O$110,0)))</f>
         <v>2</v>
       </c>
       <c r="D56" s="9" t="n">
-        <f aca="false">IF($A56="","",INDEX(BOM!$H$2:$H$108,MATCH(55,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A56="","",INDEX(BOM!$H$2:$H$110,MATCH(55,BOM!$O$2:$O$110,0)))</f>
         <v>62.33</v>
       </c>
       <c r="E56" s="9" t="n">
-        <f aca="false">IF($A56="","",INDEX(BOM!$I$2:$I$108,MATCH(55,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A56="","",INDEX(BOM!$I$2:$I$110,MATCH(55,BOM!$O$2:$O$110,0)))</f>
         <v>124.66</v>
       </c>
       <c r="F56" s="0" t="str">
-        <f aca="false">IF($A56="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(55,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(55,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A56="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(55,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(55,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G56" s="0" t="str">
-        <f aca="false">IF($A56="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(55,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A56="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(55,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(56,BOM!$O$2:$O$108,0)),"",56)</f>
+        <f aca="false">IF(ISNA(MATCH(56,BOM!$O$2:$O$110,0)),"",56)</f>
         <v>56</v>
       </c>
       <c r="B57" s="0" t="str">
-        <f aca="false">IF($A57="","",INDEX(BOM!$B$2:$B$108,MATCH(56,BOM!$O$2:$O$108,0)))</f>
-        <v>Pod linear actuator 12 V, 12" (305 mm) stroke, 1000 N (225 lbf), self-locking</v>
+        <f aca="false">IF($A57="","",INDEX(BOM!$B$2:$B$110,MATCH(56,BOM!$O$2:$O$110,0)))</f>
+        <v>Pod linear actuator 12 V, 12" (300 mm) stroke, 1500 N (330 lbf), self-locking - ONE (left casing)</v>
       </c>
       <c r="C57" s="0" t="n">
-        <f aca="false">IF($A57="","",INDEX(BOM!$G$2:$G$108,MATCH(56,BOM!$O$2:$O$108,0)))</f>
-        <v>2</v>
+        <f aca="false">IF($A57="","",INDEX(BOM!$G$2:$G$110,MATCH(56,BOM!$O$2:$O$110,0)))</f>
+        <v>1</v>
       </c>
       <c r="D57" s="9" t="n">
-        <f aca="false">IF($A57="","",INDEX(BOM!$H$2:$H$108,MATCH(56,BOM!$O$2:$O$108,0)))</f>
-        <v>48.49</v>
+        <f aca="false">IF($A57="","",INDEX(BOM!$H$2:$H$110,MATCH(56,BOM!$O$2:$O$110,0)))</f>
+        <v>67.82</v>
       </c>
       <c r="E57" s="9" t="n">
-        <f aca="false">IF($A57="","",INDEX(BOM!$I$2:$I$108,MATCH(56,BOM!$O$2:$O$108,0)))</f>
-        <v>96.98</v>
+        <f aca="false">IF($A57="","",INDEX(BOM!$I$2:$I$110,MATCH(56,BOM!$O$2:$O$110,0)))</f>
+        <v>67.82</v>
       </c>
       <c r="F57" s="0" t="str">
-        <f aca="false">IF($A57="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(56,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(56,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A57="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(56,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(56,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G57" s="0" t="str">
-        <f aca="false">IF($A57="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(56,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A57="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(56,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(57,BOM!$O$2:$O$108,0)),"",57)</f>
+        <f aca="false">IF(ISNA(MATCH(57,BOM!$O$2:$O$110,0)),"",57)</f>
         <v>57</v>
       </c>
       <c r="B58" s="0" t="str">
-        <f aca="false">IF($A58="","",INDEX(BOM!$B$2:$B$108,MATCH(57,BOM!$O$2:$O$108,0)))</f>
-        <v>Gas struts (pair), 10" (254 mm) extended, 120 lb / 534 N, 10 mm ball-stud ends</v>
+        <f aca="false">IF($A58="","",INDEX(BOM!$B$2:$B$110,MATCH(57,BOM!$O$2:$O$110,0)))</f>
+        <v>Gas struts (pair), ~250 mm extended, ~1050 N (235 lbf) each, M8 eye ends</v>
       </c>
       <c r="C58" s="0" t="n">
-        <f aca="false">IF($A58="","",INDEX(BOM!$G$2:$G$108,MATCH(57,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A58="","",INDEX(BOM!$G$2:$G$110,MATCH(57,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D58" s="9" t="n">
-        <f aca="false">IF($A58="","",INDEX(BOM!$H$2:$H$108,MATCH(57,BOM!$O$2:$O$108,0)))</f>
-        <v>30.09</v>
+        <f aca="false">IF($A58="","",INDEX(BOM!$H$2:$H$110,MATCH(57,BOM!$O$2:$O$110,0)))</f>
+        <v>60</v>
       </c>
       <c r="E58" s="9" t="n">
-        <f aca="false">IF($A58="","",INDEX(BOM!$I$2:$I$108,MATCH(57,BOM!$O$2:$O$108,0)))</f>
-        <v>30.09</v>
+        <f aca="false">IF($A58="","",INDEX(BOM!$I$2:$I$110,MATCH(57,BOM!$O$2:$O$110,0)))</f>
+        <v>60</v>
       </c>
       <c r="F58" s="0" t="str">
-        <f aca="false">IF($A58="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(57,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(57,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
-        <v>open on amazon.ca</v>
+        <f aca="false">IF($A58="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(57,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(57,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
+        <v/>
       </c>
       <c r="G58" s="0" t="str">
-        <f aca="false">IF($A58="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(57,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A58="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(57,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(58,BOM!$O$2:$O$108,0)),"",58)</f>
+        <f aca="false">IF(ISNA(MATCH(58,BOM!$O$2:$O$110,0)),"",58)</f>
         <v>58</v>
       </c>
       <c r="B59" s="0" t="str">
-        <f aca="false">IF($A59="","",INDEX(BOM!$B$2:$B$108,MATCH(58,BOM!$O$2:$O$108,0)))</f>
-        <v>10 mm ball-stud gas strut mounting brackets</v>
+        <f aca="false">IF($A59="","",INDEX(BOM!$B$2:$B$110,MATCH(58,BOM!$O$2:$O$110,0)))</f>
+        <v>Spring-loaded steel pawl (barrel bolt / gate latch)</v>
       </c>
       <c r="C59" s="0" t="n">
-        <f aca="false">IF($A59="","",INDEX(BOM!$G$2:$G$108,MATCH(58,BOM!$O$2:$O$108,0)))</f>
-        <v>1</v>
+        <f aca="false">IF($A59="","",INDEX(BOM!$G$2:$G$110,MATCH(58,BOM!$O$2:$O$110,0)))</f>
+        <v>2</v>
       </c>
       <c r="D59" s="9" t="n">
-        <f aca="false">IF($A59="","",INDEX(BOM!$H$2:$H$108,MATCH(58,BOM!$O$2:$O$108,0)))</f>
-        <v>21.99</v>
+        <f aca="false">IF($A59="","",INDEX(BOM!$H$2:$H$110,MATCH(58,BOM!$O$2:$O$110,0)))</f>
+        <v>16.99</v>
       </c>
       <c r="E59" s="9" t="n">
-        <f aca="false">IF($A59="","",INDEX(BOM!$I$2:$I$108,MATCH(58,BOM!$O$2:$O$108,0)))</f>
-        <v>21.99</v>
+        <f aca="false">IF($A59="","",INDEX(BOM!$I$2:$I$110,MATCH(58,BOM!$O$2:$O$110,0)))</f>
+        <v>33.98</v>
       </c>
       <c r="F59" s="0" t="str">
-        <f aca="false">IF($A59="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(58,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(58,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A59="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(58,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(58,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G59" s="0" t="str">
-        <f aca="false">IF($A59="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(58,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A59="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(58,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(59,BOM!$O$2:$O$108,0)),"",59)</f>
+        <f aca="false">IF(ISNA(MATCH(59,BOM!$O$2:$O$110,0)),"",59)</f>
         <v>59</v>
       </c>
       <c r="B60" s="0" t="str">
-        <f aca="false">IF($A60="","",INDEX(BOM!$B$2:$B$108,MATCH(59,BOM!$O$2:$O$108,0)))</f>
-        <v>Spring-loaded steel pawl (barrel bolt / gate latch)</v>
+        <f aca="false">IF($A60="","",INDEX(BOM!$B$2:$B$110,MATCH(59,BOM!$O$2:$O$110,0)))</f>
+        <v>Bowden cables + levers (bike brake lever set)</v>
       </c>
       <c r="C60" s="0" t="n">
-        <f aca="false">IF($A60="","",INDEX(BOM!$G$2:$G$108,MATCH(59,BOM!$O$2:$O$108,0)))</f>
-        <v>2</v>
+        <f aca="false">IF($A60="","",INDEX(BOM!$G$2:$G$110,MATCH(59,BOM!$O$2:$O$110,0)))</f>
+        <v>1</v>
       </c>
       <c r="D60" s="9" t="n">
-        <f aca="false">IF($A60="","",INDEX(BOM!$H$2:$H$108,MATCH(59,BOM!$O$2:$O$108,0)))</f>
-        <v>16.99</v>
+        <f aca="false">IF($A60="","",INDEX(BOM!$H$2:$H$110,MATCH(59,BOM!$O$2:$O$110,0)))</f>
+        <v>23.99</v>
       </c>
       <c r="E60" s="9" t="n">
-        <f aca="false">IF($A60="","",INDEX(BOM!$I$2:$I$108,MATCH(59,BOM!$O$2:$O$108,0)))</f>
-        <v>33.98</v>
+        <f aca="false">IF($A60="","",INDEX(BOM!$I$2:$I$110,MATCH(59,BOM!$O$2:$O$110,0)))</f>
+        <v>23.99</v>
       </c>
       <c r="F60" s="0" t="str">
-        <f aca="false">IF($A60="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(59,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(59,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A60="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(59,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(59,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G60" s="0" t="str">
-        <f aca="false">IF($A60="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(59,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A60="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(59,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(60,BOM!$O$2:$O$108,0)),"",60)</f>
+        <f aca="false">IF(ISNA(MATCH(60,BOM!$O$2:$O$110,0)),"",60)</f>
         <v>60</v>
       </c>
       <c r="B61" s="0" t="str">
-        <f aca="false">IF($A61="","",INDEX(BOM!$B$2:$B$108,MATCH(60,BOM!$O$2:$O$108,0)))</f>
-        <v>Bowden cables + levers (bike brake lever set)</v>
+        <f aca="false">IF($A61="","",INDEX(BOM!$B$2:$B$110,MATCH(60,BOM!$O$2:$O$110,0)))</f>
+        <v>Rubber bumper / stop pads with screws (assorted)</v>
       </c>
       <c r="C61" s="0" t="n">
-        <f aca="false">IF($A61="","",INDEX(BOM!$G$2:$G$108,MATCH(60,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A61="","",INDEX(BOM!$G$2:$G$110,MATCH(60,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D61" s="9" t="n">
-        <f aca="false">IF($A61="","",INDEX(BOM!$H$2:$H$108,MATCH(60,BOM!$O$2:$O$108,0)))</f>
-        <v>23.99</v>
+        <f aca="false">IF($A61="","",INDEX(BOM!$H$2:$H$110,MATCH(60,BOM!$O$2:$O$110,0)))</f>
+        <v>17.99</v>
       </c>
       <c r="E61" s="9" t="n">
-        <f aca="false">IF($A61="","",INDEX(BOM!$I$2:$I$108,MATCH(60,BOM!$O$2:$O$108,0)))</f>
-        <v>23.99</v>
+        <f aca="false">IF($A61="","",INDEX(BOM!$I$2:$I$110,MATCH(60,BOM!$O$2:$O$110,0)))</f>
+        <v>17.99</v>
       </c>
       <c r="F61" s="0" t="str">
-        <f aca="false">IF($A61="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(60,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(60,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A61="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(60,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(60,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G61" s="0" t="str">
-        <f aca="false">IF($A61="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(60,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A61="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(60,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(61,BOM!$O$2:$O$108,0)),"",61)</f>
+        <f aca="false">IF(ISNA(MATCH(61,BOM!$O$2:$O$110,0)),"",61)</f>
         <v>61</v>
       </c>
       <c r="B62" s="0" t="str">
-        <f aca="false">IF($A62="","",INDEX(BOM!$B$2:$B$108,MATCH(61,BOM!$O$2:$O$108,0)))</f>
-        <v>Rubber bumper / stop pads with screws (assorted)</v>
+        <f aca="false">IF($A62="","",INDEX(BOM!$B$2:$B$110,MATCH(61,BOM!$O$2:$O$110,0)))</f>
+        <v>12 V 20 A (240 W) enclosed power supply</v>
       </c>
       <c r="C62" s="0" t="n">
-        <f aca="false">IF($A62="","",INDEX(BOM!$G$2:$G$108,MATCH(61,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A62="","",INDEX(BOM!$G$2:$G$110,MATCH(61,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D62" s="9" t="n">
-        <f aca="false">IF($A62="","",INDEX(BOM!$H$2:$H$108,MATCH(61,BOM!$O$2:$O$108,0)))</f>
-        <v>17.99</v>
+        <f aca="false">IF($A62="","",INDEX(BOM!$H$2:$H$110,MATCH(61,BOM!$O$2:$O$110,0)))</f>
+        <v>33.99</v>
       </c>
       <c r="E62" s="9" t="n">
-        <f aca="false">IF($A62="","",INDEX(BOM!$I$2:$I$108,MATCH(61,BOM!$O$2:$O$108,0)))</f>
-        <v>17.99</v>
+        <f aca="false">IF($A62="","",INDEX(BOM!$I$2:$I$110,MATCH(61,BOM!$O$2:$O$110,0)))</f>
+        <v>33.99</v>
       </c>
       <c r="F62" s="0" t="str">
-        <f aca="false">IF($A62="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(61,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(61,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A62="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(61,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(61,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G62" s="0" t="str">
-        <f aca="false">IF($A62="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(61,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A62="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(61,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(62,BOM!$O$2:$O$108,0)),"",62)</f>
+        <f aca="false">IF(ISNA(MATCH(62,BOM!$O$2:$O$110,0)),"",62)</f>
         <v>62</v>
       </c>
       <c r="B63" s="0" t="str">
-        <f aca="false">IF($A63="","",INDEX(BOM!$B$2:$B$108,MATCH(62,BOM!$O$2:$O$108,0)))</f>
-        <v>12 V 20 A (240 W) enclosed power supply</v>
+        <f aca="false">IF($A63="","",INDEX(BOM!$B$2:$B$110,MATCH(62,BOM!$O$2:$O$110,0)))</f>
+        <v>Inline ATC fuse holder 12 AWG with 20/30/40 A fuses</v>
       </c>
       <c r="C63" s="0" t="n">
-        <f aca="false">IF($A63="","",INDEX(BOM!$G$2:$G$108,MATCH(62,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A63="","",INDEX(BOM!$G$2:$G$110,MATCH(62,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D63" s="9" t="n">
-        <f aca="false">IF($A63="","",INDEX(BOM!$H$2:$H$108,MATCH(62,BOM!$O$2:$O$108,0)))</f>
-        <v>33.99</v>
+        <f aca="false">IF($A63="","",INDEX(BOM!$H$2:$H$110,MATCH(62,BOM!$O$2:$O$110,0)))</f>
+        <v>18.99</v>
       </c>
       <c r="E63" s="9" t="n">
-        <f aca="false">IF($A63="","",INDEX(BOM!$I$2:$I$108,MATCH(62,BOM!$O$2:$O$108,0)))</f>
-        <v>33.99</v>
+        <f aca="false">IF($A63="","",INDEX(BOM!$I$2:$I$110,MATCH(62,BOM!$O$2:$O$110,0)))</f>
+        <v>18.99</v>
       </c>
       <c r="F63" s="0" t="str">
-        <f aca="false">IF($A63="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(62,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(62,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A63="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(62,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(62,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G63" s="0" t="str">
-        <f aca="false">IF($A63="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(62,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A63="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(62,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(63,BOM!$O$2:$O$108,0)),"",63)</f>
+        <f aca="false">IF(ISNA(MATCH(63,BOM!$O$2:$O$110,0)),"",63)</f>
         <v>63</v>
       </c>
       <c r="B64" s="0" t="str">
-        <f aca="false">IF($A64="","",INDEX(BOM!$B$2:$B$108,MATCH(63,BOM!$O$2:$O$108,0)))</f>
-        <v>Inline ATC fuse holder 12 AWG with 20/30/40 A fuses</v>
+        <f aca="false">IF($A64="","",INDEX(BOM!$B$2:$B$110,MATCH(63,BOM!$O$2:$O$110,0)))</f>
+        <v>19 mm key switch, 2 position (MOTION key) - drives a 30 A relay</v>
       </c>
       <c r="C64" s="0" t="n">
-        <f aca="false">IF($A64="","",INDEX(BOM!$G$2:$G$108,MATCH(63,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A64="","",INDEX(BOM!$G$2:$G$110,MATCH(63,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D64" s="9" t="n">
-        <f aca="false">IF($A64="","",INDEX(BOM!$H$2:$H$108,MATCH(63,BOM!$O$2:$O$108,0)))</f>
-        <v>18.99</v>
+        <f aca="false">IF($A64="","",INDEX(BOM!$H$2:$H$110,MATCH(63,BOM!$O$2:$O$110,0)))</f>
+        <v>26.11</v>
       </c>
       <c r="E64" s="9" t="n">
-        <f aca="false">IF($A64="","",INDEX(BOM!$I$2:$I$108,MATCH(63,BOM!$O$2:$O$108,0)))</f>
-        <v>18.99</v>
+        <f aca="false">IF($A64="","",INDEX(BOM!$I$2:$I$110,MATCH(63,BOM!$O$2:$O$110,0)))</f>
+        <v>26.11</v>
       </c>
       <c r="F64" s="0" t="str">
-        <f aca="false">IF($A64="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(63,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(63,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A64="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(63,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(63,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G64" s="0" t="str">
-        <f aca="false">IF($A64="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(63,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A64="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(63,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(64,BOM!$O$2:$O$108,0)),"",64)</f>
+        <f aca="false">IF(ISNA(MATCH(64,BOM!$O$2:$O$110,0)),"",64)</f>
         <v>64</v>
       </c>
       <c r="B65" s="0" t="str">
-        <f aca="false">IF($A65="","",INDEX(BOM!$B$2:$B$108,MATCH(64,BOM!$O$2:$O$108,0)))</f>
-        <v>19 mm key switch, 2 position (MOTION key) - drives a 30 A relay</v>
+        <f aca="false">IF($A65="","",INDEX(BOM!$B$2:$B$110,MATCH(64,BOM!$O$2:$O$110,0)))</f>
+        <v>22 mm mushroom E-stop, NC, latching, twist release</v>
       </c>
       <c r="C65" s="0" t="n">
-        <f aca="false">IF($A65="","",INDEX(BOM!$G$2:$G$108,MATCH(64,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A65="","",INDEX(BOM!$G$2:$G$110,MATCH(64,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D65" s="9" t="n">
-        <f aca="false">IF($A65="","",INDEX(BOM!$H$2:$H$108,MATCH(64,BOM!$O$2:$O$108,0)))</f>
-        <v>26.11</v>
+        <f aca="false">IF($A65="","",INDEX(BOM!$H$2:$H$110,MATCH(64,BOM!$O$2:$O$110,0)))</f>
+        <v>16.24</v>
       </c>
       <c r="E65" s="9" t="n">
-        <f aca="false">IF($A65="","",INDEX(BOM!$I$2:$I$108,MATCH(64,BOM!$O$2:$O$108,0)))</f>
-        <v>26.11</v>
+        <f aca="false">IF($A65="","",INDEX(BOM!$I$2:$I$110,MATCH(64,BOM!$O$2:$O$110,0)))</f>
+        <v>16.24</v>
       </c>
       <c r="F65" s="0" t="str">
-        <f aca="false">IF($A65="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(64,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(64,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A65="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(64,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(64,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G65" s="0" t="str">
-        <f aca="false">IF($A65="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(64,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A65="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(64,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(65,BOM!$O$2:$O$108,0)),"",65)</f>
+        <f aca="false">IF(ISNA(MATCH(65,BOM!$O$2:$O$110,0)),"",65)</f>
         <v>65</v>
       </c>
       <c r="B66" s="0" t="str">
-        <f aca="false">IF($A66="","",INDEX(BOM!$B$2:$B$108,MATCH(65,BOM!$O$2:$O$108,0)))</f>
-        <v>22 mm mushroom E-stop, NC, latching, twist release</v>
+        <f aca="false">IF($A66="","",INDEX(BOM!$B$2:$B$110,MATCH(65,BOM!$O$2:$O$110,0)))</f>
+        <v>DPDT (ON)-OFF-(ON) momentary toggle, 12 mm bushing</v>
       </c>
       <c r="C66" s="0" t="n">
-        <f aca="false">IF($A66="","",INDEX(BOM!$G$2:$G$108,MATCH(65,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A66="","",INDEX(BOM!$G$2:$G$110,MATCH(65,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D66" s="9" t="n">
-        <f aca="false">IF($A66="","",INDEX(BOM!$H$2:$H$108,MATCH(65,BOM!$O$2:$O$108,0)))</f>
-        <v>16.24</v>
+        <f aca="false">IF($A66="","",INDEX(BOM!$H$2:$H$110,MATCH(65,BOM!$O$2:$O$110,0)))</f>
+        <v>13.98</v>
       </c>
       <c r="E66" s="9" t="n">
-        <f aca="false">IF($A66="","",INDEX(BOM!$I$2:$I$108,MATCH(65,BOM!$O$2:$O$108,0)))</f>
-        <v>16.24</v>
+        <f aca="false">IF($A66="","",INDEX(BOM!$I$2:$I$110,MATCH(65,BOM!$O$2:$O$110,0)))</f>
+        <v>13.98</v>
       </c>
       <c r="F66" s="0" t="str">
-        <f aca="false">IF($A66="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(65,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(65,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A66="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(65,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(65,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G66" s="0" t="str">
-        <f aca="false">IF($A66="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(65,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A66="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(65,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(66,BOM!$O$2:$O$108,0)),"",66)</f>
+        <f aca="false">IF(ISNA(MATCH(66,BOM!$O$2:$O$110,0)),"",66)</f>
         <v>66</v>
       </c>
       <c r="B67" s="0" t="str">
-        <f aca="false">IF($A67="","",INDEX(BOM!$B$2:$B$108,MATCH(66,BOM!$O$2:$O$108,0)))</f>
-        <v>DPDT (ON)-OFF-(ON) momentary toggle, 12 mm bushing</v>
+        <f aca="false">IF($A67="","",INDEX(BOM!$B$2:$B$110,MATCH(66,BOM!$O$2:$O$110,0)))</f>
+        <v>12 V 30/40 A automotive relays SPDT 5-pin, 10 pcs</v>
       </c>
       <c r="C67" s="0" t="n">
-        <f aca="false">IF($A67="","",INDEX(BOM!$G$2:$G$108,MATCH(66,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A67="","",INDEX(BOM!$G$2:$G$110,MATCH(66,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D67" s="9" t="n">
-        <f aca="false">IF($A67="","",INDEX(BOM!$H$2:$H$108,MATCH(66,BOM!$O$2:$O$108,0)))</f>
-        <v>13.98</v>
+        <f aca="false">IF($A67="","",INDEX(BOM!$H$2:$H$110,MATCH(66,BOM!$O$2:$O$110,0)))</f>
+        <v>22.99</v>
       </c>
       <c r="E67" s="9" t="n">
-        <f aca="false">IF($A67="","",INDEX(BOM!$I$2:$I$108,MATCH(66,BOM!$O$2:$O$108,0)))</f>
-        <v>13.98</v>
+        <f aca="false">IF($A67="","",INDEX(BOM!$I$2:$I$110,MATCH(66,BOM!$O$2:$O$110,0)))</f>
+        <v>22.99</v>
       </c>
       <c r="F67" s="0" t="str">
-        <f aca="false">IF($A67="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(66,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(66,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A67="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(66,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(66,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G67" s="0" t="str">
-        <f aca="false">IF($A67="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(66,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A67="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(66,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(67,BOM!$O$2:$O$108,0)),"",67)</f>
+        <f aca="false">IF(ISNA(MATCH(67,BOM!$O$2:$O$110,0)),"",67)</f>
         <v>67</v>
       </c>
       <c r="B68" s="0" t="str">
-        <f aca="false">IF($A68="","",INDEX(BOM!$B$2:$B$108,MATCH(67,BOM!$O$2:$O$108,0)))</f>
-        <v>12 V 30/40 A automotive relays SPDT 5-pin, 10 pcs</v>
+        <f aca="false">IF($A68="","",INDEX(BOM!$B$2:$B$110,MATCH(67,BOM!$O$2:$O$110,0)))</f>
+        <v>V-15 roller-lever micro switches 15 A, 10 pcs</v>
       </c>
       <c r="C68" s="0" t="n">
-        <f aca="false">IF($A68="","",INDEX(BOM!$G$2:$G$108,MATCH(67,BOM!$O$2:$O$108,0)))</f>
-        <v>1</v>
+        <f aca="false">IF($A68="","",INDEX(BOM!$G$2:$G$110,MATCH(67,BOM!$O$2:$O$110,0)))</f>
+        <v>2</v>
       </c>
       <c r="D68" s="9" t="n">
-        <f aca="false">IF($A68="","",INDEX(BOM!$H$2:$H$108,MATCH(67,BOM!$O$2:$O$108,0)))</f>
-        <v>22.99</v>
+        <f aca="false">IF($A68="","",INDEX(BOM!$H$2:$H$110,MATCH(67,BOM!$O$2:$O$110,0)))</f>
+        <v>16.69</v>
       </c>
       <c r="E68" s="9" t="n">
-        <f aca="false">IF($A68="","",INDEX(BOM!$I$2:$I$108,MATCH(67,BOM!$O$2:$O$108,0)))</f>
-        <v>22.99</v>
+        <f aca="false">IF($A68="","",INDEX(BOM!$I$2:$I$110,MATCH(67,BOM!$O$2:$O$110,0)))</f>
+        <v>33.38</v>
       </c>
       <c r="F68" s="0" t="str">
-        <f aca="false">IF($A68="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(67,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(67,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A68="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(67,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(67,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G68" s="0" t="str">
-        <f aca="false">IF($A68="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(67,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A68="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(67,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(68,BOM!$O$2:$O$108,0)),"",68)</f>
+        <f aca="false">IF(ISNA(MATCH(68,BOM!$O$2:$O$110,0)),"",68)</f>
         <v>68</v>
       </c>
       <c r="B69" s="0" t="str">
-        <f aca="false">IF($A69="","",INDEX(BOM!$B$2:$B$108,MATCH(68,BOM!$O$2:$O$108,0)))</f>
-        <v>V-15 roller-lever micro switches 15 A, 10 pcs</v>
+        <f aca="false">IF($A69="","",INDEX(BOM!$B$2:$B$110,MATCH(68,BOM!$O$2:$O$110,0)))</f>
+        <v>6A10 rectifier diodes (6 A, 1000 V), 20 pcs</v>
       </c>
       <c r="C69" s="0" t="n">
-        <f aca="false">IF($A69="","",INDEX(BOM!$G$2:$G$108,MATCH(68,BOM!$O$2:$O$108,0)))</f>
-        <v>2</v>
+        <f aca="false">IF($A69="","",INDEX(BOM!$G$2:$G$110,MATCH(68,BOM!$O$2:$O$110,0)))</f>
+        <v>1</v>
       </c>
       <c r="D69" s="9" t="n">
-        <f aca="false">IF($A69="","",INDEX(BOM!$H$2:$H$108,MATCH(68,BOM!$O$2:$O$108,0)))</f>
-        <v>16.69</v>
+        <f aca="false">IF($A69="","",INDEX(BOM!$H$2:$H$110,MATCH(68,BOM!$O$2:$O$110,0)))</f>
+        <v>8.99</v>
       </c>
       <c r="E69" s="9" t="n">
-        <f aca="false">IF($A69="","",INDEX(BOM!$I$2:$I$108,MATCH(68,BOM!$O$2:$O$108,0)))</f>
-        <v>33.38</v>
+        <f aca="false">IF($A69="","",INDEX(BOM!$I$2:$I$110,MATCH(68,BOM!$O$2:$O$110,0)))</f>
+        <v>8.99</v>
       </c>
       <c r="F69" s="0" t="str">
-        <f aca="false">IF($A69="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(68,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(68,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A69="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(68,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(68,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G69" s="0" t="str">
-        <f aca="false">IF($A69="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(68,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A69="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(68,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(69,BOM!$O$2:$O$108,0)),"",69)</f>
+        <f aca="false">IF(ISNA(MATCH(69,BOM!$O$2:$O$110,0)),"",69)</f>
         <v>69</v>
       </c>
       <c r="B70" s="0" t="str">
-        <f aca="false">IF($A70="","",INDEX(BOM!$B$2:$B$108,MATCH(69,BOM!$O$2:$O$108,0)))</f>
-        <v>6A10 rectifier diodes (6 A, 1000 V), 20 pcs</v>
+        <f aca="false">IF($A70="","",INDEX(BOM!$B$2:$B$110,MATCH(69,BOM!$O$2:$O$110,0)))</f>
+        <v>14 AWG red/black 2-conductor wire, 15 m (50 ft)</v>
       </c>
       <c r="C70" s="0" t="n">
-        <f aca="false">IF($A70="","",INDEX(BOM!$G$2:$G$108,MATCH(69,BOM!$O$2:$O$108,0)))</f>
-        <v>1</v>
+        <f aca="false">IF($A70="","",INDEX(BOM!$G$2:$G$110,MATCH(69,BOM!$O$2:$O$110,0)))</f>
+        <v>2</v>
       </c>
       <c r="D70" s="9" t="n">
-        <f aca="false">IF($A70="","",INDEX(BOM!$H$2:$H$108,MATCH(69,BOM!$O$2:$O$108,0)))</f>
-        <v>8.99</v>
+        <f aca="false">IF($A70="","",INDEX(BOM!$H$2:$H$110,MATCH(69,BOM!$O$2:$O$110,0)))</f>
+        <v>17.09</v>
       </c>
       <c r="E70" s="9" t="n">
-        <f aca="false">IF($A70="","",INDEX(BOM!$I$2:$I$108,MATCH(69,BOM!$O$2:$O$108,0)))</f>
-        <v>8.99</v>
+        <f aca="false">IF($A70="","",INDEX(BOM!$I$2:$I$110,MATCH(69,BOM!$O$2:$O$110,0)))</f>
+        <v>34.18</v>
       </c>
       <c r="F70" s="0" t="str">
-        <f aca="false">IF($A70="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(69,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(69,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A70="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(69,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(69,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G70" s="0" t="str">
-        <f aca="false">IF($A70="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(69,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A70="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(69,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(70,BOM!$O$2:$O$108,0)),"",70)</f>
+        <f aca="false">IF(ISNA(MATCH(70,BOM!$O$2:$O$110,0)),"",70)</f>
         <v>70</v>
       </c>
       <c r="B71" s="0" t="str">
-        <f aca="false">IF($A71="","",INDEX(BOM!$B$2:$B$108,MATCH(70,BOM!$O$2:$O$108,0)))</f>
-        <v>14 AWG red/black 2-conductor wire, 15 m (50 ft)</v>
+        <f aca="false">IF($A71="","",INDEX(BOM!$B$2:$B$110,MATCH(70,BOM!$O$2:$O$110,0)))</f>
+        <v>Heat-shrink ring terminal kit, 260 pcs (22-10 AWG)</v>
       </c>
       <c r="C71" s="0" t="n">
-        <f aca="false">IF($A71="","",INDEX(BOM!$G$2:$G$108,MATCH(70,BOM!$O$2:$O$108,0)))</f>
-        <v>2</v>
+        <f aca="false">IF($A71="","",INDEX(BOM!$G$2:$G$110,MATCH(70,BOM!$O$2:$O$110,0)))</f>
+        <v>1</v>
       </c>
       <c r="D71" s="9" t="n">
-        <f aca="false">IF($A71="","",INDEX(BOM!$H$2:$H$108,MATCH(70,BOM!$O$2:$O$108,0)))</f>
-        <v>17.09</v>
+        <f aca="false">IF($A71="","",INDEX(BOM!$H$2:$H$110,MATCH(70,BOM!$O$2:$O$110,0)))</f>
+        <v>29.99</v>
       </c>
       <c r="E71" s="9" t="n">
-        <f aca="false">IF($A71="","",INDEX(BOM!$I$2:$I$108,MATCH(70,BOM!$O$2:$O$108,0)))</f>
-        <v>34.18</v>
+        <f aca="false">IF($A71="","",INDEX(BOM!$I$2:$I$110,MATCH(70,BOM!$O$2:$O$110,0)))</f>
+        <v>29.99</v>
       </c>
       <c r="F71" s="0" t="str">
-        <f aca="false">IF($A71="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(70,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(70,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A71="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(70,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(70,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G71" s="0" t="str">
-        <f aca="false">IF($A71="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(70,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A71="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(70,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(71,BOM!$O$2:$O$108,0)),"",71)</f>
+        <f aca="false">IF(ISNA(MATCH(71,BOM!$O$2:$O$110,0)),"",71)</f>
         <v>71</v>
       </c>
       <c r="B72" s="0" t="str">
-        <f aca="false">IF($A72="","",INDEX(BOM!$B$2:$B$108,MATCH(71,BOM!$O$2:$O$108,0)))</f>
-        <v>Heat-shrink ring terminal kit, 260 pcs (22-10 AWG)</v>
+        <f aca="false">IF($A72="","",INDEX(BOM!$B$2:$B$110,MATCH(71,BOM!$O$2:$O$110,0)))</f>
+        <v>Strip brush 25 mm in aluminium holder, ~5 m</v>
       </c>
       <c r="C72" s="0" t="n">
-        <f aca="false">IF($A72="","",INDEX(BOM!$G$2:$G$108,MATCH(71,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A72="","",INDEX(BOM!$G$2:$G$110,MATCH(71,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D72" s="9" t="n">
-        <f aca="false">IF($A72="","",INDEX(BOM!$H$2:$H$108,MATCH(71,BOM!$O$2:$O$108,0)))</f>
-        <v>29.99</v>
+        <f aca="false">IF($A72="","",INDEX(BOM!$H$2:$H$110,MATCH(71,BOM!$O$2:$O$110,0)))</f>
+        <v>60</v>
       </c>
       <c r="E72" s="9" t="n">
-        <f aca="false">IF($A72="","",INDEX(BOM!$I$2:$I$108,MATCH(71,BOM!$O$2:$O$108,0)))</f>
-        <v>29.99</v>
+        <f aca="false">IF($A72="","",INDEX(BOM!$I$2:$I$110,MATCH(71,BOM!$O$2:$O$110,0)))</f>
+        <v>60</v>
       </c>
       <c r="F72" s="0" t="str">
-        <f aca="false">IF($A72="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(71,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(71,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
-        <v>open on amazon.ca</v>
+        <f aca="false">IF($A72="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(71,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(71,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
+        <v/>
       </c>
       <c r="G72" s="0" t="str">
-        <f aca="false">IF($A72="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(71,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A72="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(71,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(72,BOM!$O$2:$O$108,0)),"",72)</f>
+        <f aca="false">IF(ISNA(MATCH(72,BOM!$O$2:$O$110,0)),"",72)</f>
         <v>72</v>
       </c>
       <c r="B73" s="0" t="str">
-        <f aca="false">IF($A73="","",INDEX(BOM!$B$2:$B$108,MATCH(72,BOM!$O$2:$O$108,0)))</f>
-        <v>Strip brush 25 mm in aluminium holder, ~5 m</v>
+        <f aca="false">IF($A73="","",INDEX(BOM!$B$2:$B$110,MATCH(72,BOM!$O$2:$O$110,0)))</f>
+        <v>High-density foam 25 mm (1") x 610 x 1830 mm</v>
       </c>
       <c r="C73" s="0" t="n">
-        <f aca="false">IF($A73="","",INDEX(BOM!$G$2:$G$108,MATCH(72,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A73="","",INDEX(BOM!$G$2:$G$110,MATCH(72,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D73" s="9" t="n">
-        <f aca="false">IF($A73="","",INDEX(BOM!$H$2:$H$108,MATCH(72,BOM!$O$2:$O$108,0)))</f>
-        <v>60</v>
+        <f aca="false">IF($A73="","",INDEX(BOM!$H$2:$H$110,MATCH(72,BOM!$O$2:$O$110,0)))</f>
+        <v>32.15</v>
       </c>
       <c r="E73" s="9" t="n">
-        <f aca="false">IF($A73="","",INDEX(BOM!$I$2:$I$108,MATCH(72,BOM!$O$2:$O$108,0)))</f>
-        <v>60</v>
+        <f aca="false">IF($A73="","",INDEX(BOM!$I$2:$I$110,MATCH(72,BOM!$O$2:$O$110,0)))</f>
+        <v>32.15</v>
       </c>
       <c r="F73" s="0" t="str">
-        <f aca="false">IF($A73="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(72,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(72,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
-        <v/>
+        <f aca="false">IF($A73="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(72,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(72,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
+        <v>open on amazon.ca</v>
       </c>
       <c r="G73" s="0" t="str">
-        <f aca="false">IF($A73="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(72,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A73="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(72,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(73,BOM!$O$2:$O$108,0)),"",73)</f>
+        <f aca="false">IF(ISNA(MATCH(73,BOM!$O$2:$O$110,0)),"",73)</f>
         <v>73</v>
       </c>
       <c r="B74" s="0" t="str">
-        <f aca="false">IF($A74="","",INDEX(BOM!$B$2:$B$108,MATCH(73,BOM!$O$2:$O$108,0)))</f>
-        <v>High-density foam 25 mm (1") x 610 x 1830 mm</v>
+        <f aca="false">IF($A74="","",INDEX(BOM!$B$2:$B$110,MATCH(73,BOM!$O$2:$O$110,0)))</f>
+        <v>Buckle kit: 25 mm side-release buckles + 9 m webbing (REDAPRIC)</v>
       </c>
       <c r="C74" s="0" t="n">
-        <f aca="false">IF($A74="","",INDEX(BOM!$G$2:$G$108,MATCH(73,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A74="","",INDEX(BOM!$G$2:$G$110,MATCH(73,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D74" s="9" t="n">
-        <f aca="false">IF($A74="","",INDEX(BOM!$H$2:$H$108,MATCH(73,BOM!$O$2:$O$108,0)))</f>
-        <v>32.15</v>
+        <f aca="false">IF($A74="","",INDEX(BOM!$H$2:$H$110,MATCH(73,BOM!$O$2:$O$110,0)))</f>
+        <v>13</v>
       </c>
       <c r="E74" s="9" t="n">
-        <f aca="false">IF($A74="","",INDEX(BOM!$I$2:$I$108,MATCH(73,BOM!$O$2:$O$108,0)))</f>
-        <v>32.15</v>
+        <f aca="false">IF($A74="","",INDEX(BOM!$I$2:$I$110,MATCH(73,BOM!$O$2:$O$110,0)))</f>
+        <v>13</v>
       </c>
       <c r="F74" s="0" t="str">
-        <f aca="false">IF($A74="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(73,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(73,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A74="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(73,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(73,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G74" s="0" t="str">
-        <f aca="false">IF($A74="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(73,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A74="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(73,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(74,BOM!$O$2:$O$108,0)),"",74)</f>
+        <f aca="false">IF(ISNA(MATCH(74,BOM!$O$2:$O$110,0)),"",74)</f>
         <v>74</v>
       </c>
       <c r="B75" s="0" t="str">
-        <f aca="false">IF($A75="","",INDEX(BOM!$B$2:$B$108,MATCH(74,BOM!$O$2:$O$108,0)))</f>
-        <v>Buckle kit: 25 mm side-release buckles + 9 m webbing (REDAPRIC)</v>
+        <f aca="false">IF($A75="","",INDEX(BOM!$B$2:$B$110,MATCH(74,BOM!$O$2:$O$110,0)))</f>
+        <v>Rated 25 mm (1") webbing, &gt;= 700 kg</v>
       </c>
       <c r="C75" s="0" t="n">
-        <f aca="false">IF($A75="","",INDEX(BOM!$G$2:$G$108,MATCH(74,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A75="","",INDEX(BOM!$G$2:$G$110,MATCH(74,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D75" s="9" t="n">
-        <f aca="false">IF($A75="","",INDEX(BOM!$H$2:$H$108,MATCH(74,BOM!$O$2:$O$108,0)))</f>
-        <v>13</v>
+        <f aca="false">IF($A75="","",INDEX(BOM!$H$2:$H$110,MATCH(74,BOM!$O$2:$O$110,0)))</f>
+        <v>19.99</v>
       </c>
       <c r="E75" s="9" t="n">
-        <f aca="false">IF($A75="","",INDEX(BOM!$I$2:$I$108,MATCH(74,BOM!$O$2:$O$108,0)))</f>
-        <v>13</v>
+        <f aca="false">IF($A75="","",INDEX(BOM!$I$2:$I$110,MATCH(74,BOM!$O$2:$O$110,0)))</f>
+        <v>19.99</v>
       </c>
       <c r="F75" s="0" t="str">
-        <f aca="false">IF($A75="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(74,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(74,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A75="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(74,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(74,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G75" s="0" t="str">
-        <f aca="false">IF($A75="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(74,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A75="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(74,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(75,BOM!$O$2:$O$108,0)),"",75)</f>
+        <f aca="false">IF(ISNA(MATCH(75,BOM!$O$2:$O$110,0)),"",75)</f>
         <v>75</v>
       </c>
       <c r="B76" s="0" t="str">
-        <f aca="false">IF($A76="","",INDEX(BOM!$B$2:$B$108,MATCH(75,BOM!$O$2:$O$108,0)))</f>
-        <v>Rated 25 mm (1") webbing, &gt;= 700 kg</v>
+        <f aca="false">IF($A76="","",INDEX(BOM!$B$2:$B$110,MATCH(75,BOM!$O$2:$O$110,0)))</f>
+        <v>Welded steel O-rings 50 mm (2") OD</v>
       </c>
       <c r="C76" s="0" t="n">
-        <f aca="false">IF($A76="","",INDEX(BOM!$G$2:$G$108,MATCH(75,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A76="","",INDEX(BOM!$G$2:$G$110,MATCH(75,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D76" s="9" t="n">
-        <f aca="false">IF($A76="","",INDEX(BOM!$H$2:$H$108,MATCH(75,BOM!$O$2:$O$108,0)))</f>
-        <v>19.99</v>
+        <f aca="false">IF($A76="","",INDEX(BOM!$H$2:$H$110,MATCH(75,BOM!$O$2:$O$110,0)))</f>
+        <v>15.99</v>
       </c>
       <c r="E76" s="9" t="n">
-        <f aca="false">IF($A76="","",INDEX(BOM!$I$2:$I$108,MATCH(75,BOM!$O$2:$O$108,0)))</f>
-        <v>19.99</v>
+        <f aca="false">IF($A76="","",INDEX(BOM!$I$2:$I$110,MATCH(75,BOM!$O$2:$O$110,0)))</f>
+        <v>15.99</v>
       </c>
       <c r="F76" s="0" t="str">
-        <f aca="false">IF($A76="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(75,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(75,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A76="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(75,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(75,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G76" s="0" t="str">
-        <f aca="false">IF($A76="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(75,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A76="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(75,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(76,BOM!$O$2:$O$108,0)),"",76)</f>
+        <f aca="false">IF(ISNA(MATCH(76,BOM!$O$2:$O$110,0)),"",76)</f>
         <v>76</v>
       </c>
       <c r="B77" s="0" t="str">
-        <f aca="false">IF($A77="","",INDEX(BOM!$B$2:$B$108,MATCH(76,BOM!$O$2:$O$108,0)))</f>
-        <v>Welded steel O-rings 50 mm (2") OD</v>
+        <f aca="false">IF($A77="","",INDEX(BOM!$B$2:$B$110,MATCH(76,BOM!$O$2:$O$110,0)))</f>
+        <v>Welded steel D-rings 25 mm (1")</v>
       </c>
       <c r="C77" s="0" t="n">
-        <f aca="false">IF($A77="","",INDEX(BOM!$G$2:$G$108,MATCH(76,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A77="","",INDEX(BOM!$G$2:$G$110,MATCH(76,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D77" s="9" t="n">
-        <f aca="false">IF($A77="","",INDEX(BOM!$H$2:$H$108,MATCH(76,BOM!$O$2:$O$108,0)))</f>
-        <v>15.99</v>
+        <f aca="false">IF($A77="","",INDEX(BOM!$H$2:$H$110,MATCH(76,BOM!$O$2:$O$110,0)))</f>
+        <v>15.97</v>
       </c>
       <c r="E77" s="9" t="n">
-        <f aca="false">IF($A77="","",INDEX(BOM!$I$2:$I$108,MATCH(76,BOM!$O$2:$O$108,0)))</f>
-        <v>15.99</v>
+        <f aca="false">IF($A77="","",INDEX(BOM!$I$2:$I$110,MATCH(76,BOM!$O$2:$O$110,0)))</f>
+        <v>15.97</v>
       </c>
       <c r="F77" s="0" t="str">
-        <f aca="false">IF($A77="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(76,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(76,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A77="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(76,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(76,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G77" s="0" t="str">
-        <f aca="false">IF($A77="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(76,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A77="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(76,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(77,BOM!$O$2:$O$108,0)),"",77)</f>
+        <f aca="false">IF(ISNA(MATCH(77,BOM!$O$2:$O$110,0)),"",77)</f>
         <v>77</v>
       </c>
       <c r="B78" s="0" t="str">
-        <f aca="false">IF($A78="","",INDEX(BOM!$B$2:$B$108,MATCH(77,BOM!$O$2:$O$108,0)))</f>
-        <v>Welded steel D-rings 25 mm (1")</v>
+        <f aca="false">IF($A78="","",INDEX(BOM!$B$2:$B$110,MATCH(77,BOM!$O$2:$O$110,0)))</f>
+        <v>2-point adjustable lap belt</v>
       </c>
       <c r="C78" s="0" t="n">
-        <f aca="false">IF($A78="","",INDEX(BOM!$G$2:$G$108,MATCH(77,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A78="","",INDEX(BOM!$G$2:$G$110,MATCH(77,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D78" s="9" t="n">
-        <f aca="false">IF($A78="","",INDEX(BOM!$H$2:$H$108,MATCH(77,BOM!$O$2:$O$108,0)))</f>
-        <v>15.97</v>
+        <f aca="false">IF($A78="","",INDEX(BOM!$H$2:$H$110,MATCH(77,BOM!$O$2:$O$110,0)))</f>
+        <v>24.99</v>
       </c>
       <c r="E78" s="9" t="n">
-        <f aca="false">IF($A78="","",INDEX(BOM!$I$2:$I$108,MATCH(77,BOM!$O$2:$O$108,0)))</f>
-        <v>15.97</v>
+        <f aca="false">IF($A78="","",INDEX(BOM!$I$2:$I$110,MATCH(77,BOM!$O$2:$O$110,0)))</f>
+        <v>24.99</v>
       </c>
       <c r="F78" s="0" t="str">
-        <f aca="false">IF($A78="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(77,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(77,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A78="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(77,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(77,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G78" s="0" t="str">
-        <f aca="false">IF($A78="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(77,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A78="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(77,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(78,BOM!$O$2:$O$108,0)),"",78)</f>
+        <f aca="false">IF(ISNA(MATCH(78,BOM!$O$2:$O$110,0)),"",78)</f>
         <v>78</v>
       </c>
       <c r="B79" s="0" t="str">
-        <f aca="false">IF($A79="","",INDEX(BOM!$B$2:$B$108,MATCH(78,BOM!$O$2:$O$108,0)))</f>
-        <v>2-point adjustable lap belt</v>
+        <f aca="false">IF($A79="","",INDEX(BOM!$B$2:$B$110,MATCH(78,BOM!$O$2:$O$110,0)))</f>
+        <v>High-density upholstery foam 50 mm (2") x 610 x 1830 mm</v>
       </c>
       <c r="C79" s="0" t="n">
-        <f aca="false">IF($A79="","",INDEX(BOM!$G$2:$G$108,MATCH(78,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A79="","",INDEX(BOM!$G$2:$G$110,MATCH(78,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D79" s="9" t="n">
-        <f aca="false">IF($A79="","",INDEX(BOM!$H$2:$H$108,MATCH(78,BOM!$O$2:$O$108,0)))</f>
-        <v>24.99</v>
+        <f aca="false">IF($A79="","",INDEX(BOM!$H$2:$H$110,MATCH(78,BOM!$O$2:$O$110,0)))</f>
+        <v>54.54</v>
       </c>
       <c r="E79" s="9" t="n">
-        <f aca="false">IF($A79="","",INDEX(BOM!$I$2:$I$108,MATCH(78,BOM!$O$2:$O$108,0)))</f>
-        <v>24.99</v>
+        <f aca="false">IF($A79="","",INDEX(BOM!$I$2:$I$110,MATCH(78,BOM!$O$2:$O$110,0)))</f>
+        <v>54.54</v>
       </c>
       <c r="F79" s="0" t="str">
-        <f aca="false">IF($A79="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(78,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(78,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A79="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(78,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(78,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G79" s="0" t="str">
-        <f aca="false">IF($A79="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(78,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A79="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(78,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(79,BOM!$O$2:$O$108,0)),"",79)</f>
+        <f aca="false">IF(ISNA(MATCH(79,BOM!$O$2:$O$110,0)),"",79)</f>
         <v>79</v>
       </c>
       <c r="B80" s="0" t="str">
-        <f aca="false">IF($A80="","",INDEX(BOM!$B$2:$B$108,MATCH(79,BOM!$O$2:$O$108,0)))</f>
-        <v>High-density upholstery foam 50 mm (2") x 610 x 1830 mm</v>
+        <f aca="false">IF($A80="","",INDEX(BOM!$B$2:$B$110,MATCH(79,BOM!$O$2:$O$110,0)))</f>
+        <v>Marine vinyl, black, 1.5 m x 1.37 m (5 ft x 54")</v>
       </c>
       <c r="C80" s="0" t="n">
-        <f aca="false">IF($A80="","",INDEX(BOM!$G$2:$G$108,MATCH(79,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A80="","",INDEX(BOM!$G$2:$G$110,MATCH(79,BOM!$O$2:$O$110,0)))</f>
         <v>1</v>
       </c>
       <c r="D80" s="9" t="n">
-        <f aca="false">IF($A80="","",INDEX(BOM!$H$2:$H$108,MATCH(79,BOM!$O$2:$O$108,0)))</f>
-        <v>54.54</v>
+        <f aca="false">IF($A80="","",INDEX(BOM!$H$2:$H$110,MATCH(79,BOM!$O$2:$O$110,0)))</f>
+        <v>43.69</v>
       </c>
       <c r="E80" s="9" t="n">
-        <f aca="false">IF($A80="","",INDEX(BOM!$I$2:$I$108,MATCH(79,BOM!$O$2:$O$108,0)))</f>
-        <v>54.54</v>
+        <f aca="false">IF($A80="","",INDEX(BOM!$I$2:$I$110,MATCH(79,BOM!$O$2:$O$110,0)))</f>
+        <v>43.69</v>
       </c>
       <c r="F80" s="0" t="str">
-        <f aca="false">IF($A80="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(79,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(79,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A80="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(79,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(79,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v>open on amazon.ca</v>
       </c>
       <c r="G80" s="0" t="str">
-        <f aca="false">IF($A80="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(79,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A80="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(79,BOM!$O$2:$O$110,0)),"search"))</f>
         <v>search</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="n">
-        <f aca="false">IF(ISNA(MATCH(80,BOM!$O$2:$O$108,0)),"",80)</f>
-        <v>80</v>
+      <c r="A81" s="0" t="str">
+        <f aca="false">IF(ISNA(MATCH(80,BOM!$O$2:$O$110,0)),"",80)</f>
+        <v/>
       </c>
       <c r="B81" s="0" t="str">
-        <f aca="false">IF($A81="","",INDEX(BOM!$B$2:$B$108,MATCH(80,BOM!$O$2:$O$108,0)))</f>
-        <v>Marine vinyl, black, 1.5 m x 1.37 m (5 ft x 54")</v>
-      </c>
-      <c r="C81" s="0" t="n">
-        <f aca="false">IF($A81="","",INDEX(BOM!$G$2:$G$108,MATCH(80,BOM!$O$2:$O$108,0)))</f>
-        <v>1</v>
-      </c>
-      <c r="D81" s="9" t="n">
-        <f aca="false">IF($A81="","",INDEX(BOM!$H$2:$H$108,MATCH(80,BOM!$O$2:$O$108,0)))</f>
-        <v>43.69</v>
-      </c>
-      <c r="E81" s="9" t="n">
-        <f aca="false">IF($A81="","",INDEX(BOM!$I$2:$I$108,MATCH(80,BOM!$O$2:$O$108,0)))</f>
-        <v>43.69</v>
+        <f aca="false">IF($A81="","",INDEX(BOM!$B$2:$B$110,MATCH(80,BOM!$O$2:$O$110,0)))</f>
+        <v/>
+      </c>
+      <c r="C81" s="0" t="str">
+        <f aca="false">IF($A81="","",INDEX(BOM!$G$2:$G$110,MATCH(80,BOM!$O$2:$O$110,0)))</f>
+        <v/>
+      </c>
+      <c r="D81" s="9" t="str">
+        <f aca="false">IF($A81="","",INDEX(BOM!$H$2:$H$110,MATCH(80,BOM!$O$2:$O$110,0)))</f>
+        <v/>
+      </c>
+      <c r="E81" s="9" t="str">
+        <f aca="false">IF($A81="","",INDEX(BOM!$I$2:$I$110,MATCH(80,BOM!$O$2:$O$110,0)))</f>
+        <v/>
       </c>
       <c r="F81" s="0" t="str">
-        <f aca="false">IF($A81="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(80,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(80,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
-        <v>open on amazon.ca</v>
+        <f aca="false">IF($A81="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(80,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(80,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
+        <v/>
       </c>
       <c r="G81" s="0" t="str">
-        <f aca="false">IF($A81="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(80,BOM!$O$2:$O$108,0)),"search"))</f>
-        <v>search</v>
+        <f aca="false">IF($A81="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(80,BOM!$O$2:$O$110,0)),"search"))</f>
+        <v/>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(81,BOM!$O$2:$O$108,0)),"",81)</f>
+        <f aca="false">IF(ISNA(MATCH(81,BOM!$O$2:$O$110,0)),"",81)</f>
         <v/>
       </c>
       <c r="B82" s="0" t="str">
-        <f aca="false">IF($A82="","",INDEX(BOM!$B$2:$B$108,MATCH(81,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A82="","",INDEX(BOM!$B$2:$B$110,MATCH(81,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C82" s="0" t="str">
-        <f aca="false">IF($A82="","",INDEX(BOM!$G$2:$G$108,MATCH(81,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A82="","",INDEX(BOM!$G$2:$G$110,MATCH(81,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D82" s="9" t="str">
-        <f aca="false">IF($A82="","",INDEX(BOM!$H$2:$H$108,MATCH(81,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A82="","",INDEX(BOM!$H$2:$H$110,MATCH(81,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E82" s="9" t="str">
-        <f aca="false">IF($A82="","",INDEX(BOM!$I$2:$I$108,MATCH(81,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A82="","",INDEX(BOM!$I$2:$I$110,MATCH(81,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F82" s="0" t="str">
-        <f aca="false">IF($A82="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(81,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(81,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A82="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(81,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(81,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G82" s="0" t="str">
-        <f aca="false">IF($A82="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(81,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A82="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(81,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(82,BOM!$O$2:$O$108,0)),"",82)</f>
+        <f aca="false">IF(ISNA(MATCH(82,BOM!$O$2:$O$110,0)),"",82)</f>
         <v/>
       </c>
       <c r="B83" s="0" t="str">
-        <f aca="false">IF($A83="","",INDEX(BOM!$B$2:$B$108,MATCH(82,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A83="","",INDEX(BOM!$B$2:$B$110,MATCH(82,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C83" s="0" t="str">
-        <f aca="false">IF($A83="","",INDEX(BOM!$G$2:$G$108,MATCH(82,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A83="","",INDEX(BOM!$G$2:$G$110,MATCH(82,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D83" s="9" t="str">
-        <f aca="false">IF($A83="","",INDEX(BOM!$H$2:$H$108,MATCH(82,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A83="","",INDEX(BOM!$H$2:$H$110,MATCH(82,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E83" s="9" t="str">
-        <f aca="false">IF($A83="","",INDEX(BOM!$I$2:$I$108,MATCH(82,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A83="","",INDEX(BOM!$I$2:$I$110,MATCH(82,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F83" s="0" t="str">
-        <f aca="false">IF($A83="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(82,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(82,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A83="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(82,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(82,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G83" s="0" t="str">
-        <f aca="false">IF($A83="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(82,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A83="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(82,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(83,BOM!$O$2:$O$108,0)),"",83)</f>
+        <f aca="false">IF(ISNA(MATCH(83,BOM!$O$2:$O$110,0)),"",83)</f>
         <v/>
       </c>
       <c r="B84" s="0" t="str">
-        <f aca="false">IF($A84="","",INDEX(BOM!$B$2:$B$108,MATCH(83,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A84="","",INDEX(BOM!$B$2:$B$110,MATCH(83,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C84" s="0" t="str">
-        <f aca="false">IF($A84="","",INDEX(BOM!$G$2:$G$108,MATCH(83,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A84="","",INDEX(BOM!$G$2:$G$110,MATCH(83,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D84" s="9" t="str">
-        <f aca="false">IF($A84="","",INDEX(BOM!$H$2:$H$108,MATCH(83,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A84="","",INDEX(BOM!$H$2:$H$110,MATCH(83,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E84" s="9" t="str">
-        <f aca="false">IF($A84="","",INDEX(BOM!$I$2:$I$108,MATCH(83,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A84="","",INDEX(BOM!$I$2:$I$110,MATCH(83,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F84" s="0" t="str">
-        <f aca="false">IF($A84="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(83,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(83,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A84="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(83,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(83,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G84" s="0" t="str">
-        <f aca="false">IF($A84="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(83,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A84="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(83,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(84,BOM!$O$2:$O$108,0)),"",84)</f>
+        <f aca="false">IF(ISNA(MATCH(84,BOM!$O$2:$O$110,0)),"",84)</f>
         <v/>
       </c>
       <c r="B85" s="0" t="str">
-        <f aca="false">IF($A85="","",INDEX(BOM!$B$2:$B$108,MATCH(84,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A85="","",INDEX(BOM!$B$2:$B$110,MATCH(84,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C85" s="0" t="str">
-        <f aca="false">IF($A85="","",INDEX(BOM!$G$2:$G$108,MATCH(84,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A85="","",INDEX(BOM!$G$2:$G$110,MATCH(84,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D85" s="9" t="str">
-        <f aca="false">IF($A85="","",INDEX(BOM!$H$2:$H$108,MATCH(84,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A85="","",INDEX(BOM!$H$2:$H$110,MATCH(84,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E85" s="9" t="str">
-        <f aca="false">IF($A85="","",INDEX(BOM!$I$2:$I$108,MATCH(84,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A85="","",INDEX(BOM!$I$2:$I$110,MATCH(84,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F85" s="0" t="str">
-        <f aca="false">IF($A85="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(84,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(84,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A85="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(84,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(84,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G85" s="0" t="str">
-        <f aca="false">IF($A85="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(84,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A85="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(84,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(85,BOM!$O$2:$O$108,0)),"",85)</f>
+        <f aca="false">IF(ISNA(MATCH(85,BOM!$O$2:$O$110,0)),"",85)</f>
         <v/>
       </c>
       <c r="B86" s="0" t="str">
-        <f aca="false">IF($A86="","",INDEX(BOM!$B$2:$B$108,MATCH(85,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A86="","",INDEX(BOM!$B$2:$B$110,MATCH(85,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C86" s="0" t="str">
-        <f aca="false">IF($A86="","",INDEX(BOM!$G$2:$G$108,MATCH(85,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A86="","",INDEX(BOM!$G$2:$G$110,MATCH(85,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D86" s="9" t="str">
-        <f aca="false">IF($A86="","",INDEX(BOM!$H$2:$H$108,MATCH(85,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A86="","",INDEX(BOM!$H$2:$H$110,MATCH(85,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E86" s="9" t="str">
-        <f aca="false">IF($A86="","",INDEX(BOM!$I$2:$I$108,MATCH(85,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A86="","",INDEX(BOM!$I$2:$I$110,MATCH(85,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F86" s="0" t="str">
-        <f aca="false">IF($A86="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(85,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(85,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A86="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(85,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(85,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G86" s="0" t="str">
-        <f aca="false">IF($A86="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(85,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A86="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(85,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(86,BOM!$O$2:$O$108,0)),"",86)</f>
+        <f aca="false">IF(ISNA(MATCH(86,BOM!$O$2:$O$110,0)),"",86)</f>
         <v/>
       </c>
       <c r="B87" s="0" t="str">
-        <f aca="false">IF($A87="","",INDEX(BOM!$B$2:$B$108,MATCH(86,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A87="","",INDEX(BOM!$B$2:$B$110,MATCH(86,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C87" s="0" t="str">
-        <f aca="false">IF($A87="","",INDEX(BOM!$G$2:$G$108,MATCH(86,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A87="","",INDEX(BOM!$G$2:$G$110,MATCH(86,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D87" s="9" t="str">
-        <f aca="false">IF($A87="","",INDEX(BOM!$H$2:$H$108,MATCH(86,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A87="","",INDEX(BOM!$H$2:$H$110,MATCH(86,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E87" s="9" t="str">
-        <f aca="false">IF($A87="","",INDEX(BOM!$I$2:$I$108,MATCH(86,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A87="","",INDEX(BOM!$I$2:$I$110,MATCH(86,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F87" s="0" t="str">
-        <f aca="false">IF($A87="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(86,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(86,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A87="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(86,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(86,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G87" s="0" t="str">
-        <f aca="false">IF($A87="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(86,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A87="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(86,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(87,BOM!$O$2:$O$108,0)),"",87)</f>
+        <f aca="false">IF(ISNA(MATCH(87,BOM!$O$2:$O$110,0)),"",87)</f>
         <v/>
       </c>
       <c r="B88" s="0" t="str">
-        <f aca="false">IF($A88="","",INDEX(BOM!$B$2:$B$108,MATCH(87,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A88="","",INDEX(BOM!$B$2:$B$110,MATCH(87,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C88" s="0" t="str">
-        <f aca="false">IF($A88="","",INDEX(BOM!$G$2:$G$108,MATCH(87,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A88="","",INDEX(BOM!$G$2:$G$110,MATCH(87,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D88" s="9" t="str">
-        <f aca="false">IF($A88="","",INDEX(BOM!$H$2:$H$108,MATCH(87,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A88="","",INDEX(BOM!$H$2:$H$110,MATCH(87,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E88" s="9" t="str">
-        <f aca="false">IF($A88="","",INDEX(BOM!$I$2:$I$108,MATCH(87,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A88="","",INDEX(BOM!$I$2:$I$110,MATCH(87,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F88" s="0" t="str">
-        <f aca="false">IF($A88="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(87,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(87,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A88="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(87,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(87,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G88" s="0" t="str">
-        <f aca="false">IF($A88="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(87,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A88="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(87,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(88,BOM!$O$2:$O$108,0)),"",88)</f>
+        <f aca="false">IF(ISNA(MATCH(88,BOM!$O$2:$O$110,0)),"",88)</f>
         <v/>
       </c>
       <c r="B89" s="0" t="str">
-        <f aca="false">IF($A89="","",INDEX(BOM!$B$2:$B$108,MATCH(88,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A89="","",INDEX(BOM!$B$2:$B$110,MATCH(88,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C89" s="0" t="str">
-        <f aca="false">IF($A89="","",INDEX(BOM!$G$2:$G$108,MATCH(88,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A89="","",INDEX(BOM!$G$2:$G$110,MATCH(88,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D89" s="9" t="str">
-        <f aca="false">IF($A89="","",INDEX(BOM!$H$2:$H$108,MATCH(88,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A89="","",INDEX(BOM!$H$2:$H$110,MATCH(88,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E89" s="9" t="str">
-        <f aca="false">IF($A89="","",INDEX(BOM!$I$2:$I$108,MATCH(88,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A89="","",INDEX(BOM!$I$2:$I$110,MATCH(88,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F89" s="0" t="str">
-        <f aca="false">IF($A89="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(88,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(88,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A89="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(88,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(88,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G89" s="0" t="str">
-        <f aca="false">IF($A89="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(88,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A89="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(88,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(89,BOM!$O$2:$O$108,0)),"",89)</f>
+        <f aca="false">IF(ISNA(MATCH(89,BOM!$O$2:$O$110,0)),"",89)</f>
         <v/>
       </c>
       <c r="B90" s="0" t="str">
-        <f aca="false">IF($A90="","",INDEX(BOM!$B$2:$B$108,MATCH(89,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A90="","",INDEX(BOM!$B$2:$B$110,MATCH(89,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C90" s="0" t="str">
-        <f aca="false">IF($A90="","",INDEX(BOM!$G$2:$G$108,MATCH(89,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A90="","",INDEX(BOM!$G$2:$G$110,MATCH(89,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D90" s="9" t="str">
-        <f aca="false">IF($A90="","",INDEX(BOM!$H$2:$H$108,MATCH(89,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A90="","",INDEX(BOM!$H$2:$H$110,MATCH(89,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E90" s="9" t="str">
-        <f aca="false">IF($A90="","",INDEX(BOM!$I$2:$I$108,MATCH(89,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A90="","",INDEX(BOM!$I$2:$I$110,MATCH(89,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F90" s="0" t="str">
-        <f aca="false">IF($A90="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(89,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(89,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A90="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(89,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(89,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G90" s="0" t="str">
-        <f aca="false">IF($A90="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(89,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A90="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(89,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(90,BOM!$O$2:$O$108,0)),"",90)</f>
+        <f aca="false">IF(ISNA(MATCH(90,BOM!$O$2:$O$110,0)),"",90)</f>
         <v/>
       </c>
       <c r="B91" s="0" t="str">
-        <f aca="false">IF($A91="","",INDEX(BOM!$B$2:$B$108,MATCH(90,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A91="","",INDEX(BOM!$B$2:$B$110,MATCH(90,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C91" s="0" t="str">
-        <f aca="false">IF($A91="","",INDEX(BOM!$G$2:$G$108,MATCH(90,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A91="","",INDEX(BOM!$G$2:$G$110,MATCH(90,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D91" s="9" t="str">
-        <f aca="false">IF($A91="","",INDEX(BOM!$H$2:$H$108,MATCH(90,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A91="","",INDEX(BOM!$H$2:$H$110,MATCH(90,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E91" s="9" t="str">
-        <f aca="false">IF($A91="","",INDEX(BOM!$I$2:$I$108,MATCH(90,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A91="","",INDEX(BOM!$I$2:$I$110,MATCH(90,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F91" s="0" t="str">
-        <f aca="false">IF($A91="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(90,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(90,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A91="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(90,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(90,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G91" s="0" t="str">
-        <f aca="false">IF($A91="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(90,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A91="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(90,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(91,BOM!$O$2:$O$108,0)),"",91)</f>
+        <f aca="false">IF(ISNA(MATCH(91,BOM!$O$2:$O$110,0)),"",91)</f>
         <v/>
       </c>
       <c r="B92" s="0" t="str">
-        <f aca="false">IF($A92="","",INDEX(BOM!$B$2:$B$108,MATCH(91,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A92="","",INDEX(BOM!$B$2:$B$110,MATCH(91,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C92" s="0" t="str">
-        <f aca="false">IF($A92="","",INDEX(BOM!$G$2:$G$108,MATCH(91,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A92="","",INDEX(BOM!$G$2:$G$110,MATCH(91,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D92" s="9" t="str">
-        <f aca="false">IF($A92="","",INDEX(BOM!$H$2:$H$108,MATCH(91,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A92="","",INDEX(BOM!$H$2:$H$110,MATCH(91,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E92" s="9" t="str">
-        <f aca="false">IF($A92="","",INDEX(BOM!$I$2:$I$108,MATCH(91,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A92="","",INDEX(BOM!$I$2:$I$110,MATCH(91,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F92" s="0" t="str">
-        <f aca="false">IF($A92="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(91,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(91,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A92="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(91,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(91,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G92" s="0" t="str">
-        <f aca="false">IF($A92="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(91,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A92="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(91,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(92,BOM!$O$2:$O$108,0)),"",92)</f>
+        <f aca="false">IF(ISNA(MATCH(92,BOM!$O$2:$O$110,0)),"",92)</f>
         <v/>
       </c>
       <c r="B93" s="0" t="str">
-        <f aca="false">IF($A93="","",INDEX(BOM!$B$2:$B$108,MATCH(92,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A93="","",INDEX(BOM!$B$2:$B$110,MATCH(92,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C93" s="0" t="str">
-        <f aca="false">IF($A93="","",INDEX(BOM!$G$2:$G$108,MATCH(92,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A93="","",INDEX(BOM!$G$2:$G$110,MATCH(92,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D93" s="9" t="str">
-        <f aca="false">IF($A93="","",INDEX(BOM!$H$2:$H$108,MATCH(92,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A93="","",INDEX(BOM!$H$2:$H$110,MATCH(92,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E93" s="9" t="str">
-        <f aca="false">IF($A93="","",INDEX(BOM!$I$2:$I$108,MATCH(92,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A93="","",INDEX(BOM!$I$2:$I$110,MATCH(92,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F93" s="0" t="str">
-        <f aca="false">IF($A93="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(92,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(92,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A93="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(92,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(92,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G93" s="0" t="str">
-        <f aca="false">IF($A93="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(92,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A93="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(92,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(93,BOM!$O$2:$O$108,0)),"",93)</f>
+        <f aca="false">IF(ISNA(MATCH(93,BOM!$O$2:$O$110,0)),"",93)</f>
         <v/>
       </c>
       <c r="B94" s="0" t="str">
-        <f aca="false">IF($A94="","",INDEX(BOM!$B$2:$B$108,MATCH(93,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A94="","",INDEX(BOM!$B$2:$B$110,MATCH(93,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C94" s="0" t="str">
-        <f aca="false">IF($A94="","",INDEX(BOM!$G$2:$G$108,MATCH(93,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A94="","",INDEX(BOM!$G$2:$G$110,MATCH(93,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D94" s="9" t="str">
-        <f aca="false">IF($A94="","",INDEX(BOM!$H$2:$H$108,MATCH(93,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A94="","",INDEX(BOM!$H$2:$H$110,MATCH(93,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E94" s="9" t="str">
-        <f aca="false">IF($A94="","",INDEX(BOM!$I$2:$I$108,MATCH(93,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A94="","",INDEX(BOM!$I$2:$I$110,MATCH(93,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F94" s="0" t="str">
-        <f aca="false">IF($A94="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(93,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(93,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A94="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(93,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(93,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G94" s="0" t="str">
-        <f aca="false">IF($A94="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(93,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A94="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(93,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(94,BOM!$O$2:$O$108,0)),"",94)</f>
+        <f aca="false">IF(ISNA(MATCH(94,BOM!$O$2:$O$110,0)),"",94)</f>
         <v/>
       </c>
       <c r="B95" s="0" t="str">
-        <f aca="false">IF($A95="","",INDEX(BOM!$B$2:$B$108,MATCH(94,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A95="","",INDEX(BOM!$B$2:$B$110,MATCH(94,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C95" s="0" t="str">
-        <f aca="false">IF($A95="","",INDEX(BOM!$G$2:$G$108,MATCH(94,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A95="","",INDEX(BOM!$G$2:$G$110,MATCH(94,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D95" s="9" t="str">
-        <f aca="false">IF($A95="","",INDEX(BOM!$H$2:$H$108,MATCH(94,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A95="","",INDEX(BOM!$H$2:$H$110,MATCH(94,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E95" s="9" t="str">
-        <f aca="false">IF($A95="","",INDEX(BOM!$I$2:$I$108,MATCH(94,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A95="","",INDEX(BOM!$I$2:$I$110,MATCH(94,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F95" s="0" t="str">
-        <f aca="false">IF($A95="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(94,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(94,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A95="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(94,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(94,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G95" s="0" t="str">
-        <f aca="false">IF($A95="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(94,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A95="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(94,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(95,BOM!$O$2:$O$108,0)),"",95)</f>
+        <f aca="false">IF(ISNA(MATCH(95,BOM!$O$2:$O$110,0)),"",95)</f>
         <v/>
       </c>
       <c r="B96" s="0" t="str">
-        <f aca="false">IF($A96="","",INDEX(BOM!$B$2:$B$108,MATCH(95,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A96="","",INDEX(BOM!$B$2:$B$110,MATCH(95,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C96" s="0" t="str">
-        <f aca="false">IF($A96="","",INDEX(BOM!$G$2:$G$108,MATCH(95,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A96="","",INDEX(BOM!$G$2:$G$110,MATCH(95,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D96" s="9" t="str">
-        <f aca="false">IF($A96="","",INDEX(BOM!$H$2:$H$108,MATCH(95,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A96="","",INDEX(BOM!$H$2:$H$110,MATCH(95,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E96" s="9" t="str">
-        <f aca="false">IF($A96="","",INDEX(BOM!$I$2:$I$108,MATCH(95,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A96="","",INDEX(BOM!$I$2:$I$110,MATCH(95,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F96" s="0" t="str">
-        <f aca="false">IF($A96="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(95,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(95,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A96="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(95,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(95,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G96" s="0" t="str">
-        <f aca="false">IF($A96="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(95,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A96="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(95,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(96,BOM!$O$2:$O$108,0)),"",96)</f>
+        <f aca="false">IF(ISNA(MATCH(96,BOM!$O$2:$O$110,0)),"",96)</f>
         <v/>
       </c>
       <c r="B97" s="0" t="str">
-        <f aca="false">IF($A97="","",INDEX(BOM!$B$2:$B$108,MATCH(96,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A97="","",INDEX(BOM!$B$2:$B$110,MATCH(96,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C97" s="0" t="str">
-        <f aca="false">IF($A97="","",INDEX(BOM!$G$2:$G$108,MATCH(96,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A97="","",INDEX(BOM!$G$2:$G$110,MATCH(96,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D97" s="9" t="str">
-        <f aca="false">IF($A97="","",INDEX(BOM!$H$2:$H$108,MATCH(96,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A97="","",INDEX(BOM!$H$2:$H$110,MATCH(96,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E97" s="9" t="str">
-        <f aca="false">IF($A97="","",INDEX(BOM!$I$2:$I$108,MATCH(96,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A97="","",INDEX(BOM!$I$2:$I$110,MATCH(96,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F97" s="0" t="str">
-        <f aca="false">IF($A97="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(96,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(96,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A97="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(96,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(96,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G97" s="0" t="str">
-        <f aca="false">IF($A97="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(96,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A97="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(96,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(97,BOM!$O$2:$O$108,0)),"",97)</f>
+        <f aca="false">IF(ISNA(MATCH(97,BOM!$O$2:$O$110,0)),"",97)</f>
         <v/>
       </c>
       <c r="B98" s="0" t="str">
-        <f aca="false">IF($A98="","",INDEX(BOM!$B$2:$B$108,MATCH(97,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A98="","",INDEX(BOM!$B$2:$B$110,MATCH(97,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C98" s="0" t="str">
-        <f aca="false">IF($A98="","",INDEX(BOM!$G$2:$G$108,MATCH(97,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A98="","",INDEX(BOM!$G$2:$G$110,MATCH(97,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D98" s="9" t="str">
-        <f aca="false">IF($A98="","",INDEX(BOM!$H$2:$H$108,MATCH(97,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A98="","",INDEX(BOM!$H$2:$H$110,MATCH(97,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E98" s="9" t="str">
-        <f aca="false">IF($A98="","",INDEX(BOM!$I$2:$I$108,MATCH(97,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A98="","",INDEX(BOM!$I$2:$I$110,MATCH(97,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F98" s="0" t="str">
-        <f aca="false">IF($A98="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(97,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(97,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A98="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(97,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(97,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G98" s="0" t="str">
-        <f aca="false">IF($A98="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(97,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A98="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(97,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(98,BOM!$O$2:$O$108,0)),"",98)</f>
+        <f aca="false">IF(ISNA(MATCH(98,BOM!$O$2:$O$110,0)),"",98)</f>
         <v/>
       </c>
       <c r="B99" s="0" t="str">
-        <f aca="false">IF($A99="","",INDEX(BOM!$B$2:$B$108,MATCH(98,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A99="","",INDEX(BOM!$B$2:$B$110,MATCH(98,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C99" s="0" t="str">
-        <f aca="false">IF($A99="","",INDEX(BOM!$G$2:$G$108,MATCH(98,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A99="","",INDEX(BOM!$G$2:$G$110,MATCH(98,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D99" s="9" t="str">
-        <f aca="false">IF($A99="","",INDEX(BOM!$H$2:$H$108,MATCH(98,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A99="","",INDEX(BOM!$H$2:$H$110,MATCH(98,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E99" s="9" t="str">
-        <f aca="false">IF($A99="","",INDEX(BOM!$I$2:$I$108,MATCH(98,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A99="","",INDEX(BOM!$I$2:$I$110,MATCH(98,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F99" s="0" t="str">
-        <f aca="false">IF($A99="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(98,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(98,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A99="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(98,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(98,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G99" s="0" t="str">
-        <f aca="false">IF($A99="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(98,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A99="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(98,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(99,BOM!$O$2:$O$108,0)),"",99)</f>
+        <f aca="false">IF(ISNA(MATCH(99,BOM!$O$2:$O$110,0)),"",99)</f>
         <v/>
       </c>
       <c r="B100" s="0" t="str">
-        <f aca="false">IF($A100="","",INDEX(BOM!$B$2:$B$108,MATCH(99,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A100="","",INDEX(BOM!$B$2:$B$110,MATCH(99,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C100" s="0" t="str">
-        <f aca="false">IF($A100="","",INDEX(BOM!$G$2:$G$108,MATCH(99,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A100="","",INDEX(BOM!$G$2:$G$110,MATCH(99,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D100" s="9" t="str">
-        <f aca="false">IF($A100="","",INDEX(BOM!$H$2:$H$108,MATCH(99,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A100="","",INDEX(BOM!$H$2:$H$110,MATCH(99,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E100" s="9" t="str">
-        <f aca="false">IF($A100="","",INDEX(BOM!$I$2:$I$108,MATCH(99,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A100="","",INDEX(BOM!$I$2:$I$110,MATCH(99,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F100" s="0" t="str">
-        <f aca="false">IF($A100="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(99,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(99,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A100="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(99,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(99,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G100" s="0" t="str">
-        <f aca="false">IF($A100="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(99,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A100="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(99,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(100,BOM!$O$2:$O$108,0)),"",100)</f>
+        <f aca="false">IF(ISNA(MATCH(100,BOM!$O$2:$O$110,0)),"",100)</f>
         <v/>
       </c>
       <c r="B101" s="0" t="str">
-        <f aca="false">IF($A101="","",INDEX(BOM!$B$2:$B$108,MATCH(100,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A101="","",INDEX(BOM!$B$2:$B$110,MATCH(100,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C101" s="0" t="str">
-        <f aca="false">IF($A101="","",INDEX(BOM!$G$2:$G$108,MATCH(100,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A101="","",INDEX(BOM!$G$2:$G$110,MATCH(100,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D101" s="9" t="str">
-        <f aca="false">IF($A101="","",INDEX(BOM!$H$2:$H$108,MATCH(100,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A101="","",INDEX(BOM!$H$2:$H$110,MATCH(100,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E101" s="9" t="str">
-        <f aca="false">IF($A101="","",INDEX(BOM!$I$2:$I$108,MATCH(100,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A101="","",INDEX(BOM!$I$2:$I$110,MATCH(100,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F101" s="0" t="str">
-        <f aca="false">IF($A101="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(100,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(100,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A101="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(100,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(100,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G101" s="0" t="str">
-        <f aca="false">IF($A101="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(100,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A101="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(100,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(101,BOM!$O$2:$O$108,0)),"",101)</f>
+        <f aca="false">IF(ISNA(MATCH(101,BOM!$O$2:$O$110,0)),"",101)</f>
         <v/>
       </c>
       <c r="B102" s="0" t="str">
-        <f aca="false">IF($A102="","",INDEX(BOM!$B$2:$B$108,MATCH(101,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A102="","",INDEX(BOM!$B$2:$B$110,MATCH(101,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C102" s="0" t="str">
-        <f aca="false">IF($A102="","",INDEX(BOM!$G$2:$G$108,MATCH(101,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A102="","",INDEX(BOM!$G$2:$G$110,MATCH(101,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D102" s="9" t="str">
-        <f aca="false">IF($A102="","",INDEX(BOM!$H$2:$H$108,MATCH(101,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A102="","",INDEX(BOM!$H$2:$H$110,MATCH(101,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E102" s="9" t="str">
-        <f aca="false">IF($A102="","",INDEX(BOM!$I$2:$I$108,MATCH(101,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A102="","",INDEX(BOM!$I$2:$I$110,MATCH(101,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F102" s="0" t="str">
-        <f aca="false">IF($A102="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(101,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(101,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A102="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(101,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(101,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G102" s="0" t="str">
-        <f aca="false">IF($A102="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(101,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A102="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(101,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(102,BOM!$O$2:$O$108,0)),"",102)</f>
+        <f aca="false">IF(ISNA(MATCH(102,BOM!$O$2:$O$110,0)),"",102)</f>
         <v/>
       </c>
       <c r="B103" s="0" t="str">
-        <f aca="false">IF($A103="","",INDEX(BOM!$B$2:$B$108,MATCH(102,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A103="","",INDEX(BOM!$B$2:$B$110,MATCH(102,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C103" s="0" t="str">
-        <f aca="false">IF($A103="","",INDEX(BOM!$G$2:$G$108,MATCH(102,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A103="","",INDEX(BOM!$G$2:$G$110,MATCH(102,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D103" s="9" t="str">
-        <f aca="false">IF($A103="","",INDEX(BOM!$H$2:$H$108,MATCH(102,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A103="","",INDEX(BOM!$H$2:$H$110,MATCH(102,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E103" s="9" t="str">
-        <f aca="false">IF($A103="","",INDEX(BOM!$I$2:$I$108,MATCH(102,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A103="","",INDEX(BOM!$I$2:$I$110,MATCH(102,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F103" s="0" t="str">
-        <f aca="false">IF($A103="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(102,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(102,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A103="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(102,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(102,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G103" s="0" t="str">
-        <f aca="false">IF($A103="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(102,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A103="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(102,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(103,BOM!$O$2:$O$108,0)),"",103)</f>
+        <f aca="false">IF(ISNA(MATCH(103,BOM!$O$2:$O$110,0)),"",103)</f>
         <v/>
       </c>
       <c r="B104" s="0" t="str">
-        <f aca="false">IF($A104="","",INDEX(BOM!$B$2:$B$108,MATCH(103,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A104="","",INDEX(BOM!$B$2:$B$110,MATCH(103,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C104" s="0" t="str">
-        <f aca="false">IF($A104="","",INDEX(BOM!$G$2:$G$108,MATCH(103,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A104="","",INDEX(BOM!$G$2:$G$110,MATCH(103,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D104" s="9" t="str">
-        <f aca="false">IF($A104="","",INDEX(BOM!$H$2:$H$108,MATCH(103,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A104="","",INDEX(BOM!$H$2:$H$110,MATCH(103,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E104" s="9" t="str">
-        <f aca="false">IF($A104="","",INDEX(BOM!$I$2:$I$108,MATCH(103,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A104="","",INDEX(BOM!$I$2:$I$110,MATCH(103,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F104" s="0" t="str">
-        <f aca="false">IF($A104="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(103,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(103,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A104="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(103,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(103,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G104" s="0" t="str">
-        <f aca="false">IF($A104="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(103,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A104="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(103,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(104,BOM!$O$2:$O$108,0)),"",104)</f>
+        <f aca="false">IF(ISNA(MATCH(104,BOM!$O$2:$O$110,0)),"",104)</f>
         <v/>
       </c>
       <c r="B105" s="0" t="str">
-        <f aca="false">IF($A105="","",INDEX(BOM!$B$2:$B$108,MATCH(104,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A105="","",INDEX(BOM!$B$2:$B$110,MATCH(104,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C105" s="0" t="str">
-        <f aca="false">IF($A105="","",INDEX(BOM!$G$2:$G$108,MATCH(104,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A105="","",INDEX(BOM!$G$2:$G$110,MATCH(104,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D105" s="9" t="str">
-        <f aca="false">IF($A105="","",INDEX(BOM!$H$2:$H$108,MATCH(104,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A105="","",INDEX(BOM!$H$2:$H$110,MATCH(104,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E105" s="9" t="str">
-        <f aca="false">IF($A105="","",INDEX(BOM!$I$2:$I$108,MATCH(104,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A105="","",INDEX(BOM!$I$2:$I$110,MATCH(104,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F105" s="0" t="str">
-        <f aca="false">IF($A105="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(104,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(104,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A105="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(104,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(104,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G105" s="0" t="str">
-        <f aca="false">IF($A105="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(104,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A105="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(104,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(105,BOM!$O$2:$O$108,0)),"",105)</f>
+        <f aca="false">IF(ISNA(MATCH(105,BOM!$O$2:$O$110,0)),"",105)</f>
         <v/>
       </c>
       <c r="B106" s="0" t="str">
-        <f aca="false">IF($A106="","",INDEX(BOM!$B$2:$B$108,MATCH(105,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A106="","",INDEX(BOM!$B$2:$B$110,MATCH(105,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C106" s="0" t="str">
-        <f aca="false">IF($A106="","",INDEX(BOM!$G$2:$G$108,MATCH(105,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A106="","",INDEX(BOM!$G$2:$G$110,MATCH(105,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D106" s="9" t="str">
-        <f aca="false">IF($A106="","",INDEX(BOM!$H$2:$H$108,MATCH(105,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A106="","",INDEX(BOM!$H$2:$H$110,MATCH(105,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E106" s="9" t="str">
-        <f aca="false">IF($A106="","",INDEX(BOM!$I$2:$I$108,MATCH(105,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A106="","",INDEX(BOM!$I$2:$I$110,MATCH(105,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F106" s="0" t="str">
-        <f aca="false">IF($A106="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(105,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(105,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A106="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(105,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(105,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G106" s="0" t="str">
-        <f aca="false">IF($A106="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(105,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A106="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(105,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(106,BOM!$O$2:$O$108,0)),"",106)</f>
+        <f aca="false">IF(ISNA(MATCH(106,BOM!$O$2:$O$110,0)),"",106)</f>
         <v/>
       </c>
       <c r="B107" s="0" t="str">
-        <f aca="false">IF($A107="","",INDEX(BOM!$B$2:$B$108,MATCH(106,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A107="","",INDEX(BOM!$B$2:$B$110,MATCH(106,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C107" s="0" t="str">
-        <f aca="false">IF($A107="","",INDEX(BOM!$G$2:$G$108,MATCH(106,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A107="","",INDEX(BOM!$G$2:$G$110,MATCH(106,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D107" s="9" t="str">
-        <f aca="false">IF($A107="","",INDEX(BOM!$H$2:$H$108,MATCH(106,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A107="","",INDEX(BOM!$H$2:$H$110,MATCH(106,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E107" s="9" t="str">
-        <f aca="false">IF($A107="","",INDEX(BOM!$I$2:$I$108,MATCH(106,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A107="","",INDEX(BOM!$I$2:$I$110,MATCH(106,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F107" s="0" t="str">
-        <f aca="false">IF($A107="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(106,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(106,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A107="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(106,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(106,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G107" s="0" t="str">
-        <f aca="false">IF($A107="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(106,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A107="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(106,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(107,BOM!$O$2:$O$108,0)),"",107)</f>
+        <f aca="false">IF(ISNA(MATCH(107,BOM!$O$2:$O$110,0)),"",107)</f>
         <v/>
       </c>
       <c r="B108" s="0" t="str">
-        <f aca="false">IF($A108="","",INDEX(BOM!$B$2:$B$108,MATCH(107,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A108="","",INDEX(BOM!$B$2:$B$110,MATCH(107,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C108" s="0" t="str">
-        <f aca="false">IF($A108="","",INDEX(BOM!$G$2:$G$108,MATCH(107,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A108="","",INDEX(BOM!$G$2:$G$110,MATCH(107,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D108" s="9" t="str">
-        <f aca="false">IF($A108="","",INDEX(BOM!$H$2:$H$108,MATCH(107,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A108="","",INDEX(BOM!$H$2:$H$110,MATCH(107,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E108" s="9" t="str">
-        <f aca="false">IF($A108="","",INDEX(BOM!$I$2:$I$108,MATCH(107,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A108="","",INDEX(BOM!$I$2:$I$110,MATCH(107,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F108" s="0" t="str">
-        <f aca="false">IF($A108="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(107,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(107,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A108="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(107,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(107,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G108" s="0" t="str">
-        <f aca="false">IF($A108="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(107,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A108="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(107,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(108,BOM!$O$2:$O$108,0)),"",108)</f>
+        <f aca="false">IF(ISNA(MATCH(108,BOM!$O$2:$O$110,0)),"",108)</f>
         <v/>
       </c>
       <c r="B109" s="0" t="str">
-        <f aca="false">IF($A109="","",INDEX(BOM!$B$2:$B$108,MATCH(108,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A109="","",INDEX(BOM!$B$2:$B$110,MATCH(108,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C109" s="0" t="str">
-        <f aca="false">IF($A109="","",INDEX(BOM!$G$2:$G$108,MATCH(108,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A109="","",INDEX(BOM!$G$2:$G$110,MATCH(108,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D109" s="9" t="str">
-        <f aca="false">IF($A109="","",INDEX(BOM!$H$2:$H$108,MATCH(108,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A109="","",INDEX(BOM!$H$2:$H$110,MATCH(108,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E109" s="9" t="str">
-        <f aca="false">IF($A109="","",INDEX(BOM!$I$2:$I$108,MATCH(108,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A109="","",INDEX(BOM!$I$2:$I$110,MATCH(108,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F109" s="0" t="str">
-        <f aca="false">IF($A109="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(108,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(108,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A109="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(108,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(108,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G109" s="0" t="str">
-        <f aca="false">IF($A109="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(108,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A109="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(108,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(109,BOM!$O$2:$O$108,0)),"",109)</f>
+        <f aca="false">IF(ISNA(MATCH(109,BOM!$O$2:$O$110,0)),"",109)</f>
         <v/>
       </c>
       <c r="B110" s="0" t="str">
-        <f aca="false">IF($A110="","",INDEX(BOM!$B$2:$B$108,MATCH(109,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A110="","",INDEX(BOM!$B$2:$B$110,MATCH(109,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C110" s="0" t="str">
-        <f aca="false">IF($A110="","",INDEX(BOM!$G$2:$G$108,MATCH(109,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A110="","",INDEX(BOM!$G$2:$G$110,MATCH(109,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D110" s="9" t="str">
-        <f aca="false">IF($A110="","",INDEX(BOM!$H$2:$H$108,MATCH(109,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A110="","",INDEX(BOM!$H$2:$H$110,MATCH(109,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E110" s="9" t="str">
-        <f aca="false">IF($A110="","",INDEX(BOM!$I$2:$I$108,MATCH(109,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A110="","",INDEX(BOM!$I$2:$I$110,MATCH(109,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F110" s="0" t="str">
-        <f aca="false">IF($A110="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(109,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(109,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A110="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(109,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(109,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G110" s="0" t="str">
-        <f aca="false">IF($A110="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(109,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A110="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(109,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(110,BOM!$O$2:$O$108,0)),"",110)</f>
+        <f aca="false">IF(ISNA(MATCH(110,BOM!$O$2:$O$110,0)),"",110)</f>
         <v/>
       </c>
       <c r="B111" s="0" t="str">
-        <f aca="false">IF($A111="","",INDEX(BOM!$B$2:$B$108,MATCH(110,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A111="","",INDEX(BOM!$B$2:$B$110,MATCH(110,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C111" s="0" t="str">
-        <f aca="false">IF($A111="","",INDEX(BOM!$G$2:$G$108,MATCH(110,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A111="","",INDEX(BOM!$G$2:$G$110,MATCH(110,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D111" s="9" t="str">
-        <f aca="false">IF($A111="","",INDEX(BOM!$H$2:$H$108,MATCH(110,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A111="","",INDEX(BOM!$H$2:$H$110,MATCH(110,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E111" s="9" t="str">
-        <f aca="false">IF($A111="","",INDEX(BOM!$I$2:$I$108,MATCH(110,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A111="","",INDEX(BOM!$I$2:$I$110,MATCH(110,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F111" s="0" t="str">
-        <f aca="false">IF($A111="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(110,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(110,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A111="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(110,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(110,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G111" s="0" t="str">
-        <f aca="false">IF($A111="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(110,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A111="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(110,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(111,BOM!$O$2:$O$108,0)),"",111)</f>
+        <f aca="false">IF(ISNA(MATCH(111,BOM!$O$2:$O$110,0)),"",111)</f>
         <v/>
       </c>
       <c r="B112" s="0" t="str">
-        <f aca="false">IF($A112="","",INDEX(BOM!$B$2:$B$108,MATCH(111,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A112="","",INDEX(BOM!$B$2:$B$110,MATCH(111,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C112" s="0" t="str">
-        <f aca="false">IF($A112="","",INDEX(BOM!$G$2:$G$108,MATCH(111,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A112="","",INDEX(BOM!$G$2:$G$110,MATCH(111,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D112" s="9" t="str">
-        <f aca="false">IF($A112="","",INDEX(BOM!$H$2:$H$108,MATCH(111,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A112="","",INDEX(BOM!$H$2:$H$110,MATCH(111,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E112" s="9" t="str">
-        <f aca="false">IF($A112="","",INDEX(BOM!$I$2:$I$108,MATCH(111,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A112="","",INDEX(BOM!$I$2:$I$110,MATCH(111,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F112" s="0" t="str">
-        <f aca="false">IF($A112="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(111,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(111,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A112="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(111,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(111,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G112" s="0" t="str">
-        <f aca="false">IF($A112="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(111,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A112="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(111,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(112,BOM!$O$2:$O$108,0)),"",112)</f>
+        <f aca="false">IF(ISNA(MATCH(112,BOM!$O$2:$O$110,0)),"",112)</f>
         <v/>
       </c>
       <c r="B113" s="0" t="str">
-        <f aca="false">IF($A113="","",INDEX(BOM!$B$2:$B$108,MATCH(112,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A113="","",INDEX(BOM!$B$2:$B$110,MATCH(112,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C113" s="0" t="str">
-        <f aca="false">IF($A113="","",INDEX(BOM!$G$2:$G$108,MATCH(112,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A113="","",INDEX(BOM!$G$2:$G$110,MATCH(112,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D113" s="9" t="str">
-        <f aca="false">IF($A113="","",INDEX(BOM!$H$2:$H$108,MATCH(112,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A113="","",INDEX(BOM!$H$2:$H$110,MATCH(112,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E113" s="9" t="str">
-        <f aca="false">IF($A113="","",INDEX(BOM!$I$2:$I$108,MATCH(112,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A113="","",INDEX(BOM!$I$2:$I$110,MATCH(112,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F113" s="0" t="str">
-        <f aca="false">IF($A113="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(112,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(112,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A113="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(112,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(112,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G113" s="0" t="str">
-        <f aca="false">IF($A113="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(112,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A113="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(112,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(113,BOM!$O$2:$O$108,0)),"",113)</f>
+        <f aca="false">IF(ISNA(MATCH(113,BOM!$O$2:$O$110,0)),"",113)</f>
         <v/>
       </c>
       <c r="B114" s="0" t="str">
-        <f aca="false">IF($A114="","",INDEX(BOM!$B$2:$B$108,MATCH(113,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A114="","",INDEX(BOM!$B$2:$B$110,MATCH(113,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C114" s="0" t="str">
-        <f aca="false">IF($A114="","",INDEX(BOM!$G$2:$G$108,MATCH(113,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A114="","",INDEX(BOM!$G$2:$G$110,MATCH(113,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D114" s="9" t="str">
-        <f aca="false">IF($A114="","",INDEX(BOM!$H$2:$H$108,MATCH(113,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A114="","",INDEX(BOM!$H$2:$H$110,MATCH(113,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E114" s="9" t="str">
-        <f aca="false">IF($A114="","",INDEX(BOM!$I$2:$I$108,MATCH(113,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A114="","",INDEX(BOM!$I$2:$I$110,MATCH(113,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F114" s="0" t="str">
-        <f aca="false">IF($A114="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(113,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(113,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A114="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(113,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(113,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G114" s="0" t="str">
-        <f aca="false">IF($A114="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(113,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A114="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(113,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(114,BOM!$O$2:$O$108,0)),"",114)</f>
+        <f aca="false">IF(ISNA(MATCH(114,BOM!$O$2:$O$110,0)),"",114)</f>
         <v/>
       </c>
       <c r="B115" s="0" t="str">
-        <f aca="false">IF($A115="","",INDEX(BOM!$B$2:$B$108,MATCH(114,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A115="","",INDEX(BOM!$B$2:$B$110,MATCH(114,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C115" s="0" t="str">
-        <f aca="false">IF($A115="","",INDEX(BOM!$G$2:$G$108,MATCH(114,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A115="","",INDEX(BOM!$G$2:$G$110,MATCH(114,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D115" s="9" t="str">
-        <f aca="false">IF($A115="","",INDEX(BOM!$H$2:$H$108,MATCH(114,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A115="","",INDEX(BOM!$H$2:$H$110,MATCH(114,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E115" s="9" t="str">
-        <f aca="false">IF($A115="","",INDEX(BOM!$I$2:$I$108,MATCH(114,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A115="","",INDEX(BOM!$I$2:$I$110,MATCH(114,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F115" s="0" t="str">
-        <f aca="false">IF($A115="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(114,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(114,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A115="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(114,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(114,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G115" s="0" t="str">
-        <f aca="false">IF($A115="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(114,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A115="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(114,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(115,BOM!$O$2:$O$108,0)),"",115)</f>
+        <f aca="false">IF(ISNA(MATCH(115,BOM!$O$2:$O$110,0)),"",115)</f>
         <v/>
       </c>
       <c r="B116" s="0" t="str">
-        <f aca="false">IF($A116="","",INDEX(BOM!$B$2:$B$108,MATCH(115,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A116="","",INDEX(BOM!$B$2:$B$110,MATCH(115,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C116" s="0" t="str">
-        <f aca="false">IF($A116="","",INDEX(BOM!$G$2:$G$108,MATCH(115,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A116="","",INDEX(BOM!$G$2:$G$110,MATCH(115,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D116" s="9" t="str">
-        <f aca="false">IF($A116="","",INDEX(BOM!$H$2:$H$108,MATCH(115,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A116="","",INDEX(BOM!$H$2:$H$110,MATCH(115,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E116" s="9" t="str">
-        <f aca="false">IF($A116="","",INDEX(BOM!$I$2:$I$108,MATCH(115,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A116="","",INDEX(BOM!$I$2:$I$110,MATCH(115,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F116" s="0" t="str">
-        <f aca="false">IF($A116="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(115,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(115,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A116="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(115,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(115,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G116" s="0" t="str">
-        <f aca="false">IF($A116="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(115,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A116="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(115,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(116,BOM!$O$2:$O$108,0)),"",116)</f>
+        <f aca="false">IF(ISNA(MATCH(116,BOM!$O$2:$O$110,0)),"",116)</f>
         <v/>
       </c>
       <c r="B117" s="0" t="str">
-        <f aca="false">IF($A117="","",INDEX(BOM!$B$2:$B$108,MATCH(116,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A117="","",INDEX(BOM!$B$2:$B$110,MATCH(116,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C117" s="0" t="str">
-        <f aca="false">IF($A117="","",INDEX(BOM!$G$2:$G$108,MATCH(116,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A117="","",INDEX(BOM!$G$2:$G$110,MATCH(116,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D117" s="9" t="str">
-        <f aca="false">IF($A117="","",INDEX(BOM!$H$2:$H$108,MATCH(116,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A117="","",INDEX(BOM!$H$2:$H$110,MATCH(116,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E117" s="9" t="str">
-        <f aca="false">IF($A117="","",INDEX(BOM!$I$2:$I$108,MATCH(116,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A117="","",INDEX(BOM!$I$2:$I$110,MATCH(116,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F117" s="0" t="str">
-        <f aca="false">IF($A117="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(116,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(116,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A117="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(116,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(116,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G117" s="0" t="str">
-        <f aca="false">IF($A117="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(116,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A117="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(116,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(117,BOM!$O$2:$O$108,0)),"",117)</f>
+        <f aca="false">IF(ISNA(MATCH(117,BOM!$O$2:$O$110,0)),"",117)</f>
         <v/>
       </c>
       <c r="B118" s="0" t="str">
-        <f aca="false">IF($A118="","",INDEX(BOM!$B$2:$B$108,MATCH(117,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A118="","",INDEX(BOM!$B$2:$B$110,MATCH(117,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C118" s="0" t="str">
-        <f aca="false">IF($A118="","",INDEX(BOM!$G$2:$G$108,MATCH(117,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A118="","",INDEX(BOM!$G$2:$G$110,MATCH(117,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D118" s="9" t="str">
-        <f aca="false">IF($A118="","",INDEX(BOM!$H$2:$H$108,MATCH(117,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A118="","",INDEX(BOM!$H$2:$H$110,MATCH(117,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E118" s="9" t="str">
-        <f aca="false">IF($A118="","",INDEX(BOM!$I$2:$I$108,MATCH(117,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A118="","",INDEX(BOM!$I$2:$I$110,MATCH(117,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F118" s="0" t="str">
-        <f aca="false">IF($A118="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(117,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(117,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A118="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(117,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(117,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G118" s="0" t="str">
-        <f aca="false">IF($A118="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(117,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A118="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(117,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(118,BOM!$O$2:$O$108,0)),"",118)</f>
+        <f aca="false">IF(ISNA(MATCH(118,BOM!$O$2:$O$110,0)),"",118)</f>
         <v/>
       </c>
       <c r="B119" s="0" t="str">
-        <f aca="false">IF($A119="","",INDEX(BOM!$B$2:$B$108,MATCH(118,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A119="","",INDEX(BOM!$B$2:$B$110,MATCH(118,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C119" s="0" t="str">
-        <f aca="false">IF($A119="","",INDEX(BOM!$G$2:$G$108,MATCH(118,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A119="","",INDEX(BOM!$G$2:$G$110,MATCH(118,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D119" s="9" t="str">
-        <f aca="false">IF($A119="","",INDEX(BOM!$H$2:$H$108,MATCH(118,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A119="","",INDEX(BOM!$H$2:$H$110,MATCH(118,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E119" s="9" t="str">
-        <f aca="false">IF($A119="","",INDEX(BOM!$I$2:$I$108,MATCH(118,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A119="","",INDEX(BOM!$I$2:$I$110,MATCH(118,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F119" s="0" t="str">
-        <f aca="false">IF($A119="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(118,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(118,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A119="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(118,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(118,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G119" s="0" t="str">
-        <f aca="false">IF($A119="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(118,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A119="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(118,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(119,BOM!$O$2:$O$108,0)),"",119)</f>
+        <f aca="false">IF(ISNA(MATCH(119,BOM!$O$2:$O$110,0)),"",119)</f>
         <v/>
       </c>
       <c r="B120" s="0" t="str">
-        <f aca="false">IF($A120="","",INDEX(BOM!$B$2:$B$108,MATCH(119,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A120="","",INDEX(BOM!$B$2:$B$110,MATCH(119,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C120" s="0" t="str">
-        <f aca="false">IF($A120="","",INDEX(BOM!$G$2:$G$108,MATCH(119,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A120="","",INDEX(BOM!$G$2:$G$110,MATCH(119,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D120" s="9" t="str">
-        <f aca="false">IF($A120="","",INDEX(BOM!$H$2:$H$108,MATCH(119,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A120="","",INDEX(BOM!$H$2:$H$110,MATCH(119,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E120" s="9" t="str">
-        <f aca="false">IF($A120="","",INDEX(BOM!$I$2:$I$108,MATCH(119,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A120="","",INDEX(BOM!$I$2:$I$110,MATCH(119,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F120" s="0" t="str">
-        <f aca="false">IF($A120="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(119,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(119,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A120="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(119,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(119,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G120" s="0" t="str">
-        <f aca="false">IF($A120="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(119,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A120="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(119,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="str">
-        <f aca="false">IF(ISNA(MATCH(120,BOM!$O$2:$O$108,0)),"",120)</f>
+        <f aca="false">IF(ISNA(MATCH(120,BOM!$O$2:$O$110,0)),"",120)</f>
         <v/>
       </c>
       <c r="B121" s="0" t="str">
-        <f aca="false">IF($A121="","",INDEX(BOM!$B$2:$B$108,MATCH(120,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A121="","",INDEX(BOM!$B$2:$B$110,MATCH(120,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="C121" s="0" t="str">
-        <f aca="false">IF($A121="","",INDEX(BOM!$G$2:$G$108,MATCH(120,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A121="","",INDEX(BOM!$G$2:$G$110,MATCH(120,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="D121" s="9" t="str">
-        <f aca="false">IF($A121="","",INDEX(BOM!$H$2:$H$108,MATCH(120,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A121="","",INDEX(BOM!$H$2:$H$110,MATCH(120,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="E121" s="9" t="str">
-        <f aca="false">IF($A121="","",INDEX(BOM!$I$2:$I$108,MATCH(120,BOM!$O$2:$O$108,0)))</f>
+        <f aca="false">IF($A121="","",INDEX(BOM!$I$2:$I$110,MATCH(120,BOM!$O$2:$O$110,0)))</f>
         <v/>
       </c>
       <c r="F121" s="0" t="str">
-        <f aca="false">IF($A121="","",IF(INDEX(BOM!$K$2:$K$108,MATCH(120,BOM!$O$2:$O$108,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$108,MATCH(120,BOM!$O$2:$O$108,0)),"open on amazon.ca")))</f>
+        <f aca="false">IF($A121="","",IF(INDEX(BOM!$K$2:$K$110,MATCH(120,BOM!$O$2:$O$110,0))="","",HYPERLINK(INDEX(BOM!$K$2:$K$110,MATCH(120,BOM!$O$2:$O$110,0)),"open on amazon.ca")))</f>
         <v/>
       </c>
       <c r="G121" s="0" t="str">
-        <f aca="false">IF($A121="","",HYPERLINK(INDEX(BOM!$L$2:$L$108,MATCH(120,BOM!$O$2:$O$108,0)),"search"))</f>
+        <f aca="false">IF($A121="","",HYPERLINK(INDEX(BOM!$L$2:$L$110,MATCH(120,BOM!$O$2:$O$110,0)),"search"))</f>
         <v/>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="10" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E123" s="9" t="n">
         <f aca="false">SUM(E2:E121)</f>
-        <v>2189.97</v>
+        <v>2168.73</v>
       </c>
     </row>
   </sheetData>
@@ -11906,47 +12007,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>
